--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -6806,9 +6806,7 @@
       <c r="D11" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="49" t="s">
-        <v>111</v>
-      </c>
+      <c r="E11" s="48"/>
       <c r="F11" s="49" t="s">
         <v>111</v>
       </c>

--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -6752,8 +6752,8 @@
       <c r="D8" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="29">
-        <v>20</v>
+      <c s="29" r="E8" t="n">
+        <v>10</v>
       </c>
       <c r="F8" s="29">
         <v>20</v>
@@ -7097,8 +7097,8 @@
       <c r="B8" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="61">
-        <v>-10</v>
+      <c s="61" r="C8" t="n">
+        <v>-5</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -7228,9 +7228,9 @@
       <c r="B14" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="69">
-        <f>Parameters!D24</f>
-        <v>20</v>
+      <c s="69" r="C14" t="n">
+        <f>IF(C6="RA60",Parameters!D27,Parameters!D24)</f>
+        <v>10</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -7832,7 +7832,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="whole" sqref="C8" xr:uid="{00000000-0002-0000-0500-000003000000}">
-      <formula1>-20</formula1>
+      <formula1>-C14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="whole" sqref="C9" xr:uid="{00000000-0002-0000-0500-000004000000}">
@@ -11637,10 +11637,8 @@
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="90" t="inlineStr">
-        <is>
-          <t>Sweep 使用 40 格 R；计算器按型号换算。</t>
-        </is>
+      <c s="90" r="F23" t="str">
+        <v>Sweep 使用 8 系 C、40 格 R。</v>
       </c>
       <c r="G23" s="91"/>
       <c r="H23" s="91"/>
@@ -11654,8 +11652,8 @@
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="62" t="s">
-        <v>67</v>
+      <c s="62" r="B24" t="str">
+        <v>HSC · 8 系</v>
       </c>
       <c r="C24" s="73"/>
       <c r="D24" s="69">
@@ -11719,11 +11717,15 @@
       <c r="N26" s="82"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="12" customHeight="1">
+    <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c s="62" r="B27" t="str">
+        <v>HSC · 6 系</v>
+      </c>
+      <c s="73" r="C27"/>
+      <c s="69" r="D27" t="n">
+        <v>10</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -11979,7 +11981,8 @@
       <c r="O41" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="D5:H5"/>
@@ -19058,9 +19061,9 @@
         <f>Calculator!C7</f>
         <v>-12</v>
       </c>
-      <c r="D165" s="117">
+      <c s="117" r="D165" t="n">
         <f>Calculator!C8</f>
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="E165" s="117">
         <f>Calculator!C9</f>
@@ -19114,8 +19117,8 @@
         <f>MIN(4,MAX(1,INT((1+C165/Parameters!$D$23)*4)+1))</f>
         <v>3</v>
       </c>
-      <c r="R165" s="117">
-        <f>MIN(4,MAX(1,INT((1+D165/Parameters!$D$24)*4)+1))</f>
+      <c s="117" r="R165" t="n">
+        <f>MIN(4,MAX(1,INT((1+D165/Calculator!$C$14)*4)+1))</f>
         <v>3</v>
       </c>
       <c r="S165" s="117">
@@ -19126,8 +19129,8 @@
         <f>MAX(0,MIN(1,(1+C165/Parameters!$D$23)*4-(Q165-1)))</f>
         <v>0</v>
       </c>
-      <c r="U165" s="117">
-        <f>MAX(0,MIN(1,(1+D165/Parameters!$D$24)*4-(R165-1)))</f>
+      <c s="117" r="U165" t="n">
+        <f>MAX(0,MIN(1,(1+D165/Calculator!$C$14)*4-(R165-1)))</f>
         <v>0</v>
       </c>
       <c r="V165" s="117">

--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A79284-0296-47CC-94EA-B1A0D79C5356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E71426E-0C2C-43A5-9E07-AAA127F4B1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -1880,11 +1880,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1899,13 +1899,13 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1920,28 +1920,28 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1950,7 +1950,7 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2082,26 +2082,53 @@
     <xf numFmtId="0" fontId="82" fillId="71" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2109,41 +2136,23 @@
     <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2159,18 +2168,6 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6585,14 +6582,14 @@
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -6643,7 +6640,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="74" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="6"/>
@@ -6663,7 +6660,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="70"/>
+      <c r="B7" s="74"/>
       <c r="C7" s="6"/>
       <c r="D7" s="19" t="s">
         <v>77</v>
@@ -6746,9 +6743,7 @@
       <c r="F11" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="22" t="s">
-        <v>83</v>
-      </c>
+      <c r="G11" s="21"/>
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" ht="31" customHeight="1">
@@ -6797,40 +6792,40 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="67"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="25" customHeight="1">
@@ -6912,20 +6907,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -6955,15 +6950,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6994,13 +6989,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -7038,16 +7033,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="78">
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="85">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>1736.47</v>
       </c>
-      <c r="J8" s="79"/>
+      <c r="J8" s="86"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -7085,16 +7080,16 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="78">
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="85">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1519.2</v>
       </c>
-      <c r="J10" s="79"/>
+      <c r="J10" s="86"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -7146,13 +7141,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="74" t="s">
+      <c r="F13" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -7170,11 +7165,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="80" t="s">
+      <c r="F14" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
       <c r="I14" s="34">
         <f>Samples!F165</f>
         <v>3650</v>
@@ -7199,11 +7194,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="77" t="s">
+      <c r="F15" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="35">
         <f>Samples!I165</f>
         <v>3431</v>
@@ -7223,11 +7218,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="83" t="s">
+      <c r="F16" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
       <c r="I16" s="34">
         <f>Samples!J165</f>
         <v>1750</v>
@@ -7247,11 +7242,11 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="76" t="s">
+      <c r="F17" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="80"/>
       <c r="I17" s="35">
         <f>Samples!L165</f>
         <v>5181</v>
@@ -7293,11 +7288,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="80" t="s">
+      <c r="F19" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
       <c r="I19" s="34">
         <f>Samples!M165</f>
         <v>3600</v>
@@ -7317,11 +7312,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="77" t="s">
+      <c r="F20" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
       <c r="I20" s="35">
         <f>Samples!P165</f>
         <v>3096</v>
@@ -7358,11 +7353,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="83" t="s">
+      <c r="F22" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
       <c r="I22" s="37">
         <f>Samples!G165</f>
         <v>0.08</v>
@@ -7382,11 +7377,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="76" t="s">
+      <c r="F23" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
       <c r="I23" s="38">
         <f>Samples!K165</f>
         <v>0.35</v>
@@ -7406,11 +7401,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="80" t="s">
+      <c r="F24" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
       <c r="I24" s="37">
         <f>Samples!N165</f>
         <v>0.25</v>
@@ -7460,20 +7455,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="76"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="76"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -7734,17 +7729,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -7752,6 +7736,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -7808,20 +7803,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -7851,15 +7846,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7889,15 +7884,15 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8481,18 +8476,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8566,20 +8561,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -8609,15 +8604,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8647,15 +8642,15 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9239,18 +9234,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9324,20 +9319,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -9367,15 +9362,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9398,18 +9393,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9993,18 +9988,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10074,20 +10069,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -10117,15 +10112,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10148,18 +10143,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -10743,18 +10738,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="87"/>
-      <c r="I41" s="87"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10828,40 +10823,40 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="91" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -10885,21 +10880,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="75" t="s">
+      <c r="J5" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -11529,73 +11524,73 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
-      <c r="N22" s="75"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="81"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="31">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="90" t="s">
+      <c r="F23" s="93" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="91"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="94"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="94"/>
+      <c r="L23" s="94"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="82" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="82"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="33">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="94"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="94"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="94"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="81"/>
+      <c r="C25" s="78"/>
       <c r="D25" s="31">
         <v>40</v>
       </c>
@@ -11613,33 +11608,33 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="77" t="s">
+      <c r="B26" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="82"/>
+      <c r="C26" s="80"/>
       <c r="D26" s="33">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="92" t="s">
+      <c r="F26" s="95" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="89"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="89"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="82"/>
+      <c r="C27" s="80"/>
       <c r="D27" s="33">
         <v>10</v>
       </c>
@@ -11657,140 +11652,140 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="95"/>
-      <c r="D28" s="95"/>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="95"/>
-      <c r="H28" s="95"/>
-      <c r="I28" s="95"/>
-      <c r="J28" s="95"/>
-      <c r="K28" s="95"/>
-      <c r="L28" s="95"/>
-      <c r="M28" s="95"/>
-      <c r="N28" s="95"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89"/>
+      <c r="M28" s="89"/>
+      <c r="N28" s="89"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="93"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
-      <c r="L29" s="93"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="93"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="87"/>
+      <c r="N29" s="87"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="90"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="87"/>
+      <c r="M31" s="87"/>
+      <c r="N31" s="87"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="93"/>
-      <c r="C32" s="93"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="93"/>
-      <c r="I32" s="93"/>
-      <c r="J32" s="93"/>
-      <c r="K32" s="93"/>
-      <c r="L32" s="93"/>
-      <c r="M32" s="93"/>
-      <c r="N32" s="93"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="87"/>
+      <c r="M32" s="87"/>
+      <c r="N32" s="87"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="93"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="93"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="93"/>
-      <c r="I33" s="93"/>
-      <c r="J33" s="93"/>
-      <c r="K33" s="93"/>
-      <c r="L33" s="93"/>
-      <c r="M33" s="93"/>
-      <c r="N33" s="93"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
+      <c r="L33" s="87"/>
+      <c r="M33" s="87"/>
+      <c r="N33" s="87"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="93"/>
-      <c r="C34" s="93"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="93"/>
-      <c r="K34" s="93"/>
-      <c r="L34" s="93"/>
-      <c r="M34" s="93"/>
-      <c r="N34" s="93"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="87"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="87"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="87"/>
+      <c r="N34" s="87"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="93"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="93"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="93"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="93"/>
-      <c r="L35" s="93"/>
-      <c r="M35" s="93"/>
-      <c r="N35" s="93"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="87"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="87"/>
+      <c r="N35" s="87"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23.15" customHeight="1">
@@ -11897,14 +11892,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -11917,6 +11904,14 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11938,29 +11933,29 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="96" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
@@ -13631,29 +13626,29 @@
     </row>
     <row r="41" spans="1:22" ht="32" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="97" t="s">
+      <c r="B41" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="97"/>
-      <c r="D41" s="97"/>
-      <c r="E41" s="97"/>
-      <c r="F41" s="97"/>
-      <c r="G41" s="97"/>
-      <c r="H41" s="97"/>
-      <c r="I41" s="97"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="97"/>
-      <c r="L41" s="97"/>
-      <c r="M41" s="97"/>
-      <c r="N41" s="97"/>
-      <c r="O41" s="97"/>
-      <c r="P41" s="98"/>
-      <c r="Q41" s="98"/>
-      <c r="R41" s="98"/>
-      <c r="S41" s="98"/>
-      <c r="T41" s="98"/>
-      <c r="U41" s="98"/>
-      <c r="V41" s="98"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
+      <c r="N41" s="96"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="97"/>
+      <c r="Q41" s="97"/>
+      <c r="R41" s="97"/>
+      <c r="S41" s="97"/>
+      <c r="T41" s="97"/>
+      <c r="U41" s="97"/>
+      <c r="V41" s="97"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
@@ -15285,29 +15280,29 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="98" t="s">
+      <c r="B81" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="C81" s="98"/>
-      <c r="D81" s="98"/>
-      <c r="E81" s="98"/>
-      <c r="F81" s="98"/>
-      <c r="G81" s="98"/>
-      <c r="H81" s="98"/>
-      <c r="I81" s="98"/>
-      <c r="J81" s="98"/>
-      <c r="K81" s="98"/>
-      <c r="L81" s="98"/>
-      <c r="M81" s="98"/>
-      <c r="N81" s="98"/>
-      <c r="O81" s="98"/>
-      <c r="P81" s="98"/>
-      <c r="Q81" s="98"/>
-      <c r="R81" s="98"/>
-      <c r="S81" s="98"/>
-      <c r="T81" s="98"/>
-      <c r="U81" s="98"/>
-      <c r="V81" s="98"/>
+      <c r="C81" s="97"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="97"/>
+      <c r="F81" s="97"/>
+      <c r="G81" s="97"/>
+      <c r="H81" s="97"/>
+      <c r="I81" s="97"/>
+      <c r="J81" s="97"/>
+      <c r="K81" s="97"/>
+      <c r="L81" s="97"/>
+      <c r="M81" s="97"/>
+      <c r="N81" s="97"/>
+      <c r="O81" s="97"/>
+      <c r="P81" s="97"/>
+      <c r="Q81" s="97"/>
+      <c r="R81" s="97"/>
+      <c r="S81" s="97"/>
+      <c r="T81" s="97"/>
+      <c r="U81" s="97"/>
+      <c r="V81" s="97"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -16938,29 +16933,29 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="98" t="s">
+      <c r="B121" s="97" t="s">
         <v>96</v>
       </c>
-      <c r="C121" s="98"/>
-      <c r="D121" s="98"/>
-      <c r="E121" s="98"/>
-      <c r="F121" s="98"/>
-      <c r="G121" s="98"/>
-      <c r="H121" s="98"/>
-      <c r="I121" s="98"/>
-      <c r="J121" s="98"/>
-      <c r="K121" s="98"/>
-      <c r="L121" s="98"/>
-      <c r="M121" s="98"/>
-      <c r="N121" s="98"/>
-      <c r="O121" s="98"/>
-      <c r="P121" s="98"/>
-      <c r="Q121" s="98"/>
-      <c r="R121" s="98"/>
-      <c r="S121" s="98"/>
-      <c r="T121" s="98"/>
-      <c r="U121" s="98"/>
-      <c r="V121" s="98"/>
+      <c r="C121" s="97"/>
+      <c r="D121" s="97"/>
+      <c r="E121" s="97"/>
+      <c r="F121" s="97"/>
+      <c r="G121" s="97"/>
+      <c r="H121" s="97"/>
+      <c r="I121" s="97"/>
+      <c r="J121" s="97"/>
+      <c r="K121" s="97"/>
+      <c r="L121" s="97"/>
+      <c r="M121" s="97"/>
+      <c r="N121" s="97"/>
+      <c r="O121" s="97"/>
+      <c r="P121" s="97"/>
+      <c r="Q121" s="97"/>
+      <c r="R121" s="97"/>
+      <c r="S121" s="97"/>
+      <c r="T121" s="97"/>
+      <c r="U121" s="97"/>
+      <c r="V121" s="97"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -18852,29 +18847,29 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="99" t="s">
+      <c r="B161" s="98" t="s">
         <v>97</v>
       </c>
-      <c r="C161" s="99"/>
-      <c r="D161" s="99"/>
-      <c r="E161" s="99"/>
-      <c r="F161" s="99"/>
-      <c r="G161" s="99"/>
-      <c r="H161" s="99"/>
-      <c r="I161" s="99"/>
-      <c r="J161" s="99"/>
-      <c r="K161" s="99"/>
-      <c r="L161" s="99"/>
-      <c r="M161" s="99"/>
-      <c r="N161" s="99"/>
-      <c r="O161" s="99"/>
-      <c r="P161" s="99"/>
-      <c r="Q161" s="99"/>
-      <c r="R161" s="99"/>
-      <c r="S161" s="99"/>
-      <c r="T161" s="99"/>
-      <c r="U161" s="99"/>
-      <c r="V161" s="99"/>
+      <c r="C161" s="98"/>
+      <c r="D161" s="98"/>
+      <c r="E161" s="98"/>
+      <c r="F161" s="98"/>
+      <c r="G161" s="98"/>
+      <c r="H161" s="98"/>
+      <c r="I161" s="98"/>
+      <c r="J161" s="98"/>
+      <c r="K161" s="98"/>
+      <c r="L161" s="98"/>
+      <c r="M161" s="98"/>
+      <c r="N161" s="98"/>
+      <c r="O161" s="98"/>
+      <c r="P161" s="98"/>
+      <c r="Q161" s="98"/>
+      <c r="R161" s="98"/>
+      <c r="S161" s="98"/>
+      <c r="T161" s="98"/>
+      <c r="U161" s="98"/>
+      <c r="V161" s="98"/>
     </row>
     <row r="164" spans="2:22" ht="44" customHeight="1">
       <c r="B164" s="63" t="s">

--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\damping-rx-sync-20261026\native\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E71426E-0C2C-43A5-9E07-AAA127F4B1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACEAC72-8851-44CF-AEBC-70E45295771A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="99">
   <si>
     <t>Valving</t>
   </si>
@@ -366,6 +366,10 @@
   </si>
   <si>
     <t>Calculator</t>
+  </si>
+  <si>
+    <t>Type-A</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1880,11 +1884,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1899,13 +1903,13 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1920,28 +1924,28 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1950,7 +1954,7 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2082,17 +2086,56 @@
     <xf numFmtId="0" fontId="82" fillId="71" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2106,35 +2149,8 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2142,32 +2158,17 @@
     <xf numFmtId="2" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6199,19 +6200,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -6234,25 +6230,20 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -6275,25 +6266,20 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -6316,25 +6302,20 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -6357,7 +6338,7 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6582,14 +6563,14 @@
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -6640,7 +6621,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="74" t="s">
+      <c r="B6" s="87" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="6"/>
@@ -6660,7 +6641,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="74"/>
+      <c r="B7" s="87"/>
       <c r="C7" s="6"/>
       <c r="D7" s="19" t="s">
         <v>77</v>
@@ -6792,40 +6773,40 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="25" customHeight="1">
@@ -6907,20 +6888,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -6947,18 +6928,18 @@
         <v>0</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6989,13 +6970,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84"/>
-      <c r="J6" s="84"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -7033,16 +7014,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="82" t="s">
+      <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="85">
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="89">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>1736.47</v>
       </c>
-      <c r="J8" s="86"/>
+      <c r="J8" s="90"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -7080,16 +7061,16 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="82" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="85">
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="89">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1519.2</v>
       </c>
-      <c r="J10" s="86"/>
+      <c r="J10" s="90"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -7141,13 +7122,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="83" t="s">
+      <c r="F13" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -7165,11 +7146,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="77" t="s">
+      <c r="F14" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
       <c r="I14" s="34">
         <f>Samples!F165</f>
         <v>3650</v>
@@ -7194,11 +7175,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="79" t="s">
+      <c r="F15" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="35">
         <f>Samples!I165</f>
         <v>3431</v>
@@ -7218,11 +7199,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="81" t="s">
+      <c r="F16" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
       <c r="I16" s="34">
         <f>Samples!J165</f>
         <v>1750</v>
@@ -7242,11 +7223,11 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="82" t="s">
+      <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
       <c r="I17" s="35">
         <f>Samples!L165</f>
         <v>5181</v>
@@ -7288,11 +7269,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
       <c r="I19" s="34">
         <f>Samples!M165</f>
         <v>3600</v>
@@ -7312,11 +7293,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="79" t="s">
+      <c r="F20" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
       <c r="I20" s="35">
         <f>Samples!P165</f>
         <v>3096</v>
@@ -7353,11 +7334,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="81" t="s">
+      <c r="F22" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
       <c r="I22" s="37">
         <f>Samples!G165</f>
         <v>0.08</v>
@@ -7377,11 +7358,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="82" t="s">
+      <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
       <c r="I23" s="38">
         <f>Samples!K165</f>
         <v>0.35</v>
@@ -7401,11 +7382,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="77" t="s">
+      <c r="F24" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
       <c r="I24" s="37">
         <f>Samples!N165</f>
         <v>0.25</v>
@@ -7455,20 +7436,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="92" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="93"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -7729,6 +7710,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -7736,17 +7728,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -7803,20 +7784,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -7846,15 +7827,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7884,15 +7865,15 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8476,18 +8457,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94"/>
+      <c r="M41" s="94"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8561,20 +8542,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -8604,15 +8585,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8642,15 +8623,15 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9234,18 +9215,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94"/>
+      <c r="M41" s="94"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9319,20 +9300,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -9362,15 +9343,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9393,18 +9374,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9988,18 +9969,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94"/>
+      <c r="M41" s="94"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10069,20 +10050,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -10112,15 +10093,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10143,18 +10124,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -10738,18 +10719,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94"/>
+      <c r="M41" s="94"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10823,40 +10804,40 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="92"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
-      <c r="N3" s="92"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -10880,21 +10861,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="84" t="s">
+      <c r="D5" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="84" t="s">
+      <c r="J5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -11470,21 +11451,21 @@
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="42">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="K19" s="37">
         <f>(J19+L19)/2</f>
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="L19" s="42">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="M19" s="37">
         <f>(L19+N19)/2</f>
-        <v>0.59000000000000008</v>
+        <v>0.65</v>
       </c>
       <c r="N19" s="42">
-        <v>0.56000000000000005</v>
+        <v>0.62</v>
       </c>
       <c r="O19" s="1"/>
     </row>
@@ -11524,73 +11505,73 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="81" t="s">
+      <c r="B23" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="78"/>
+      <c r="C23" s="75"/>
       <c r="D23" s="31">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="93" t="s">
+      <c r="F23" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="78"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="82" t="s">
+      <c r="B24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="80"/>
+      <c r="C24" s="67"/>
       <c r="D24" s="33">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="94"/>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="94"/>
-      <c r="N24" s="94"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="78"/>
+      <c r="N24" s="78"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="81" t="s">
+      <c r="B25" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="78"/>
+      <c r="C25" s="75"/>
       <c r="D25" s="31">
         <v>40</v>
       </c>
@@ -11608,33 +11589,33 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="80"/>
+      <c r="C26" s="67"/>
       <c r="D26" s="33">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="95" t="s">
+      <c r="F26" s="79" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="92"/>
-      <c r="H26" s="92"/>
-      <c r="I26" s="92"/>
-      <c r="J26" s="92"/>
-      <c r="K26" s="92"/>
-      <c r="L26" s="92"/>
-      <c r="M26" s="92"/>
-      <c r="N26" s="92"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="82" t="s">
+      <c r="B27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="80"/>
+      <c r="C27" s="67"/>
       <c r="D27" s="33">
         <v>10</v>
       </c>
@@ -11652,140 +11633,140 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="89"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="82"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="87"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="87"/>
-      <c r="G29" s="87"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="87"/>
-      <c r="N29" s="87"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="M29" s="80"/>
+      <c r="N29" s="80"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="90"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="90"/>
-      <c r="K30" s="90"/>
-      <c r="L30" s="90"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="90"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83"/>
+      <c r="M30" s="83"/>
+      <c r="N30" s="83"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="87"/>
-      <c r="C31" s="87"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="87"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="87"/>
-      <c r="N31" s="87"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="80"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="80"/>
+      <c r="M31" s="80"/>
+      <c r="N31" s="80"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="87"/>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="87"/>
-      <c r="N32" s="87"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+      <c r="J32" s="80"/>
+      <c r="K32" s="80"/>
+      <c r="L32" s="80"/>
+      <c r="M32" s="80"/>
+      <c r="N32" s="80"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87"/>
-      <c r="N33" s="87"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="80"/>
+      <c r="L33" s="80"/>
+      <c r="M33" s="80"/>
+      <c r="N33" s="80"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="87"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="87"/>
-      <c r="G34" s="87"/>
-      <c r="H34" s="87"/>
-      <c r="I34" s="87"/>
-      <c r="J34" s="87"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="87"/>
-      <c r="N34" s="87"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="80"/>
+      <c r="L34" s="80"/>
+      <c r="M34" s="80"/>
+      <c r="N34" s="80"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="87"/>
-      <c r="C35" s="87"/>
-      <c r="D35" s="87"/>
-      <c r="E35" s="87"/>
-      <c r="F35" s="87"/>
-      <c r="G35" s="87"/>
-      <c r="H35" s="87"/>
-      <c r="I35" s="87"/>
-      <c r="J35" s="87"/>
-      <c r="K35" s="87"/>
-      <c r="L35" s="87"/>
-      <c r="M35" s="87"/>
-      <c r="N35" s="87"/>
+      <c r="B35" s="80"/>
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="80"/>
+      <c r="J35" s="80"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="80"/>
+      <c r="M35" s="80"/>
+      <c r="N35" s="80"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23.15" customHeight="1">
@@ -11892,6 +11873,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -11904,14 +11893,6 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11933,29 +11914,29 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="95" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
@@ -13626,29 +13607,29 @@
     </row>
     <row r="41" spans="1:22" ht="32" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="96" t="s">
+      <c r="B41" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
-      <c r="N41" s="96"/>
-      <c r="O41" s="96"/>
-      <c r="P41" s="97"/>
-      <c r="Q41" s="97"/>
-      <c r="R41" s="97"/>
-      <c r="S41" s="97"/>
-      <c r="T41" s="97"/>
-      <c r="U41" s="97"/>
-      <c r="V41" s="97"/>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="95"/>
+      <c r="I41" s="95"/>
+      <c r="J41" s="95"/>
+      <c r="K41" s="95"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="95"/>
+      <c r="N41" s="95"/>
+      <c r="O41" s="95"/>
+      <c r="P41" s="96"/>
+      <c r="Q41" s="96"/>
+      <c r="R41" s="96"/>
+      <c r="S41" s="96"/>
+      <c r="T41" s="96"/>
+      <c r="U41" s="96"/>
+      <c r="V41" s="96"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
@@ -15280,29 +15261,29 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="97" t="s">
+      <c r="B81" s="96" t="s">
         <v>95</v>
       </c>
-      <c r="C81" s="97"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="97"/>
-      <c r="F81" s="97"/>
-      <c r="G81" s="97"/>
-      <c r="H81" s="97"/>
-      <c r="I81" s="97"/>
-      <c r="J81" s="97"/>
-      <c r="K81" s="97"/>
-      <c r="L81" s="97"/>
-      <c r="M81" s="97"/>
-      <c r="N81" s="97"/>
-      <c r="O81" s="97"/>
-      <c r="P81" s="97"/>
-      <c r="Q81" s="97"/>
-      <c r="R81" s="97"/>
-      <c r="S81" s="97"/>
-      <c r="T81" s="97"/>
-      <c r="U81" s="97"/>
-      <c r="V81" s="97"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="96"/>
+      <c r="E81" s="96"/>
+      <c r="F81" s="96"/>
+      <c r="G81" s="96"/>
+      <c r="H81" s="96"/>
+      <c r="I81" s="96"/>
+      <c r="J81" s="96"/>
+      <c r="K81" s="96"/>
+      <c r="L81" s="96"/>
+      <c r="M81" s="96"/>
+      <c r="N81" s="96"/>
+      <c r="O81" s="96"/>
+      <c r="P81" s="96"/>
+      <c r="Q81" s="96"/>
+      <c r="R81" s="96"/>
+      <c r="S81" s="96"/>
+      <c r="T81" s="96"/>
+      <c r="U81" s="96"/>
+      <c r="V81" s="96"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -16933,29 +16914,29 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="97" t="s">
+      <c r="B121" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="C121" s="97"/>
-      <c r="D121" s="97"/>
-      <c r="E121" s="97"/>
-      <c r="F121" s="97"/>
-      <c r="G121" s="97"/>
-      <c r="H121" s="97"/>
-      <c r="I121" s="97"/>
-      <c r="J121" s="97"/>
-      <c r="K121" s="97"/>
-      <c r="L121" s="97"/>
-      <c r="M121" s="97"/>
-      <c r="N121" s="97"/>
-      <c r="O121" s="97"/>
-      <c r="P121" s="97"/>
-      <c r="Q121" s="97"/>
-      <c r="R121" s="97"/>
-      <c r="S121" s="97"/>
-      <c r="T121" s="97"/>
-      <c r="U121" s="97"/>
-      <c r="V121" s="97"/>
+      <c r="C121" s="96"/>
+      <c r="D121" s="96"/>
+      <c r="E121" s="96"/>
+      <c r="F121" s="96"/>
+      <c r="G121" s="96"/>
+      <c r="H121" s="96"/>
+      <c r="I121" s="96"/>
+      <c r="J121" s="96"/>
+      <c r="K121" s="96"/>
+      <c r="L121" s="96"/>
+      <c r="M121" s="96"/>
+      <c r="N121" s="96"/>
+      <c r="O121" s="96"/>
+      <c r="P121" s="96"/>
+      <c r="Q121" s="96"/>
+      <c r="R121" s="96"/>
+      <c r="S121" s="96"/>
+      <c r="T121" s="96"/>
+      <c r="U121" s="96"/>
+      <c r="V121" s="96"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -18847,29 +18828,29 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="98" t="s">
+      <c r="B161" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="C161" s="98"/>
-      <c r="D161" s="98"/>
-      <c r="E161" s="98"/>
-      <c r="F161" s="98"/>
-      <c r="G161" s="98"/>
-      <c r="H161" s="98"/>
-      <c r="I161" s="98"/>
-      <c r="J161" s="98"/>
-      <c r="K161" s="98"/>
-      <c r="L161" s="98"/>
-      <c r="M161" s="98"/>
-      <c r="N161" s="98"/>
-      <c r="O161" s="98"/>
-      <c r="P161" s="98"/>
-      <c r="Q161" s="98"/>
-      <c r="R161" s="98"/>
-      <c r="S161" s="98"/>
-      <c r="T161" s="98"/>
-      <c r="U161" s="98"/>
-      <c r="V161" s="98"/>
+      <c r="C161" s="97"/>
+      <c r="D161" s="97"/>
+      <c r="E161" s="97"/>
+      <c r="F161" s="97"/>
+      <c r="G161" s="97"/>
+      <c r="H161" s="97"/>
+      <c r="I161" s="97"/>
+      <c r="J161" s="97"/>
+      <c r="K161" s="97"/>
+      <c r="L161" s="97"/>
+      <c r="M161" s="97"/>
+      <c r="N161" s="97"/>
+      <c r="O161" s="97"/>
+      <c r="P161" s="97"/>
+      <c r="Q161" s="97"/>
+      <c r="R161" s="97"/>
+      <c r="S161" s="97"/>
+      <c r="T161" s="97"/>
+      <c r="U161" s="97"/>
+      <c r="V161" s="97"/>
     </row>
     <row r="164" spans="2:22" ht="44" customHeight="1">
       <c r="B164" s="63" t="s">

--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\damping-rx-sync-20261026\native\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACEAC72-8851-44CF-AEBC-70E45295771A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE25B4BC-4EB4-44EC-B003-32040F202683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -380,7 +380,7 @@
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="83">
+  <fonts count="82">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -548,13 +548,6 @@
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF667B91"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -927,7 +920,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="72">
+  <fills count="71">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -997,11 +990,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1285,7 +1273,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="73">
+  <borders count="72">
     <border>
       <left/>
       <right/>
@@ -1404,15 +1392,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFDCE4EB"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1884,11 +1863,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1903,10 +1882,10 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1921,10 +1900,10 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1939,10 +1918,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1975,56 +1954,59 @@
     <xf numFmtId="1" fontId="25" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="30" fillId="19" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="35" fillId="24" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="36" fillId="25" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="37" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="38" fillId="27" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="29" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="40" fillId="29" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="41" fillId="30" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="42" fillId="31" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="36" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="48" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="36" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="49" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="50" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="51" fillId="40" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="48" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="49" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="50" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="51" fillId="40" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="52" fillId="41" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="60" fillId="49" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="50" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="51" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2036,7 +2018,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="54" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="55" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2048,57 +2030,63 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="58" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="59" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="60" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="71" fillId="60" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="72" fillId="61" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="73" fillId="62" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="73" fillId="62" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="74" fillId="63" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="64" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="75" fillId="64" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="76" fillId="65" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="77" fillId="66" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="78" fillId="67" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="68" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="81" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="71" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2107,13 +2095,16 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2121,21 +2112,6 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2149,39 +2125,39 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="59" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="49" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="67" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="66" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2199,7 +2175,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3049,7 +3025,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3889,7 +3865,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4722,7 +4698,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -6542,7 +6518,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -6561,19 +6537,19 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="35" customHeight="1">
+    <row r="2" spans="1:8" ht="35.1" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" ht="25" customHeight="1">
+    <row r="3" spans="1:8" ht="24.95" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -6583,7 +6559,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" ht="32" customHeight="1">
+    <row r="4" spans="1:8" ht="32.1" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="6"/>
@@ -6601,7 +6577,7 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" ht="31" customHeight="1">
+    <row r="5" spans="1:8" ht="30.95" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="6"/>
@@ -6619,9 +6595,9 @@
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" ht="31" customHeight="1">
+    <row r="6" spans="1:8" ht="30.95" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="86" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="6"/>
@@ -6639,9 +6615,9 @@
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="31" customHeight="1">
+    <row r="7" spans="1:8" ht="30.95" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="87"/>
+      <c r="B7" s="86"/>
       <c r="C7" s="6"/>
       <c r="D7" s="19" t="s">
         <v>77</v>
@@ -6657,7 +6633,7 @@
       </c>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="31" customHeight="1">
+    <row r="8" spans="1:8" ht="30.95" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="23" t="s">
         <v>65</v>
@@ -6677,7 +6653,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="31" customHeight="1">
+    <row r="9" spans="1:8" ht="30.95" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="17" t="s">
         <v>76</v>
@@ -6697,7 +6673,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="31" customHeight="1">
+    <row r="10" spans="1:8" ht="30.95" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="8"/>
       <c r="C10" s="6"/>
@@ -6713,7 +6689,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="31" customHeight="1">
+    <row r="11" spans="1:8" ht="30.95" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="8"/>
       <c r="C11" s="6"/>
@@ -6727,7 +6703,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="31" customHeight="1">
+    <row r="12" spans="1:8" ht="30.95" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="8"/>
       <c r="C12" s="6"/>
@@ -6745,7 +6721,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="31" customHeight="1">
+    <row r="13" spans="1:8" ht="30.95" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="8"/>
       <c r="C13" s="6"/>
@@ -6759,7 +6735,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="25" customHeight="1">
+    <row r="14" spans="1:8" ht="24.95" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -6769,47 +6745,47 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="22" customHeight="1">
+    <row r="15" spans="1:8" ht="21.95" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="22" customHeight="1">
+    <row r="16" spans="1:8" ht="21.95" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="84"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="22" customHeight="1">
+    <row r="17" spans="1:8" ht="21.95" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="22" customHeight="1">
+    <row r="18" spans="1:8" ht="21.95" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="25" customHeight="1">
+    <row r="19" spans="1:8" ht="24.95" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -6819,7 +6795,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="25" customHeight="1">
+    <row r="20" spans="1:8" ht="24.95" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -6829,7 +6805,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="25" customHeight="1">
+    <row r="21" spans="1:8" ht="24.95" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -6860,7 +6836,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -6886,22 +6862,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -6922,7 +6898,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -6931,19 +6907,19 @@
         <v>98</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -6960,7 +6936,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="32" customHeight="1">
+    <row r="6" spans="1:15" ht="32.1" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="27" t="s">
         <v>59</v>
@@ -6970,20 +6946,20 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="28" customHeight="1">
+    <row r="7" spans="1:15" ht="27.95" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="28" t="s">
         <v>7</v>
@@ -7004,7 +6980,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="28" customHeight="1">
+    <row r="8" spans="1:15" ht="27.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="25" t="s">
         <v>9</v>
@@ -7014,23 +6990,23 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="89">
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="91">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>1736.47</v>
       </c>
-      <c r="J8" s="90"/>
+      <c r="J8" s="92"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="28" customHeight="1">
+    <row r="9" spans="1:15" ht="27.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="28" t="s">
         <v>20</v>
@@ -7051,7 +7027,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="28" customHeight="1">
+    <row r="10" spans="1:15" ht="27.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="27" t="s">
         <v>21</v>
@@ -7061,23 +7037,23 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="89">
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="91">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1519.2</v>
       </c>
-      <c r="J10" s="90"/>
+      <c r="J10" s="92"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -7094,7 +7070,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -7111,7 +7087,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="32" customHeight="1">
+    <row r="13" spans="1:15" ht="32.1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="27" t="s">
         <v>23</v>
@@ -7122,20 +7098,20 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="28" customHeight="1">
+    <row r="14" spans="1:15" ht="27.95" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="32" t="s">
         <v>24</v>
@@ -7146,11 +7122,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="91" t="s">
+      <c r="F14" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
       <c r="I14" s="34">
         <f>Samples!F165</f>
         <v>3650</v>
@@ -7164,7 +7140,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="28" customHeight="1">
+    <row r="15" spans="1:15" ht="27.95" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="27" t="s">
         <v>25</v>
@@ -7175,11 +7151,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="67"/>
-      <c r="H15" s="67"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
       <c r="I15" s="35">
         <f>Samples!I165</f>
         <v>3431</v>
@@ -7193,17 +7169,17 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="28" customHeight="1">
+    <row r="16" spans="1:15" ht="27.95" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="74" t="s">
+      <c r="F16" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
       <c r="I16" s="34">
         <f>Samples!J165</f>
         <v>1750</v>
@@ -7217,17 +7193,17 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="28" customHeight="1">
+    <row r="17" spans="1:15" ht="27.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="67"/>
-      <c r="H17" s="67"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
       <c r="I17" s="35">
         <f>Samples!L165</f>
         <v>5181</v>
@@ -7241,7 +7217,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="28" customHeight="1">
+    <row r="18" spans="1:15" ht="27.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="27" t="s">
         <v>28</v>
@@ -7263,17 +7239,17 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="28" customHeight="1">
+    <row r="19" spans="1:15" ht="27.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="91" t="s">
+      <c r="F19" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
       <c r="I19" s="34">
         <f>Samples!M165</f>
         <v>3600</v>
@@ -7287,17 +7263,17 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="28" customHeight="1">
+    <row r="20" spans="1:15" ht="27.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="67"/>
-      <c r="H20" s="67"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
       <c r="I20" s="35">
         <f>Samples!P165</f>
         <v>3096</v>
@@ -7311,7 +7287,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="28" customHeight="1">
+    <row r="21" spans="1:15" ht="27.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -7328,17 +7304,17 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="28" customHeight="1">
+    <row r="22" spans="1:15" ht="27.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="74" t="s">
+      <c r="F22" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
       <c r="I22" s="37">
         <f>Samples!G165</f>
         <v>0.08</v>
@@ -7352,17 +7328,17 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="28" customHeight="1">
+    <row r="23" spans="1:15" ht="27.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
       <c r="I23" s="38">
         <f>Samples!K165</f>
         <v>0.35</v>
@@ -7376,17 +7352,17 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="28" customHeight="1">
+    <row r="24" spans="1:15" ht="27.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="91" t="s">
+      <c r="F24" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
       <c r="I24" s="37">
         <f>Samples!N165</f>
         <v>0.25</v>
@@ -7400,7 +7376,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7417,7 +7393,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -7434,26 +7410,26 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="92" t="s">
+      <c r="B27" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
+      <c r="L27" s="88"/>
+      <c r="M27" s="88"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -7470,7 +7446,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -7487,7 +7463,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -7504,7 +7480,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -7521,7 +7497,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -7538,7 +7514,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -7555,7 +7531,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -7572,7 +7548,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -7589,7 +7565,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -7606,7 +7582,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -7623,7 +7599,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -7640,7 +7616,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -7657,7 +7633,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -7674,7 +7650,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -7691,7 +7667,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7710,17 +7686,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -7728,6 +7693,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -7759,7 +7735,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -7782,22 +7758,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -7818,7 +7794,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -7827,19 +7803,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -7856,7 +7832,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="27" t="s">
         <v>2</v>
@@ -7865,19 +7841,19 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -7894,7 +7870,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -7911,7 +7887,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -7928,7 +7904,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -7945,7 +7921,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -7962,7 +7938,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -7979,7 +7955,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -7996,7 +7972,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -8013,7 +7989,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -8030,7 +8006,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -8047,7 +8023,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8064,7 +8040,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -8081,7 +8057,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -8098,7 +8074,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -8115,7 +8091,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -8132,7 +8108,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -8149,7 +8125,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -8166,7 +8142,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -8183,7 +8159,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -8200,7 +8176,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -8217,7 +8193,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -8234,7 +8210,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -8251,7 +8227,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -8268,7 +8244,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -8285,7 +8261,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -8302,7 +8278,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -8319,7 +8295,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -8336,7 +8312,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -8353,7 +8329,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -8370,7 +8346,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -8387,7 +8363,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -8404,7 +8380,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -8421,7 +8397,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -8438,7 +8414,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -8455,24 +8431,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-      <c r="M41" s="94"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -8517,7 +8493,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -8540,22 +8516,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -8576,7 +8552,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -8585,19 +8561,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -8614,7 +8590,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="27" t="s">
         <v>3</v>
@@ -8623,19 +8599,19 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -8652,7 +8628,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -8669,7 +8645,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -8686,7 +8662,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -8703,7 +8679,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -8720,7 +8696,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -8737,7 +8713,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -8754,7 +8730,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -8771,7 +8747,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -8788,7 +8764,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -8805,7 +8781,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8822,7 +8798,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -8839,7 +8815,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -8856,7 +8832,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -8873,7 +8849,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -8890,7 +8866,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -8907,7 +8883,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -8924,7 +8900,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -8941,7 +8917,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -8958,7 +8934,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -8975,7 +8951,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -8992,7 +8968,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -9009,7 +8985,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -9026,7 +9002,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -9043,7 +9019,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -9060,7 +9036,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -9077,7 +9053,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -9094,7 +9070,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -9111,7 +9087,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -9128,7 +9104,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -9145,7 +9121,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -9162,7 +9138,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -9179,7 +9155,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -9196,7 +9172,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -9213,24 +9189,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-      <c r="M41" s="94"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -9275,7 +9251,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -9298,22 +9274,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -9334,7 +9310,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -9343,19 +9319,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -9372,24 +9348,24 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -9406,7 +9382,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -9423,7 +9399,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -9440,7 +9416,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -9457,7 +9433,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -9474,7 +9450,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -9491,7 +9467,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -9508,7 +9484,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -9525,7 +9501,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -9542,7 +9518,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -9559,7 +9535,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -9576,7 +9552,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -9593,7 +9569,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -9610,7 +9586,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -9627,7 +9603,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -9644,7 +9620,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -9661,7 +9637,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -9678,7 +9654,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -9695,7 +9671,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -9712,7 +9688,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -9729,7 +9705,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -9746,7 +9722,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -9763,7 +9739,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -9780,7 +9756,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -9797,7 +9773,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -9814,7 +9790,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -9831,7 +9807,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -9848,7 +9824,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -9865,7 +9841,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -9882,7 +9858,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -9899,7 +9875,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -9916,7 +9892,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -9933,7 +9909,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -9950,7 +9926,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -9967,24 +9943,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-      <c r="M41" s="94"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -10025,7 +10001,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -10048,22 +10024,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -10084,7 +10060,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10093,19 +10069,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14" customHeight="1">
+    <row r="5" spans="1:15" ht="14.1" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -10122,24 +10098,24 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="28" customHeight="1">
+    <row r="6" spans="1:15" ht="27.95" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.15" customHeight="1">
+    <row r="7" spans="1:15" ht="23.1" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -10156,7 +10132,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.15" customHeight="1">
+    <row r="8" spans="1:15" ht="23.1" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -10173,7 +10149,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.15" customHeight="1">
+    <row r="9" spans="1:15" ht="23.1" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -10190,7 +10166,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.15" customHeight="1">
+    <row r="10" spans="1:15" ht="23.1" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -10207,7 +10183,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.15" customHeight="1">
+    <row r="11" spans="1:15" ht="23.1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -10224,7 +10200,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.15" customHeight="1">
+    <row r="12" spans="1:15" ht="23.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -10241,7 +10217,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.15" customHeight="1">
+    <row r="13" spans="1:15" ht="23.1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -10258,7 +10234,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.15" customHeight="1">
+    <row r="14" spans="1:15" ht="23.1" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -10275,7 +10251,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.15" customHeight="1">
+    <row r="15" spans="1:15" ht="23.1" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -10292,7 +10268,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.15" customHeight="1">
+    <row r="16" spans="1:15" ht="23.1" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -10309,7 +10285,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.15" customHeight="1">
+    <row r="17" spans="1:15" ht="23.1" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -10326,7 +10302,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.15" customHeight="1">
+    <row r="18" spans="1:15" ht="23.1" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -10343,7 +10319,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.15" customHeight="1">
+    <row r="19" spans="1:15" ht="23.1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -10360,7 +10336,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.15" customHeight="1">
+    <row r="20" spans="1:15" ht="23.1" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -10377,7 +10353,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.15" customHeight="1">
+    <row r="21" spans="1:15" ht="23.1" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -10394,7 +10370,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.15" customHeight="1">
+    <row r="22" spans="1:15" ht="23.1" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -10411,7 +10387,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.15" customHeight="1">
+    <row r="23" spans="1:15" ht="23.1" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -10428,7 +10404,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.15" customHeight="1">
+    <row r="24" spans="1:15" ht="23.1" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -10445,7 +10421,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.15" customHeight="1">
+    <row r="25" spans="1:15" ht="23.1" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -10462,7 +10438,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.15" customHeight="1">
+    <row r="26" spans="1:15" ht="23.1" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -10479,7 +10455,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.15" customHeight="1">
+    <row r="27" spans="1:15" ht="23.1" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -10496,7 +10472,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.15" customHeight="1">
+    <row r="28" spans="1:15" ht="23.1" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -10513,7 +10489,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -10530,7 +10506,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.15" customHeight="1">
+    <row r="30" spans="1:15" ht="23.1" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -10547,7 +10523,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -10564,7 +10540,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -10581,7 +10557,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -10598,7 +10574,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -10615,7 +10591,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -10632,7 +10608,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -10649,7 +10625,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -10666,7 +10642,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -10683,7 +10659,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -10700,7 +10676,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -10717,24 +10693,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-      <c r="M41" s="94"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.15" customHeight="1">
+    <row r="42" spans="1:15" ht="23.1" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -10775,7 +10751,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -10802,45 +10778,45 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.1" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+      <c r="M3" s="74"/>
+      <c r="N3" s="74"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="28" customHeight="1">
+    <row r="4" spans="1:15" ht="27.95" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -10857,25 +10833,25 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="32" customHeight="1">
+    <row r="5" spans="1:15" ht="32.1" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="72" t="s">
+      <c r="J5" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -10924,7 +10900,7 @@
       </c>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="29" customHeight="1">
+    <row r="7" spans="1:15" ht="29.1" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="25" t="s">
         <v>7</v>
@@ -10975,7 +10951,7 @@
       </c>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="29" customHeight="1">
+    <row r="8" spans="1:15" ht="29.1" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="28" t="s">
         <v>9</v>
@@ -11043,7 +11019,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="29" customHeight="1">
+    <row r="10" spans="1:15" ht="29.1" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="25" t="s">
         <v>10</v>
@@ -11088,7 +11064,7 @@
       </c>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="29" customHeight="1">
+    <row r="11" spans="1:15" ht="29.1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="32" t="s">
         <v>44</v>
@@ -11133,7 +11109,7 @@
       </c>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="29" customHeight="1">
+    <row r="12" spans="1:15" ht="29.1" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="25" t="s">
         <v>13</v>
@@ -11178,7 +11154,7 @@
       </c>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="29" customHeight="1">
+    <row r="13" spans="1:15" ht="29.1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="32" t="s">
         <v>50</v>
@@ -11221,7 +11197,7 @@
       </c>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="29" customHeight="1">
+    <row r="14" spans="1:15" ht="29.1" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="27" t="s">
         <v>45</v>
@@ -11334,7 +11310,7 @@
       </c>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="29" customHeight="1">
+    <row r="17" spans="1:15" ht="29.1" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="25" t="s">
         <v>15</v>
@@ -11379,7 +11355,7 @@
       </c>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="29" customHeight="1">
+    <row r="18" spans="1:15" ht="29.1" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="28" t="s">
         <v>16</v>
@@ -11424,7 +11400,7 @@
       </c>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="29" customHeight="1">
+    <row r="19" spans="1:15" ht="29.1" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="25" t="s">
         <v>17</v>
@@ -11503,75 +11479,75 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="32" customHeight="1">
+    <row r="22" spans="1:15" ht="32.1" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="75"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="29" customHeight="1">
+    <row r="23" spans="1:15" ht="29.1" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="31">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="77" t="s">
+      <c r="F23" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="81"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="29" customHeight="1">
+    <row r="24" spans="1:15" ht="29.1" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="67"/>
+      <c r="C24" s="71"/>
       <c r="D24" s="33">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="81"/>
+      <c r="N24" s="81"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="29" customHeight="1">
+    <row r="25" spans="1:15" ht="29.1" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="75"/>
+      <c r="C25" s="78"/>
       <c r="D25" s="31">
         <v>40</v>
       </c>
@@ -11587,35 +11563,35 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="29" customHeight="1">
+    <row r="26" spans="1:15" ht="29.1" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="67"/>
+      <c r="C26" s="71"/>
       <c r="D26" s="33">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="79" t="s">
+      <c r="F26" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="74"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="29" customHeight="1">
+    <row r="27" spans="1:15" ht="29.1" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="67"/>
+      <c r="C27" s="71"/>
       <c r="D27" s="33">
         <v>10</v>
       </c>
@@ -11633,143 +11609,143 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="81" t="s">
+      <c r="B28" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="82"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="82"/>
-      <c r="N28" s="82"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.15" customHeight="1">
+    <row r="29" spans="1:15" ht="23.1" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="80"/>
-      <c r="M29" s="80"/>
-      <c r="N29" s="80"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="31" customHeight="1">
+    <row r="30" spans="1:15" ht="30.95" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="83"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="69"/>
+      <c r="N30" s="69"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.15" customHeight="1">
+    <row r="31" spans="1:15" ht="23.1" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="80"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="80"/>
-      <c r="M31" s="80"/>
-      <c r="N31" s="80"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.15" customHeight="1">
+    <row r="32" spans="1:15" ht="23.1" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80"/>
-      <c r="M32" s="80"/>
-      <c r="N32" s="80"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.15" customHeight="1">
+    <row r="33" spans="1:15" ht="23.1" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="80"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="80"/>
-      <c r="M33" s="80"/>
-      <c r="N33" s="80"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.15" customHeight="1">
+    <row r="34" spans="1:15" ht="23.1" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="80"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.15" customHeight="1">
+    <row r="35" spans="1:15" ht="23.1" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
-      <c r="I35" s="80"/>
-      <c r="J35" s="80"/>
-      <c r="K35" s="80"/>
-      <c r="L35" s="80"/>
-      <c r="M35" s="80"/>
-      <c r="N35" s="80"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.15" customHeight="1">
+    <row r="36" spans="1:15" ht="23.1" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -11786,7 +11762,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.15" customHeight="1">
+    <row r="37" spans="1:15" ht="23.1" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -11803,7 +11779,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.15" customHeight="1">
+    <row r="38" spans="1:15" ht="23.1" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -11820,7 +11796,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.15" customHeight="1">
+    <row r="39" spans="1:15" ht="23.1" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -11837,7 +11813,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.15" customHeight="1">
+    <row r="40" spans="1:15" ht="23.1" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -11854,7 +11830,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.15" customHeight="1">
+    <row r="41" spans="1:15" ht="23.1" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -11873,14 +11849,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -11893,6 +11861,14 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11905,40 +11881,40 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:V165"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="22" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="32" customHeight="1">
+    <row r="1" spans="1:22" ht="32.1" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-    </row>
-    <row r="2" spans="1:22" ht="22" customHeight="1">
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+    </row>
+    <row r="2" spans="1:22" ht="21.95" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="46"/>
       <c r="C2" s="46"/>
@@ -11962,7 +11938,7 @@
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:22" ht="22" customHeight="1">
+    <row r="3" spans="1:22" ht="21.95" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -11986,7 +11962,7 @@
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="44" customHeight="1">
+    <row r="4" spans="1:22" ht="44.1" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="47" t="s">
         <v>30</v>
@@ -12052,7 +12028,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="25" customHeight="1">
+    <row r="5" spans="1:22" ht="24.95" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="51" t="str">
         <f>"c "&amp;C5</f>
@@ -12139,7 +12115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="25" customHeight="1">
+    <row r="6" spans="1:22" ht="24.95" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="53" t="str">
         <f>"c "&amp;C6</f>
@@ -12226,7 +12202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="25" customHeight="1">
+    <row r="7" spans="1:22" ht="24.95" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="51" t="str">
         <f>"c "&amp;C7</f>
@@ -12313,7 +12289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="25" customHeight="1">
+    <row r="8" spans="1:22" ht="24.95" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="53" t="str">
         <f>"c "&amp;C8</f>
@@ -12400,7 +12376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="25" customHeight="1">
+    <row r="9" spans="1:22" ht="24.95" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="51" t="str">
         <f>"c "&amp;C9</f>
@@ -12487,7 +12463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="22" customHeight="1">
+    <row r="10" spans="1:22" ht="21.95" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12511,7 +12487,7 @@
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
     </row>
-    <row r="11" spans="1:22" ht="22" customHeight="1">
+    <row r="11" spans="1:22" ht="21.95" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -12535,7 +12511,7 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" spans="1:22" ht="22" customHeight="1">
+    <row r="12" spans="1:22" ht="21.95" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -12600,7 +12576,7 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
     </row>
-    <row r="14" spans="1:22" ht="25" customHeight="1">
+    <row r="14" spans="1:22" ht="24.95" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="57">
         <v>0</v>
@@ -12641,7 +12617,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
     </row>
-    <row r="15" spans="1:22" ht="25" customHeight="1">
+    <row r="15" spans="1:22" ht="24.95" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="58">
         <v>0.05</v>
@@ -12682,7 +12658,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
     </row>
-    <row r="16" spans="1:22" ht="25" customHeight="1">
+    <row r="16" spans="1:22" ht="24.95" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="57">
         <v>0.1</v>
@@ -12723,7 +12699,7 @@
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
     </row>
-    <row r="17" spans="1:22" ht="25" customHeight="1">
+    <row r="17" spans="1:22" ht="24.95" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="58">
         <v>0.15</v>
@@ -12764,7 +12740,7 @@
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
     </row>
-    <row r="18" spans="1:22" ht="25" customHeight="1">
+    <row r="18" spans="1:22" ht="24.95" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="57">
         <v>0.2</v>
@@ -12805,7 +12781,7 @@
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
     </row>
-    <row r="19" spans="1:22" ht="25" customHeight="1">
+    <row r="19" spans="1:22" ht="24.95" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="58">
         <v>0.25</v>
@@ -12846,7 +12822,7 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
     </row>
-    <row r="20" spans="1:22" ht="25" customHeight="1">
+    <row r="20" spans="1:22" ht="24.95" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="57">
         <v>0.3</v>
@@ -12887,7 +12863,7 @@
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
     </row>
-    <row r="21" spans="1:22" ht="25" customHeight="1">
+    <row r="21" spans="1:22" ht="24.95" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="58">
         <v>0.35</v>
@@ -12928,7 +12904,7 @@
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
     </row>
-    <row r="22" spans="1:22" ht="25" customHeight="1">
+    <row r="22" spans="1:22" ht="24.95" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="57">
         <v>0.4</v>
@@ -12969,7 +12945,7 @@
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
     </row>
-    <row r="23" spans="1:22" ht="25" customHeight="1">
+    <row r="23" spans="1:22" ht="24.95" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="58">
         <v>0.45</v>
@@ -13010,7 +12986,7 @@
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
     </row>
-    <row r="24" spans="1:22" ht="25" customHeight="1">
+    <row r="24" spans="1:22" ht="24.95" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="57">
         <v>0.5</v>
@@ -13051,7 +13027,7 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
     </row>
-    <row r="25" spans="1:22" ht="25" customHeight="1">
+    <row r="25" spans="1:22" ht="24.95" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="58">
         <v>0.55000000000000004</v>
@@ -13092,7 +13068,7 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
     </row>
-    <row r="26" spans="1:22" ht="25" customHeight="1">
+    <row r="26" spans="1:22" ht="24.95" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="57">
         <v>0.6</v>
@@ -13133,7 +13109,7 @@
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
     </row>
-    <row r="27" spans="1:22" ht="25" customHeight="1">
+    <row r="27" spans="1:22" ht="24.95" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="58">
         <v>0.65</v>
@@ -13174,7 +13150,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
     </row>
-    <row r="28" spans="1:22" ht="25" customHeight="1">
+    <row r="28" spans="1:22" ht="24.95" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="57">
         <v>0.7</v>
@@ -13215,7 +13191,7 @@
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
     </row>
-    <row r="29" spans="1:22" ht="25" customHeight="1">
+    <row r="29" spans="1:22" ht="24.95" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="58">
         <v>0.75</v>
@@ -13256,7 +13232,7 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" spans="1:22" ht="25" customHeight="1">
+    <row r="30" spans="1:22" ht="24.95" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="57">
         <v>0.8</v>
@@ -13297,7 +13273,7 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
     </row>
-    <row r="31" spans="1:22" ht="25" customHeight="1">
+    <row r="31" spans="1:22" ht="24.95" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="58">
         <v>0.85</v>
@@ -13338,7 +13314,7 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" spans="1:22" ht="25" customHeight="1">
+    <row r="32" spans="1:22" ht="24.95" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="57">
         <v>0.9</v>
@@ -13379,7 +13355,7 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="1:22" ht="25" customHeight="1">
+    <row r="33" spans="1:22" ht="24.95" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="58">
         <v>0.95</v>
@@ -13420,7 +13396,7 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" spans="1:22" ht="25" customHeight="1">
+    <row r="34" spans="1:22" ht="24.95" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="57">
         <v>1</v>
@@ -13461,7 +13437,7 @@
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
     </row>
-    <row r="35" spans="1:22" ht="22" customHeight="1">
+    <row r="35" spans="1:22" ht="21.95" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -13485,7 +13461,7 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" spans="1:22" ht="22" customHeight="1">
+    <row r="36" spans="1:22" ht="21.95" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -13509,7 +13485,7 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
     </row>
-    <row r="37" spans="1:22" ht="22" customHeight="1">
+    <row r="37" spans="1:22" ht="21.95" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -13533,7 +13509,7 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
     </row>
-    <row r="38" spans="1:22" ht="22" customHeight="1">
+    <row r="38" spans="1:22" ht="21.95" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -13557,7 +13533,7 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
     </row>
-    <row r="39" spans="1:22" ht="22" customHeight="1">
+    <row r="39" spans="1:22" ht="21.95" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -13581,7 +13557,7 @@
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
     </row>
-    <row r="40" spans="1:22" ht="22" customHeight="1">
+    <row r="40" spans="1:22" ht="21.95" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -13605,33 +13581,33 @@
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
     </row>
-    <row r="41" spans="1:22" ht="32" customHeight="1">
+    <row r="41" spans="1:22" ht="32.1" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="95" t="s">
+      <c r="B41" s="94" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="95"/>
-      <c r="D41" s="95"/>
-      <c r="E41" s="95"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="95"/>
-      <c r="H41" s="95"/>
-      <c r="I41" s="95"/>
-      <c r="J41" s="95"/>
-      <c r="K41" s="95"/>
-      <c r="L41" s="95"/>
-      <c r="M41" s="95"/>
-      <c r="N41" s="95"/>
-      <c r="O41" s="95"/>
-      <c r="P41" s="96"/>
-      <c r="Q41" s="96"/>
-      <c r="R41" s="96"/>
-      <c r="S41" s="96"/>
-      <c r="T41" s="96"/>
-      <c r="U41" s="96"/>
-      <c r="V41" s="96"/>
-    </row>
-    <row r="42" spans="1:22" ht="22" customHeight="1">
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94"/>
+      <c r="M41" s="94"/>
+      <c r="N41" s="94"/>
+      <c r="O41" s="94"/>
+      <c r="P41" s="95"/>
+      <c r="Q41" s="95"/>
+      <c r="R41" s="95"/>
+      <c r="S41" s="95"/>
+      <c r="T41" s="95"/>
+      <c r="U41" s="95"/>
+      <c r="V41" s="95"/>
+    </row>
+    <row r="42" spans="1:22" ht="21.95" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -13655,7 +13631,7 @@
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
     </row>
-    <row r="43" spans="1:22" ht="22" customHeight="1">
+    <row r="43" spans="1:22" ht="21.95" customHeight="1">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -13678,7 +13654,7 @@
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
     </row>
-    <row r="44" spans="1:22" ht="44" customHeight="1">
+    <row r="44" spans="1:22" ht="44.1" customHeight="1">
       <c r="B44" s="50" t="s">
         <v>30</v>
       </c>
@@ -13743,7 +13719,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="25" customHeight="1">
+    <row r="45" spans="1:22" ht="24.95" customHeight="1">
       <c r="B45" s="52" t="str">
         <f>"C "&amp;D45</f>
         <v>C -20</v>
@@ -13829,7 +13805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="25" customHeight="1">
+    <row r="46" spans="1:22" ht="24.95" customHeight="1">
       <c r="B46" s="54" t="str">
         <f>"C "&amp;D46</f>
         <v>C -15</v>
@@ -13915,7 +13891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="25" customHeight="1">
+    <row r="47" spans="1:22" ht="24.95" customHeight="1">
       <c r="B47" s="52" t="str">
         <f>"C "&amp;D47</f>
         <v>C -10</v>
@@ -14001,7 +13977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="25" customHeight="1">
+    <row r="48" spans="1:22" ht="24.95" customHeight="1">
       <c r="B48" s="54" t="str">
         <f>"C "&amp;D48</f>
         <v>C -5</v>
@@ -14087,7 +14063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" ht="25" customHeight="1">
+    <row r="49" spans="2:22" ht="24.95" customHeight="1">
       <c r="B49" s="52" t="str">
         <f>"C "&amp;D49</f>
         <v>C 0</v>
@@ -14173,7 +14149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:22" ht="22" customHeight="1">
+    <row r="50" spans="2:22" ht="21.95" customHeight="1">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -14196,7 +14172,7 @@
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
     </row>
-    <row r="51" spans="2:22" ht="22" customHeight="1">
+    <row r="51" spans="2:22" ht="21.95" customHeight="1">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -14219,7 +14195,7 @@
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
     </row>
-    <row r="52" spans="2:22" ht="22" customHeight="1">
+    <row r="52" spans="2:22" ht="21.95" customHeight="1">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -14282,7 +14258,7 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
     </row>
-    <row r="54" spans="2:22" ht="25" customHeight="1">
+    <row r="54" spans="2:22" ht="24.95" customHeight="1">
       <c r="B54" s="61">
         <v>0</v>
       </c>
@@ -14322,7 +14298,7 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
     </row>
-    <row r="55" spans="2:22" ht="25" customHeight="1">
+    <row r="55" spans="2:22" ht="24.95" customHeight="1">
       <c r="B55" s="62">
         <v>0.05</v>
       </c>
@@ -14362,7 +14338,7 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
     </row>
-    <row r="56" spans="2:22" ht="25" customHeight="1">
+    <row r="56" spans="2:22" ht="24.95" customHeight="1">
       <c r="B56" s="61">
         <v>0.1</v>
       </c>
@@ -14402,7 +14378,7 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
     </row>
-    <row r="57" spans="2:22" ht="25" customHeight="1">
+    <row r="57" spans="2:22" ht="24.95" customHeight="1">
       <c r="B57" s="62">
         <v>0.15</v>
       </c>
@@ -14442,7 +14418,7 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
     </row>
-    <row r="58" spans="2:22" ht="25" customHeight="1">
+    <row r="58" spans="2:22" ht="24.95" customHeight="1">
       <c r="B58" s="61">
         <v>0.2</v>
       </c>
@@ -14482,7 +14458,7 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
     </row>
-    <row r="59" spans="2:22" ht="25" customHeight="1">
+    <row r="59" spans="2:22" ht="24.95" customHeight="1">
       <c r="B59" s="62">
         <v>0.25</v>
       </c>
@@ -14522,7 +14498,7 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
     </row>
-    <row r="60" spans="2:22" ht="25" customHeight="1">
+    <row r="60" spans="2:22" ht="24.95" customHeight="1">
       <c r="B60" s="61">
         <v>0.3</v>
       </c>
@@ -14562,7 +14538,7 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
     </row>
-    <row r="61" spans="2:22" ht="25" customHeight="1">
+    <row r="61" spans="2:22" ht="24.95" customHeight="1">
       <c r="B61" s="62">
         <v>0.35</v>
       </c>
@@ -14602,7 +14578,7 @@
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
     </row>
-    <row r="62" spans="2:22" ht="25" customHeight="1">
+    <row r="62" spans="2:22" ht="24.95" customHeight="1">
       <c r="B62" s="61">
         <v>0.4</v>
       </c>
@@ -14642,7 +14618,7 @@
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
     </row>
-    <row r="63" spans="2:22" ht="25" customHeight="1">
+    <row r="63" spans="2:22" ht="24.95" customHeight="1">
       <c r="B63" s="62">
         <v>0.45</v>
       </c>
@@ -14682,7 +14658,7 @@
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
     </row>
-    <row r="64" spans="2:22" ht="25" customHeight="1">
+    <row r="64" spans="2:22" ht="24.95" customHeight="1">
       <c r="B64" s="61">
         <v>0.5</v>
       </c>
@@ -14722,7 +14698,7 @@
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
     </row>
-    <row r="65" spans="2:22" ht="25" customHeight="1">
+    <row r="65" spans="2:22" ht="24.95" customHeight="1">
       <c r="B65" s="62">
         <v>0.55000000000000004</v>
       </c>
@@ -14762,7 +14738,7 @@
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
     </row>
-    <row r="66" spans="2:22" ht="25" customHeight="1">
+    <row r="66" spans="2:22" ht="24.95" customHeight="1">
       <c r="B66" s="61">
         <v>0.6</v>
       </c>
@@ -14802,7 +14778,7 @@
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
     </row>
-    <row r="67" spans="2:22" ht="25" customHeight="1">
+    <row r="67" spans="2:22" ht="24.95" customHeight="1">
       <c r="B67" s="62">
         <v>0.65</v>
       </c>
@@ -14842,7 +14818,7 @@
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
     </row>
-    <row r="68" spans="2:22" ht="25" customHeight="1">
+    <row r="68" spans="2:22" ht="24.95" customHeight="1">
       <c r="B68" s="61">
         <v>0.7</v>
       </c>
@@ -14882,7 +14858,7 @@
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
     </row>
-    <row r="69" spans="2:22" ht="25" customHeight="1">
+    <row r="69" spans="2:22" ht="24.95" customHeight="1">
       <c r="B69" s="62">
         <v>0.75</v>
       </c>
@@ -14922,7 +14898,7 @@
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
     </row>
-    <row r="70" spans="2:22" ht="25" customHeight="1">
+    <row r="70" spans="2:22" ht="24.95" customHeight="1">
       <c r="B70" s="61">
         <v>0.8</v>
       </c>
@@ -14962,7 +14938,7 @@
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
     </row>
-    <row r="71" spans="2:22" ht="25" customHeight="1">
+    <row r="71" spans="2:22" ht="24.95" customHeight="1">
       <c r="B71" s="62">
         <v>0.85</v>
       </c>
@@ -15002,7 +14978,7 @@
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
     </row>
-    <row r="72" spans="2:22" ht="25" customHeight="1">
+    <row r="72" spans="2:22" ht="24.95" customHeight="1">
       <c r="B72" s="61">
         <v>0.9</v>
       </c>
@@ -15042,7 +15018,7 @@
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
     </row>
-    <row r="73" spans="2:22" ht="25" customHeight="1">
+    <row r="73" spans="2:22" ht="24.95" customHeight="1">
       <c r="B73" s="62">
         <v>0.95</v>
       </c>
@@ -15082,7 +15058,7 @@
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
     </row>
-    <row r="74" spans="2:22" ht="25" customHeight="1">
+    <row r="74" spans="2:22" ht="24.95" customHeight="1">
       <c r="B74" s="61">
         <v>1</v>
       </c>
@@ -15122,7 +15098,7 @@
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
     </row>
-    <row r="75" spans="2:22" ht="22" customHeight="1">
+    <row r="75" spans="2:22" ht="21.95" customHeight="1">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -15145,7 +15121,7 @@
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
     </row>
-    <row r="76" spans="2:22" ht="22" customHeight="1">
+    <row r="76" spans="2:22" ht="21.95" customHeight="1">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -15168,7 +15144,7 @@
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
     </row>
-    <row r="77" spans="2:22" ht="22" customHeight="1">
+    <row r="77" spans="2:22" ht="21.95" customHeight="1">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -15191,7 +15167,7 @@
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
     </row>
-    <row r="78" spans="2:22" ht="22" customHeight="1">
+    <row r="78" spans="2:22" ht="21.95" customHeight="1">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -15214,7 +15190,7 @@
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
     </row>
-    <row r="79" spans="2:22" ht="22" customHeight="1">
+    <row r="79" spans="2:22" ht="21.95" customHeight="1">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -15237,7 +15213,7 @@
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
     </row>
-    <row r="80" spans="2:22" ht="22" customHeight="1">
+    <row r="80" spans="2:22" ht="21.95" customHeight="1">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -15260,32 +15236,32 @@
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
     </row>
-    <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="96" t="s">
+    <row r="81" spans="2:22" ht="32.1" customHeight="1">
+      <c r="B81" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="C81" s="96"/>
-      <c r="D81" s="96"/>
-      <c r="E81" s="96"/>
-      <c r="F81" s="96"/>
-      <c r="G81" s="96"/>
-      <c r="H81" s="96"/>
-      <c r="I81" s="96"/>
-      <c r="J81" s="96"/>
-      <c r="K81" s="96"/>
-      <c r="L81" s="96"/>
-      <c r="M81" s="96"/>
-      <c r="N81" s="96"/>
-      <c r="O81" s="96"/>
-      <c r="P81" s="96"/>
-      <c r="Q81" s="96"/>
-      <c r="R81" s="96"/>
-      <c r="S81" s="96"/>
-      <c r="T81" s="96"/>
-      <c r="U81" s="96"/>
-      <c r="V81" s="96"/>
-    </row>
-    <row r="82" spans="2:22" ht="22" customHeight="1">
+      <c r="C81" s="95"/>
+      <c r="D81" s="95"/>
+      <c r="E81" s="95"/>
+      <c r="F81" s="95"/>
+      <c r="G81" s="95"/>
+      <c r="H81" s="95"/>
+      <c r="I81" s="95"/>
+      <c r="J81" s="95"/>
+      <c r="K81" s="95"/>
+      <c r="L81" s="95"/>
+      <c r="M81" s="95"/>
+      <c r="N81" s="95"/>
+      <c r="O81" s="95"/>
+      <c r="P81" s="95"/>
+      <c r="Q81" s="95"/>
+      <c r="R81" s="95"/>
+      <c r="S81" s="95"/>
+      <c r="T81" s="95"/>
+      <c r="U81" s="95"/>
+      <c r="V81" s="95"/>
+    </row>
+    <row r="82" spans="2:22" ht="21.95" customHeight="1">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -15308,7 +15284,7 @@
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
     </row>
-    <row r="83" spans="2:22" ht="22" customHeight="1">
+    <row r="83" spans="2:22" ht="21.95" customHeight="1">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -15331,7 +15307,7 @@
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
     </row>
-    <row r="84" spans="2:22" ht="44" customHeight="1">
+    <row r="84" spans="2:22" ht="44.1" customHeight="1">
       <c r="B84" s="50" t="s">
         <v>30</v>
       </c>
@@ -15396,7 +15372,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="2:22" ht="25" customHeight="1">
+    <row r="85" spans="2:22" ht="24.95" customHeight="1">
       <c r="B85" s="52" t="str">
         <f>"R "&amp;E85</f>
         <v>R -40</v>
@@ -15482,7 +15458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:22" ht="25" customHeight="1">
+    <row r="86" spans="2:22" ht="24.95" customHeight="1">
       <c r="B86" s="54" t="str">
         <f>"R "&amp;E86</f>
         <v>R -30</v>
@@ -15568,7 +15544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:22" ht="25" customHeight="1">
+    <row r="87" spans="2:22" ht="24.95" customHeight="1">
       <c r="B87" s="52" t="str">
         <f>"R "&amp;E87</f>
         <v>R -20</v>
@@ -15654,7 +15630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:22" ht="25" customHeight="1">
+    <row r="88" spans="2:22" ht="24.95" customHeight="1">
       <c r="B88" s="54" t="str">
         <f>"R "&amp;E88</f>
         <v>R -10</v>
@@ -15740,7 +15716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:22" ht="25" customHeight="1">
+    <row r="89" spans="2:22" ht="24.95" customHeight="1">
       <c r="B89" s="52" t="str">
         <f>"R "&amp;E89</f>
         <v>R 0</v>
@@ -15826,7 +15802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:22" ht="22" customHeight="1">
+    <row r="90" spans="2:22" ht="21.95" customHeight="1">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -15849,7 +15825,7 @@
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
     </row>
-    <row r="91" spans="2:22" ht="22" customHeight="1">
+    <row r="91" spans="2:22" ht="21.95" customHeight="1">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -15872,7 +15848,7 @@
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
     </row>
-    <row r="92" spans="2:22" ht="22" customHeight="1">
+    <row r="92" spans="2:22" ht="21.95" customHeight="1">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -15935,7 +15911,7 @@
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
     </row>
-    <row r="94" spans="2:22" ht="25" customHeight="1">
+    <row r="94" spans="2:22" ht="24.95" customHeight="1">
       <c r="B94" s="61">
         <v>0</v>
       </c>
@@ -15975,7 +15951,7 @@
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
     </row>
-    <row r="95" spans="2:22" ht="25" customHeight="1">
+    <row r="95" spans="2:22" ht="24.95" customHeight="1">
       <c r="B95" s="62">
         <v>0.05</v>
       </c>
@@ -16015,7 +15991,7 @@
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
     </row>
-    <row r="96" spans="2:22" ht="25" customHeight="1">
+    <row r="96" spans="2:22" ht="24.95" customHeight="1">
       <c r="B96" s="61">
         <v>0.1</v>
       </c>
@@ -16055,7 +16031,7 @@
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
     </row>
-    <row r="97" spans="2:22" ht="25" customHeight="1">
+    <row r="97" spans="2:22" ht="24.95" customHeight="1">
       <c r="B97" s="62">
         <v>0.15</v>
       </c>
@@ -16095,7 +16071,7 @@
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
     </row>
-    <row r="98" spans="2:22" ht="25" customHeight="1">
+    <row r="98" spans="2:22" ht="24.95" customHeight="1">
       <c r="B98" s="61">
         <v>0.2</v>
       </c>
@@ -16135,7 +16111,7 @@
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
     </row>
-    <row r="99" spans="2:22" ht="25" customHeight="1">
+    <row r="99" spans="2:22" ht="24.95" customHeight="1">
       <c r="B99" s="62">
         <v>0.25</v>
       </c>
@@ -16175,7 +16151,7 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
     </row>
-    <row r="100" spans="2:22" ht="25" customHeight="1">
+    <row r="100" spans="2:22" ht="24.95" customHeight="1">
       <c r="B100" s="61">
         <v>0.3</v>
       </c>
@@ -16215,7 +16191,7 @@
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
     </row>
-    <row r="101" spans="2:22" ht="25" customHeight="1">
+    <row r="101" spans="2:22" ht="24.95" customHeight="1">
       <c r="B101" s="62">
         <v>0.35</v>
       </c>
@@ -16255,7 +16231,7 @@
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
     </row>
-    <row r="102" spans="2:22" ht="25" customHeight="1">
+    <row r="102" spans="2:22" ht="24.95" customHeight="1">
       <c r="B102" s="61">
         <v>0.4</v>
       </c>
@@ -16295,7 +16271,7 @@
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
     </row>
-    <row r="103" spans="2:22" ht="25" customHeight="1">
+    <row r="103" spans="2:22" ht="24.95" customHeight="1">
       <c r="B103" s="62">
         <v>0.45</v>
       </c>
@@ -16335,7 +16311,7 @@
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
     </row>
-    <row r="104" spans="2:22" ht="25" customHeight="1">
+    <row r="104" spans="2:22" ht="24.95" customHeight="1">
       <c r="B104" s="61">
         <v>0.5</v>
       </c>
@@ -16375,7 +16351,7 @@
       <c r="U104" s="4"/>
       <c r="V104" s="4"/>
     </row>
-    <row r="105" spans="2:22" ht="25" customHeight="1">
+    <row r="105" spans="2:22" ht="24.95" customHeight="1">
       <c r="B105" s="62">
         <v>0.55000000000000004</v>
       </c>
@@ -16415,7 +16391,7 @@
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
     </row>
-    <row r="106" spans="2:22" ht="25" customHeight="1">
+    <row r="106" spans="2:22" ht="24.95" customHeight="1">
       <c r="B106" s="61">
         <v>0.6</v>
       </c>
@@ -16455,7 +16431,7 @@
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
     </row>
-    <row r="107" spans="2:22" ht="25" customHeight="1">
+    <row r="107" spans="2:22" ht="24.95" customHeight="1">
       <c r="B107" s="62">
         <v>0.65</v>
       </c>
@@ -16495,7 +16471,7 @@
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
     </row>
-    <row r="108" spans="2:22" ht="25" customHeight="1">
+    <row r="108" spans="2:22" ht="24.95" customHeight="1">
       <c r="B108" s="61">
         <v>0.7</v>
       </c>
@@ -16535,7 +16511,7 @@
       <c r="U108" s="4"/>
       <c r="V108" s="4"/>
     </row>
-    <row r="109" spans="2:22" ht="25" customHeight="1">
+    <row r="109" spans="2:22" ht="24.95" customHeight="1">
       <c r="B109" s="62">
         <v>0.75</v>
       </c>
@@ -16575,7 +16551,7 @@
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
     </row>
-    <row r="110" spans="2:22" ht="25" customHeight="1">
+    <row r="110" spans="2:22" ht="24.95" customHeight="1">
       <c r="B110" s="61">
         <v>0.8</v>
       </c>
@@ -16615,7 +16591,7 @@
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
     </row>
-    <row r="111" spans="2:22" ht="25" customHeight="1">
+    <row r="111" spans="2:22" ht="24.95" customHeight="1">
       <c r="B111" s="62">
         <v>0.85</v>
       </c>
@@ -16655,7 +16631,7 @@
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
     </row>
-    <row r="112" spans="2:22" ht="25" customHeight="1">
+    <row r="112" spans="2:22" ht="24.95" customHeight="1">
       <c r="B112" s="61">
         <v>0.9</v>
       </c>
@@ -16695,7 +16671,7 @@
       <c r="U112" s="4"/>
       <c r="V112" s="4"/>
     </row>
-    <row r="113" spans="2:22" ht="25" customHeight="1">
+    <row r="113" spans="2:22" ht="24.95" customHeight="1">
       <c r="B113" s="62">
         <v>0.95</v>
       </c>
@@ -16735,7 +16711,7 @@
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
     </row>
-    <row r="114" spans="2:22" ht="25" customHeight="1">
+    <row r="114" spans="2:22" ht="24.95" customHeight="1">
       <c r="B114" s="61">
         <v>1</v>
       </c>
@@ -16775,7 +16751,7 @@
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
     </row>
-    <row r="115" spans="2:22" ht="22" customHeight="1">
+    <row r="115" spans="2:22" ht="21.95" customHeight="1">
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -16798,7 +16774,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
     </row>
-    <row r="116" spans="2:22" ht="22" customHeight="1">
+    <row r="116" spans="2:22" ht="21.95" customHeight="1">
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -16821,7 +16797,7 @@
       <c r="U116" s="4"/>
       <c r="V116" s="4"/>
     </row>
-    <row r="117" spans="2:22" ht="22" customHeight="1">
+    <row r="117" spans="2:22" ht="21.95" customHeight="1">
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
@@ -16844,7 +16820,7 @@
       <c r="U117" s="4"/>
       <c r="V117" s="4"/>
     </row>
-    <row r="118" spans="2:22" ht="22" customHeight="1">
+    <row r="118" spans="2:22" ht="21.95" customHeight="1">
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
@@ -16867,7 +16843,7 @@
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
     </row>
-    <row r="119" spans="2:22" ht="22" customHeight="1">
+    <row r="119" spans="2:22" ht="21.95" customHeight="1">
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -16890,7 +16866,7 @@
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
     </row>
-    <row r="120" spans="2:22" ht="22" customHeight="1">
+    <row r="120" spans="2:22" ht="21.95" customHeight="1">
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -16913,32 +16889,32 @@
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
     </row>
-    <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="96" t="s">
+    <row r="121" spans="2:22" ht="32.1" customHeight="1">
+      <c r="B121" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="C121" s="96"/>
-      <c r="D121" s="96"/>
-      <c r="E121" s="96"/>
-      <c r="F121" s="96"/>
-      <c r="G121" s="96"/>
-      <c r="H121" s="96"/>
-      <c r="I121" s="96"/>
-      <c r="J121" s="96"/>
-      <c r="K121" s="96"/>
-      <c r="L121" s="96"/>
-      <c r="M121" s="96"/>
-      <c r="N121" s="96"/>
-      <c r="O121" s="96"/>
-      <c r="P121" s="96"/>
-      <c r="Q121" s="96"/>
-      <c r="R121" s="96"/>
-      <c r="S121" s="96"/>
-      <c r="T121" s="96"/>
-      <c r="U121" s="96"/>
-      <c r="V121" s="96"/>
-    </row>
-    <row r="122" spans="2:22" ht="22" customHeight="1">
+      <c r="C121" s="95"/>
+      <c r="D121" s="95"/>
+      <c r="E121" s="95"/>
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="95"/>
+      <c r="I121" s="95"/>
+      <c r="J121" s="95"/>
+      <c r="K121" s="95"/>
+      <c r="L121" s="95"/>
+      <c r="M121" s="95"/>
+      <c r="N121" s="95"/>
+      <c r="O121" s="95"/>
+      <c r="P121" s="95"/>
+      <c r="Q121" s="95"/>
+      <c r="R121" s="95"/>
+      <c r="S121" s="95"/>
+      <c r="T121" s="95"/>
+      <c r="U121" s="95"/>
+      <c r="V121" s="95"/>
+    </row>
+    <row r="122" spans="2:22" ht="21.95" customHeight="1">
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -16961,7 +16937,7 @@
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
     </row>
-    <row r="123" spans="2:22" ht="22" customHeight="1">
+    <row r="123" spans="2:22" ht="21.95" customHeight="1">
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -16984,7 +16960,7 @@
       <c r="U123" s="4"/>
       <c r="V123" s="4"/>
     </row>
-    <row r="124" spans="2:22" ht="44" customHeight="1">
+    <row r="124" spans="2:22" ht="44.1" customHeight="1">
       <c r="B124" s="50" t="s">
         <v>30</v>
       </c>
@@ -17049,7 +17025,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="125" spans="2:22" ht="25" customHeight="1">
+    <row r="125" spans="2:22" ht="24.95" customHeight="1">
       <c r="B125" s="52" t="str">
         <f>"c "&amp;C125&amp;" / C "&amp;D125</f>
         <v>c -24 / C -20</v>
@@ -17135,7 +17111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:22" ht="25" customHeight="1">
+    <row r="126" spans="2:22" ht="24.95" customHeight="1">
       <c r="B126" s="54" t="str">
         <f>"c "&amp;C126&amp;" / C "&amp;D126</f>
         <v>c -18 / C -15</v>
@@ -17221,7 +17197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:22" ht="25" customHeight="1">
+    <row r="127" spans="2:22" ht="24.95" customHeight="1">
       <c r="B127" s="52" t="str">
         <f>"c "&amp;C127&amp;" / C "&amp;D127</f>
         <v>c -12 / C -10</v>
@@ -17307,7 +17283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:22" ht="25" customHeight="1">
+    <row r="128" spans="2:22" ht="24.95" customHeight="1">
       <c r="B128" s="54" t="str">
         <f>"c "&amp;C128&amp;" / C "&amp;D128</f>
         <v>c -6 / C -5</v>
@@ -17393,7 +17369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:22" ht="25" customHeight="1">
+    <row r="129" spans="2:22" ht="24.95" customHeight="1">
       <c r="B129" s="52" t="str">
         <f>"c "&amp;C129&amp;" / C "&amp;D129</f>
         <v>c 0 / C 0</v>
@@ -17479,7 +17455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="2:22" ht="22" customHeight="1">
+    <row r="130" spans="2:22" ht="21.95" customHeight="1">
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -17502,7 +17478,7 @@
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
     </row>
-    <row r="131" spans="2:22" ht="22" customHeight="1">
+    <row r="131" spans="2:22" ht="21.95" customHeight="1">
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
@@ -17525,7 +17501,7 @@
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
     </row>
-    <row r="132" spans="2:22" ht="22" customHeight="1">
+    <row r="132" spans="2:22" ht="21.95" customHeight="1">
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -17603,7 +17579,7 @@
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
     </row>
-    <row r="134" spans="2:22" ht="25" customHeight="1">
+    <row r="134" spans="2:22" ht="24.95" customHeight="1">
       <c r="B134" s="61">
         <v>0</v>
       </c>
@@ -17658,7 +17634,7 @@
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
     </row>
-    <row r="135" spans="2:22" ht="25" customHeight="1">
+    <row r="135" spans="2:22" ht="24.95" customHeight="1">
       <c r="B135" s="62">
         <v>0.05</v>
       </c>
@@ -17713,7 +17689,7 @@
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
     </row>
-    <row r="136" spans="2:22" ht="25" customHeight="1">
+    <row r="136" spans="2:22" ht="24.95" customHeight="1">
       <c r="B136" s="61">
         <v>0.1</v>
       </c>
@@ -17768,7 +17744,7 @@
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
     </row>
-    <row r="137" spans="2:22" ht="25" customHeight="1">
+    <row r="137" spans="2:22" ht="24.95" customHeight="1">
       <c r="B137" s="62">
         <v>0.15</v>
       </c>
@@ -17823,7 +17799,7 @@
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
     </row>
-    <row r="138" spans="2:22" ht="25" customHeight="1">
+    <row r="138" spans="2:22" ht="24.95" customHeight="1">
       <c r="B138" s="61">
         <v>0.2</v>
       </c>
@@ -17878,7 +17854,7 @@
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
     </row>
-    <row r="139" spans="2:22" ht="25" customHeight="1">
+    <row r="139" spans="2:22" ht="24.95" customHeight="1">
       <c r="B139" s="62">
         <v>0.25</v>
       </c>
@@ -17933,7 +17909,7 @@
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
     </row>
-    <row r="140" spans="2:22" ht="25" customHeight="1">
+    <row r="140" spans="2:22" ht="24.95" customHeight="1">
       <c r="B140" s="61">
         <v>0.3</v>
       </c>
@@ -17988,7 +17964,7 @@
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
     </row>
-    <row r="141" spans="2:22" ht="25" customHeight="1">
+    <row r="141" spans="2:22" ht="24.95" customHeight="1">
       <c r="B141" s="62">
         <v>0.35</v>
       </c>
@@ -18043,7 +18019,7 @@
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
     </row>
-    <row r="142" spans="2:22" ht="25" customHeight="1">
+    <row r="142" spans="2:22" ht="24.95" customHeight="1">
       <c r="B142" s="61">
         <v>0.4</v>
       </c>
@@ -18098,7 +18074,7 @@
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
     </row>
-    <row r="143" spans="2:22" ht="25" customHeight="1">
+    <row r="143" spans="2:22" ht="24.95" customHeight="1">
       <c r="B143" s="62">
         <v>0.45</v>
       </c>
@@ -18153,7 +18129,7 @@
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
     </row>
-    <row r="144" spans="2:22" ht="25" customHeight="1">
+    <row r="144" spans="2:22" ht="24.95" customHeight="1">
       <c r="B144" s="61">
         <v>0.5</v>
       </c>
@@ -18208,7 +18184,7 @@
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
     </row>
-    <row r="145" spans="2:22" ht="25" customHeight="1">
+    <row r="145" spans="2:22" ht="24.95" customHeight="1">
       <c r="B145" s="62">
         <v>0.55000000000000004</v>
       </c>
@@ -18263,7 +18239,7 @@
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
     </row>
-    <row r="146" spans="2:22" ht="25" customHeight="1">
+    <row r="146" spans="2:22" ht="24.95" customHeight="1">
       <c r="B146" s="61">
         <v>0.6</v>
       </c>
@@ -18318,7 +18294,7 @@
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
     </row>
-    <row r="147" spans="2:22" ht="25" customHeight="1">
+    <row r="147" spans="2:22" ht="24.95" customHeight="1">
       <c r="B147" s="62">
         <v>0.65</v>
       </c>
@@ -18373,7 +18349,7 @@
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
     </row>
-    <row r="148" spans="2:22" ht="25" customHeight="1">
+    <row r="148" spans="2:22" ht="24.95" customHeight="1">
       <c r="B148" s="61">
         <v>0.7</v>
       </c>
@@ -18428,7 +18404,7 @@
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
     </row>
-    <row r="149" spans="2:22" ht="25" customHeight="1">
+    <row r="149" spans="2:22" ht="24.95" customHeight="1">
       <c r="B149" s="62">
         <v>0.75</v>
       </c>
@@ -18483,7 +18459,7 @@
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
     </row>
-    <row r="150" spans="2:22" ht="25" customHeight="1">
+    <row r="150" spans="2:22" ht="24.95" customHeight="1">
       <c r="B150" s="61">
         <v>0.8</v>
       </c>
@@ -18538,7 +18514,7 @@
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
     </row>
-    <row r="151" spans="2:22" ht="25" customHeight="1">
+    <row r="151" spans="2:22" ht="24.95" customHeight="1">
       <c r="B151" s="62">
         <v>0.85</v>
       </c>
@@ -18593,7 +18569,7 @@
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
     </row>
-    <row r="152" spans="2:22" ht="25" customHeight="1">
+    <row r="152" spans="2:22" ht="24.95" customHeight="1">
       <c r="B152" s="61">
         <v>0.9</v>
       </c>
@@ -18648,7 +18624,7 @@
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
     </row>
-    <row r="153" spans="2:22" ht="25" customHeight="1">
+    <row r="153" spans="2:22" ht="24.95" customHeight="1">
       <c r="B153" s="62">
         <v>0.95</v>
       </c>
@@ -18703,7 +18679,7 @@
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
     </row>
-    <row r="154" spans="2:22" ht="25" customHeight="1">
+    <row r="154" spans="2:22" ht="24.95" customHeight="1">
       <c r="B154" s="61">
         <v>1</v>
       </c>
@@ -18758,7 +18734,7 @@
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
     </row>
-    <row r="155" spans="2:22" ht="22" customHeight="1">
+    <row r="155" spans="2:22" ht="21.95" customHeight="1">
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -18781,7 +18757,7 @@
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
     </row>
-    <row r="156" spans="2:22" ht="22" customHeight="1">
+    <row r="156" spans="2:22" ht="21.95" customHeight="1">
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -18804,7 +18780,7 @@
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
     </row>
-    <row r="157" spans="2:22" ht="22" customHeight="1">
+    <row r="157" spans="2:22" ht="21.95" customHeight="1">
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -18827,32 +18803,32 @@
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
     </row>
-    <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="97" t="s">
+    <row r="161" spans="2:22" ht="32.1" customHeight="1">
+      <c r="B161" s="96" t="s">
         <v>97</v>
       </c>
-      <c r="C161" s="97"/>
-      <c r="D161" s="97"/>
-      <c r="E161" s="97"/>
-      <c r="F161" s="97"/>
-      <c r="G161" s="97"/>
-      <c r="H161" s="97"/>
-      <c r="I161" s="97"/>
-      <c r="J161" s="97"/>
-      <c r="K161" s="97"/>
-      <c r="L161" s="97"/>
-      <c r="M161" s="97"/>
-      <c r="N161" s="97"/>
-      <c r="O161" s="97"/>
-      <c r="P161" s="97"/>
-      <c r="Q161" s="97"/>
-      <c r="R161" s="97"/>
-      <c r="S161" s="97"/>
-      <c r="T161" s="97"/>
-      <c r="U161" s="97"/>
-      <c r="V161" s="97"/>
-    </row>
-    <row r="164" spans="2:22" ht="44" customHeight="1">
+      <c r="C161" s="96"/>
+      <c r="D161" s="96"/>
+      <c r="E161" s="96"/>
+      <c r="F161" s="96"/>
+      <c r="G161" s="96"/>
+      <c r="H161" s="96"/>
+      <c r="I161" s="96"/>
+      <c r="J161" s="96"/>
+      <c r="K161" s="96"/>
+      <c r="L161" s="96"/>
+      <c r="M161" s="96"/>
+      <c r="N161" s="96"/>
+      <c r="O161" s="96"/>
+      <c r="P161" s="96"/>
+      <c r="Q161" s="96"/>
+      <c r="R161" s="96"/>
+      <c r="S161" s="96"/>
+      <c r="T161" s="96"/>
+      <c r="U161" s="96"/>
+      <c r="V161" s="96"/>
+    </row>
+    <row r="164" spans="2:22" ht="44.1" customHeight="1">
       <c r="B164" s="63" t="s">
         <v>30</v>
       </c>
@@ -18917,7 +18893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="2:22" ht="25" customHeight="1">
+    <row r="165" spans="2:22" ht="24.95" customHeight="1">
       <c r="B165" s="66"/>
       <c r="C165" s="65">
         <f>Calculator!C7</f>

--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE25B4BC-4EB4-44EC-B003-32040F202683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D60C570-573C-4FDC-87D8-154D1E472998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -1863,11 +1863,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1882,10 +1882,10 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1900,10 +1900,10 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1918,10 +1918,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2065,43 +2065,64 @@
     <xf numFmtId="0" fontId="81" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="27" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2113,38 +2134,14 @@
     <xf numFmtId="0" fontId="55" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2157,7 +2154,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2175,7 +2172,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3025,7 +3022,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3865,7 +3862,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -4698,7 +4695,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -6518,7 +6515,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -6537,19 +6534,19 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="35.1" customHeight="1">
+    <row r="2" spans="1:8" ht="35.15" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:8" ht="24.95" customHeight="1">
+    <row r="3" spans="1:8" ht="25" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -6559,7 +6556,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" ht="32.1" customHeight="1">
+    <row r="4" spans="1:8" ht="32.15" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="6"/>
@@ -6577,7 +6574,7 @@
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:8" ht="30.95" customHeight="1">
+    <row r="5" spans="1:8" ht="31" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="6"/>
@@ -6595,9 +6592,9 @@
       </c>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="1:8" ht="30.95" customHeight="1">
+    <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="73" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="6"/>
@@ -6615,9 +6612,9 @@
       </c>
       <c r="H6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="30.95" customHeight="1">
+    <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="86"/>
+      <c r="B7" s="73"/>
       <c r="C7" s="6"/>
       <c r="D7" s="19" t="s">
         <v>77</v>
@@ -6633,7 +6630,7 @@
       </c>
       <c r="H7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="30.95" customHeight="1">
+    <row r="8" spans="1:8" ht="31" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="23" t="s">
         <v>65</v>
@@ -6653,7 +6650,7 @@
       </c>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="30.95" customHeight="1">
+    <row r="9" spans="1:8" ht="31" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="17" t="s">
         <v>76</v>
@@ -6673,7 +6670,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="30.95" customHeight="1">
+    <row r="10" spans="1:8" ht="31" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="8"/>
       <c r="C10" s="6"/>
@@ -6689,7 +6686,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="30.95" customHeight="1">
+    <row r="11" spans="1:8" ht="31" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="8"/>
       <c r="C11" s="6"/>
@@ -6703,7 +6700,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="30.95" customHeight="1">
+    <row r="12" spans="1:8" ht="31" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="8"/>
       <c r="C12" s="6"/>
@@ -6721,7 +6718,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="30.95" customHeight="1">
+    <row r="13" spans="1:8" ht="31" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="8"/>
       <c r="C13" s="6"/>
@@ -6735,7 +6732,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="24.95" customHeight="1">
+    <row r="14" spans="1:8" ht="25" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -6745,47 +6742,47 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="21.95" customHeight="1">
+    <row r="15" spans="1:8" ht="22" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="21.95" customHeight="1">
+    <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="21.95" customHeight="1">
+    <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="21.95" customHeight="1">
+    <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="24.95" customHeight="1">
+    <row r="19" spans="1:8" ht="25" customHeight="1">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -6795,7 +6792,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="24.95" customHeight="1">
+    <row r="20" spans="1:8" ht="25" customHeight="1">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -6805,7 +6802,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="24.95" customHeight="1">
+    <row r="21" spans="1:8" ht="25" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -6836,7 +6833,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -6862,22 +6859,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -6898,7 +6895,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -6907,19 +6904,19 @@
         <v>98</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -6936,7 +6933,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="32.1" customHeight="1">
+    <row r="6" spans="1:15" ht="32.15" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="27" t="s">
         <v>59</v>
@@ -6946,7 +6943,7 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="76" t="s">
+      <c r="F6" s="74" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="75"/>
@@ -6959,7 +6956,7 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="27.95" customHeight="1">
+    <row r="7" spans="1:15" ht="28" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="28" t="s">
         <v>7</v>
@@ -6980,7 +6977,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="27.95" customHeight="1">
+    <row r="8" spans="1:15" ht="28" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="25" t="s">
         <v>9</v>
@@ -6990,23 +6987,23 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="91">
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="77">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>1736.47</v>
       </c>
-      <c r="J8" s="92"/>
+      <c r="J8" s="78"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="27.95" customHeight="1">
+    <row r="9" spans="1:15" ht="28" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="28" t="s">
         <v>20</v>
@@ -7027,7 +7024,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="27.95" customHeight="1">
+    <row r="10" spans="1:15" ht="28" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="27" t="s">
         <v>21</v>
@@ -7037,23 +7034,23 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="91">
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="77">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1519.2</v>
       </c>
-      <c r="J10" s="92"/>
+      <c r="J10" s="78"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -7070,7 +7067,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -7087,7 +7084,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="32.1" customHeight="1">
+    <row r="13" spans="1:15" ht="32.15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="27" t="s">
         <v>23</v>
@@ -7098,7 +7095,7 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="76" t="s">
+      <c r="F13" s="74" t="s">
         <v>47</v>
       </c>
       <c r="G13" s="75"/>
@@ -7111,7 +7108,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="27.95" customHeight="1">
+    <row r="14" spans="1:15" ht="28" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="32" t="s">
         <v>24</v>
@@ -7122,11 +7119,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="89" t="s">
+      <c r="F14" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
       <c r="I14" s="34">
         <f>Samples!F165</f>
         <v>3650</v>
@@ -7140,7 +7137,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="27.95" customHeight="1">
+    <row r="15" spans="1:15" ht="28" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="27" t="s">
         <v>25</v>
@@ -7151,11 +7148,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="79" t="s">
+      <c r="F15" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
       <c r="I15" s="35">
         <f>Samples!I165</f>
         <v>3431</v>
@@ -7169,17 +7166,17 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="27.95" customHeight="1">
+    <row r="16" spans="1:15" ht="28" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
       <c r="I16" s="34">
         <f>Samples!J165</f>
         <v>1750</v>
@@ -7193,17 +7190,17 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="27.95" customHeight="1">
+    <row r="17" spans="1:15" ht="28" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="70" t="s">
+      <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
       <c r="I17" s="35">
         <f>Samples!L165</f>
         <v>5181</v>
@@ -7217,7 +7214,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="27.95" customHeight="1">
+    <row r="18" spans="1:15" ht="28" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="27" t="s">
         <v>28</v>
@@ -7239,17 +7236,17 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="27.95" customHeight="1">
+    <row r="19" spans="1:15" ht="28" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="89" t="s">
+      <c r="F19" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
       <c r="I19" s="34">
         <f>Samples!M165</f>
         <v>3600</v>
@@ -7263,17 +7260,17 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="27.95" customHeight="1">
+    <row r="20" spans="1:15" ht="28" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="79" t="s">
+      <c r="F20" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
       <c r="I20" s="35">
         <f>Samples!P165</f>
         <v>3096</v>
@@ -7287,7 +7284,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="27.95" customHeight="1">
+    <row r="21" spans="1:15" ht="28" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -7304,17 +7301,17 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="27.95" customHeight="1">
+    <row r="22" spans="1:15" ht="28" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="77" t="s">
+      <c r="F22" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
       <c r="I22" s="37">
         <f>Samples!G165</f>
         <v>0.08</v>
@@ -7328,17 +7325,17 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="27.95" customHeight="1">
+    <row r="23" spans="1:15" ht="28" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="70" t="s">
+      <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
       <c r="I23" s="38">
         <f>Samples!K165</f>
         <v>0.35</v>
@@ -7352,17 +7349,17 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="27.95" customHeight="1">
+    <row r="24" spans="1:15" ht="28" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="89" t="s">
+      <c r="F24" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
       <c r="I24" s="37">
         <f>Samples!N165</f>
         <v>0.25</v>
@@ -7376,7 +7373,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -7393,7 +7390,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -7410,26 +7407,26 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="83" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="88"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -7446,7 +7443,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -7463,7 +7460,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -7480,7 +7477,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -7497,7 +7494,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -7514,7 +7511,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -7531,7 +7528,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -7548,7 +7545,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -7565,7 +7562,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -7582,7 +7579,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -7599,7 +7596,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -7616,7 +7613,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -7633,7 +7630,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -7650,7 +7647,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -7667,7 +7664,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -7686,6 +7683,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -7693,17 +7701,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -7735,7 +7732,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -7758,22 +7755,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -7794,7 +7791,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -7803,19 +7800,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -7832,7 +7829,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="27" t="s">
         <v>2</v>
@@ -7841,19 +7838,19 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -7870,7 +7867,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -7887,7 +7884,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -7904,7 +7901,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -7921,7 +7918,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -7938,7 +7935,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -7955,7 +7952,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -7972,7 +7969,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -7989,7 +7986,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -8006,7 +8003,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -8023,7 +8020,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8040,7 +8037,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -8057,7 +8054,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -8074,7 +8071,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -8091,7 +8088,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -8108,7 +8105,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -8125,7 +8122,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -8142,7 +8139,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -8159,7 +8156,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -8176,7 +8173,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -8193,7 +8190,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -8210,7 +8207,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -8227,7 +8224,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -8244,7 +8241,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -8261,7 +8258,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -8278,7 +8275,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -8295,7 +8292,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -8312,7 +8309,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -8329,7 +8326,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -8346,7 +8343,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -8363,7 +8360,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -8380,7 +8377,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -8397,7 +8394,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -8414,7 +8411,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -8431,24 +8428,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -8493,7 +8490,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -8516,22 +8513,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -8552,7 +8549,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -8561,19 +8558,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -8590,7 +8587,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="27" t="s">
         <v>3</v>
@@ -8599,19 +8596,19 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -8628,7 +8625,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -8645,7 +8642,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -8662,7 +8659,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -8679,7 +8676,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -8696,7 +8693,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -8713,7 +8710,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -8730,7 +8727,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -8747,7 +8744,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -8764,7 +8761,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -8781,7 +8778,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8798,7 +8795,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -8815,7 +8812,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -8832,7 +8829,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -8849,7 +8846,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -8866,7 +8863,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -8883,7 +8880,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -8900,7 +8897,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -8917,7 +8914,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -8934,7 +8931,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -8951,7 +8948,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -8968,7 +8965,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -8985,7 +8982,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -9002,7 +8999,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -9019,7 +9016,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -9036,7 +9033,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -9053,7 +9050,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -9070,7 +9067,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -9087,7 +9084,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -9104,7 +9101,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -9121,7 +9118,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -9138,7 +9135,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -9155,7 +9152,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -9172,7 +9169,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -9189,24 +9186,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -9251,7 +9248,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -9274,22 +9271,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -9310,7 +9307,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -9319,19 +9316,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -9348,24 +9345,24 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -9382,7 +9379,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -9399,7 +9396,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -9416,7 +9413,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -9433,7 +9430,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -9450,7 +9447,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -9467,7 +9464,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -9484,7 +9481,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -9501,7 +9498,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -9518,7 +9515,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -9535,7 +9532,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -9552,7 +9549,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -9569,7 +9566,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -9586,7 +9583,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -9603,7 +9600,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -9620,7 +9617,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -9637,7 +9634,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -9654,7 +9651,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -9671,7 +9668,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -9688,7 +9685,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -9705,7 +9702,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -9722,7 +9719,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -9739,7 +9736,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -9756,7 +9753,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -9773,7 +9770,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -9790,7 +9787,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -9807,7 +9804,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -9824,7 +9821,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -9841,7 +9838,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -9858,7 +9855,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -9875,7 +9872,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -9892,7 +9889,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -9909,7 +9906,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -9926,7 +9923,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -9943,24 +9940,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -10001,7 +9998,7 @@
     <tabColor rgb="FF31475E"/>
   </sheetPr>
   <dimension ref="A1:O42"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="15" width="10.5" customWidth="1"/>
@@ -10024,22 +10021,22 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -10060,7 +10057,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10069,19 +10066,19 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="14.1" customHeight="1">
+    <row r="5" spans="1:15" ht="14.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -10098,24 +10095,24 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="27.95" customHeight="1">
+    <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="23.1" customHeight="1">
+    <row r="7" spans="1:15" ht="23.15" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -10132,7 +10129,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="23.1" customHeight="1">
+    <row r="8" spans="1:15" ht="23.15" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -10149,7 +10146,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="23.1" customHeight="1">
+    <row r="9" spans="1:15" ht="23.15" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -10166,7 +10163,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="23.1" customHeight="1">
+    <row r="10" spans="1:15" ht="23.15" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -10183,7 +10180,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="23.1" customHeight="1">
+    <row r="11" spans="1:15" ht="23.15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -10200,7 +10197,7 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="23.1" customHeight="1">
+    <row r="12" spans="1:15" ht="23.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -10217,7 +10214,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="23.1" customHeight="1">
+    <row r="13" spans="1:15" ht="23.15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -10234,7 +10231,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="23.1" customHeight="1">
+    <row r="14" spans="1:15" ht="23.15" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -10251,7 +10248,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="23.1" customHeight="1">
+    <row r="15" spans="1:15" ht="23.15" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -10268,7 +10265,7 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="23.1" customHeight="1">
+    <row r="16" spans="1:15" ht="23.15" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -10285,7 +10282,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="23.1" customHeight="1">
+    <row r="17" spans="1:15" ht="23.15" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -10302,7 +10299,7 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="23.1" customHeight="1">
+    <row r="18" spans="1:15" ht="23.15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -10319,7 +10316,7 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="23.1" customHeight="1">
+    <row r="19" spans="1:15" ht="23.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -10336,7 +10333,7 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="23.1" customHeight="1">
+    <row r="20" spans="1:15" ht="23.15" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -10353,7 +10350,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="23.1" customHeight="1">
+    <row r="21" spans="1:15" ht="23.15" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -10370,7 +10367,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="23.1" customHeight="1">
+    <row r="22" spans="1:15" ht="23.15" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -10387,7 +10384,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="23.1" customHeight="1">
+    <row r="23" spans="1:15" ht="23.15" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -10404,7 +10401,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="23.1" customHeight="1">
+    <row r="24" spans="1:15" ht="23.15" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -10421,7 +10418,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="23.1" customHeight="1">
+    <row r="25" spans="1:15" ht="23.15" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -10438,7 +10435,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="23.1" customHeight="1">
+    <row r="26" spans="1:15" ht="23.15" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -10455,7 +10452,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="23.1" customHeight="1">
+    <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -10472,7 +10469,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="23.1" customHeight="1">
+    <row r="28" spans="1:15" ht="23.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -10489,7 +10486,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -10506,7 +10503,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="23.1" customHeight="1">
+    <row r="30" spans="1:15" ht="23.15" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -10523,7 +10520,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -10540,7 +10537,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -10557,7 +10554,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -10574,7 +10571,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -10591,7 +10588,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -10608,7 +10605,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -10625,7 +10622,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -10642,7 +10639,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -10659,7 +10656,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -10676,7 +10673,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -10693,24 +10690,24 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="93"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" ht="23.1" customHeight="1">
+    <row r="42" spans="1:15" ht="23.15" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -10751,7 +10748,7 @@
     <tabColor rgb="FFC49A32"/>
   </sheetPr>
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -10778,45 +10775,45 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35.1" customHeight="1">
+    <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="86"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="86"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="86"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="27.95" customHeight="1">
+    <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -10833,7 +10830,7 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="32.1" customHeight="1">
+    <row r="5" spans="1:15" ht="32.15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -10900,7 +10897,7 @@
       </c>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="29.1" customHeight="1">
+    <row r="7" spans="1:15" ht="29.15" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="25" t="s">
         <v>7</v>
@@ -10951,7 +10948,7 @@
       </c>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="29.1" customHeight="1">
+    <row r="8" spans="1:15" ht="29.15" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="28" t="s">
         <v>9</v>
@@ -11019,7 +11016,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="29.1" customHeight="1">
+    <row r="10" spans="1:15" ht="29.15" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="25" t="s">
         <v>10</v>
@@ -11064,7 +11061,7 @@
       </c>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="1:15" ht="29.1" customHeight="1">
+    <row r="11" spans="1:15" ht="29.15" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="32" t="s">
         <v>44</v>
@@ -11109,7 +11106,7 @@
       </c>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="29.1" customHeight="1">
+    <row r="12" spans="1:15" ht="29.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="25" t="s">
         <v>13</v>
@@ -11154,7 +11151,7 @@
       </c>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="29.1" customHeight="1">
+    <row r="13" spans="1:15" ht="29.15" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="32" t="s">
         <v>50</v>
@@ -11197,7 +11194,7 @@
       </c>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="1:15" ht="29.1" customHeight="1">
+    <row r="14" spans="1:15" ht="29.15" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="27" t="s">
         <v>45</v>
@@ -11310,7 +11307,7 @@
       </c>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="29.1" customHeight="1">
+    <row r="17" spans="1:15" ht="29.15" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="25" t="s">
         <v>15</v>
@@ -11355,7 +11352,7 @@
       </c>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="29.1" customHeight="1">
+    <row r="18" spans="1:15" ht="29.15" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="28" t="s">
         <v>16</v>
@@ -11400,7 +11397,7 @@
       </c>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="29.1" customHeight="1">
+    <row r="19" spans="1:15" ht="29.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="25" t="s">
         <v>17</v>
@@ -11479,9 +11476,9 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="32.1" customHeight="1">
+    <row r="22" spans="1:15" ht="32.15" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="74" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="75"/>
@@ -11498,56 +11495,56 @@
       <c r="N22" s="75"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="29.1" customHeight="1">
+    <row r="23" spans="1:15" ht="29.15" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="77" t="s">
+      <c r="B23" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="78"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="31">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="80" t="s">
+      <c r="F23" s="87" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="81"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="88"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="29.1" customHeight="1">
+    <row r="24" spans="1:15" ht="29.15" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="81"/>
       <c r="D24" s="33">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="81"/>
-      <c r="N24" s="81"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="88"/>
+      <c r="L24" s="88"/>
+      <c r="M24" s="88"/>
+      <c r="N24" s="88"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="29.1" customHeight="1">
+    <row r="25" spans="1:15" ht="29.15" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="77" t="s">
+      <c r="B25" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="78"/>
+      <c r="C25" s="80"/>
       <c r="D25" s="31">
         <v>40</v>
       </c>
@@ -11563,35 +11560,35 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="29.1" customHeight="1">
+    <row r="26" spans="1:15" ht="29.15" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="81"/>
       <c r="D26" s="33">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="82" t="s">
+      <c r="F26" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="86"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="29.1" customHeight="1">
+    <row r="27" spans="1:15" ht="29.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="71"/>
+      <c r="C27" s="81"/>
       <c r="D27" s="33">
         <v>10</v>
       </c>
@@ -11609,24 +11606,24 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="67" t="s">
+      <c r="B28" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="68"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="68"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="68"/>
-      <c r="N28" s="68"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="91"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="23.1" customHeight="1">
+    <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -11643,24 +11640,24 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="30.95" customHeight="1">
+    <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="69"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="92"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="23.1" customHeight="1">
+    <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -11677,7 +11674,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="23.1" customHeight="1">
+    <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -11694,7 +11691,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="23.1" customHeight="1">
+    <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -11711,7 +11708,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="23.1" customHeight="1">
+    <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -11728,7 +11725,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="23.1" customHeight="1">
+    <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -11745,7 +11742,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" ht="23.1" customHeight="1">
+    <row r="36" spans="1:15" ht="23.15" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -11762,7 +11759,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" ht="23.1" customHeight="1">
+    <row r="37" spans="1:15" ht="23.15" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -11779,7 +11776,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" ht="23.1" customHeight="1">
+    <row r="38" spans="1:15" ht="23.15" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -11796,7 +11793,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" ht="23.1" customHeight="1">
+    <row r="39" spans="1:15" ht="23.15" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -11813,7 +11810,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" ht="23.1" customHeight="1">
+    <row r="40" spans="1:15" ht="23.15" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -11830,7 +11827,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" ht="23.1" customHeight="1">
+    <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -11849,6 +11846,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -11861,14 +11866,6 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11881,40 +11878,40 @@
     <tabColor rgb="FF93A0AC"/>
   </sheetPr>
   <dimension ref="A1:V165"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="22" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="32.1" customHeight="1">
+    <row r="1" spans="1:22" ht="32.15" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-    </row>
-    <row r="2" spans="1:22" ht="21.95" customHeight="1">
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+    </row>
+    <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="46"/>
       <c r="C2" s="46"/>
@@ -11938,7 +11935,7 @@
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:22" ht="21.95" customHeight="1">
+    <row r="3" spans="1:22" ht="22" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -11962,7 +11959,7 @@
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="44.1" customHeight="1">
+    <row r="4" spans="1:22" ht="44.15" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="47" t="s">
         <v>30</v>
@@ -12028,7 +12025,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="24.95" customHeight="1">
+    <row r="5" spans="1:22" ht="25" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="51" t="str">
         <f>"c "&amp;C5</f>
@@ -12115,7 +12112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="24.95" customHeight="1">
+    <row r="6" spans="1:22" ht="25" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="53" t="str">
         <f>"c "&amp;C6</f>
@@ -12202,7 +12199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="24.95" customHeight="1">
+    <row r="7" spans="1:22" ht="25" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="51" t="str">
         <f>"c "&amp;C7</f>
@@ -12289,7 +12286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="24.95" customHeight="1">
+    <row r="8" spans="1:22" ht="25" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="53" t="str">
         <f>"c "&amp;C8</f>
@@ -12376,7 +12373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="24.95" customHeight="1">
+    <row r="9" spans="1:22" ht="25" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="51" t="str">
         <f>"c "&amp;C9</f>
@@ -12463,7 +12460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="21.95" customHeight="1">
+    <row r="10" spans="1:22" ht="22" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12487,7 +12484,7 @@
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
     </row>
-    <row r="11" spans="1:22" ht="21.95" customHeight="1">
+    <row r="11" spans="1:22" ht="22" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -12511,7 +12508,7 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" spans="1:22" ht="21.95" customHeight="1">
+    <row r="12" spans="1:22" ht="22" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -12576,7 +12573,7 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
     </row>
-    <row r="14" spans="1:22" ht="24.95" customHeight="1">
+    <row r="14" spans="1:22" ht="25" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="57">
         <v>0</v>
@@ -12617,7 +12614,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
     </row>
-    <row r="15" spans="1:22" ht="24.95" customHeight="1">
+    <row r="15" spans="1:22" ht="25" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="58">
         <v>0.05</v>
@@ -12658,7 +12655,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
     </row>
-    <row r="16" spans="1:22" ht="24.95" customHeight="1">
+    <row r="16" spans="1:22" ht="25" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="57">
         <v>0.1</v>
@@ -12699,7 +12696,7 @@
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
     </row>
-    <row r="17" spans="1:22" ht="24.95" customHeight="1">
+    <row r="17" spans="1:22" ht="25" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="58">
         <v>0.15</v>
@@ -12740,7 +12737,7 @@
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
     </row>
-    <row r="18" spans="1:22" ht="24.95" customHeight="1">
+    <row r="18" spans="1:22" ht="25" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="57">
         <v>0.2</v>
@@ -12781,7 +12778,7 @@
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
     </row>
-    <row r="19" spans="1:22" ht="24.95" customHeight="1">
+    <row r="19" spans="1:22" ht="25" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="58">
         <v>0.25</v>
@@ -12822,7 +12819,7 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
     </row>
-    <row r="20" spans="1:22" ht="24.95" customHeight="1">
+    <row r="20" spans="1:22" ht="25" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="57">
         <v>0.3</v>
@@ -12863,7 +12860,7 @@
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
     </row>
-    <row r="21" spans="1:22" ht="24.95" customHeight="1">
+    <row r="21" spans="1:22" ht="25" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="58">
         <v>0.35</v>
@@ -12904,7 +12901,7 @@
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
     </row>
-    <row r="22" spans="1:22" ht="24.95" customHeight="1">
+    <row r="22" spans="1:22" ht="25" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="57">
         <v>0.4</v>
@@ -12945,7 +12942,7 @@
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
     </row>
-    <row r="23" spans="1:22" ht="24.95" customHeight="1">
+    <row r="23" spans="1:22" ht="25" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="58">
         <v>0.45</v>
@@ -12986,7 +12983,7 @@
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
     </row>
-    <row r="24" spans="1:22" ht="24.95" customHeight="1">
+    <row r="24" spans="1:22" ht="25" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="57">
         <v>0.5</v>
@@ -13027,7 +13024,7 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
     </row>
-    <row r="25" spans="1:22" ht="24.95" customHeight="1">
+    <row r="25" spans="1:22" ht="25" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="58">
         <v>0.55000000000000004</v>
@@ -13068,7 +13065,7 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
     </row>
-    <row r="26" spans="1:22" ht="24.95" customHeight="1">
+    <row r="26" spans="1:22" ht="25" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="57">
         <v>0.6</v>
@@ -13109,7 +13106,7 @@
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
     </row>
-    <row r="27" spans="1:22" ht="24.95" customHeight="1">
+    <row r="27" spans="1:22" ht="25" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="58">
         <v>0.65</v>
@@ -13150,7 +13147,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
     </row>
-    <row r="28" spans="1:22" ht="24.95" customHeight="1">
+    <row r="28" spans="1:22" ht="25" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="57">
         <v>0.7</v>
@@ -13191,7 +13188,7 @@
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
     </row>
-    <row r="29" spans="1:22" ht="24.95" customHeight="1">
+    <row r="29" spans="1:22" ht="25" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="58">
         <v>0.75</v>
@@ -13232,7 +13229,7 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" spans="1:22" ht="24.95" customHeight="1">
+    <row r="30" spans="1:22" ht="25" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="57">
         <v>0.8</v>
@@ -13273,7 +13270,7 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
     </row>
-    <row r="31" spans="1:22" ht="24.95" customHeight="1">
+    <row r="31" spans="1:22" ht="25" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="58">
         <v>0.85</v>
@@ -13314,7 +13311,7 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" spans="1:22" ht="24.95" customHeight="1">
+    <row r="32" spans="1:22" ht="25" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="57">
         <v>0.9</v>
@@ -13355,7 +13352,7 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="1:22" ht="24.95" customHeight="1">
+    <row r="33" spans="1:22" ht="25" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="58">
         <v>0.95</v>
@@ -13396,7 +13393,7 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" spans="1:22" ht="24.95" customHeight="1">
+    <row r="34" spans="1:22" ht="25" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="57">
         <v>1</v>
@@ -13437,7 +13434,7 @@
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
     </row>
-    <row r="35" spans="1:22" ht="21.95" customHeight="1">
+    <row r="35" spans="1:22" ht="22" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -13461,7 +13458,7 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" spans="1:22" ht="21.95" customHeight="1">
+    <row r="36" spans="1:22" ht="22" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -13485,7 +13482,7 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
     </row>
-    <row r="37" spans="1:22" ht="21.95" customHeight="1">
+    <row r="37" spans="1:22" ht="22" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -13509,7 +13506,7 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
     </row>
-    <row r="38" spans="1:22" ht="21.95" customHeight="1">
+    <row r="38" spans="1:22" ht="22" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -13533,7 +13530,7 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
     </row>
-    <row r="39" spans="1:22" ht="21.95" customHeight="1">
+    <row r="39" spans="1:22" ht="22" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -13557,7 +13554,7 @@
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
     </row>
-    <row r="40" spans="1:22" ht="21.95" customHeight="1">
+    <row r="40" spans="1:22" ht="22" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -13581,33 +13578,33 @@
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
     </row>
-    <row r="41" spans="1:22" ht="32.1" customHeight="1">
+    <row r="41" spans="1:22" ht="32.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="94" t="s">
+      <c r="B41" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="94"/>
-      <c r="J41" s="94"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="94"/>
-      <c r="M41" s="94"/>
-      <c r="N41" s="94"/>
-      <c r="O41" s="94"/>
-      <c r="P41" s="95"/>
-      <c r="Q41" s="95"/>
-      <c r="R41" s="95"/>
-      <c r="S41" s="95"/>
-      <c r="T41" s="95"/>
-      <c r="U41" s="95"/>
-      <c r="V41" s="95"/>
-    </row>
-    <row r="42" spans="1:22" ht="21.95" customHeight="1">
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
+      <c r="N41" s="93"/>
+      <c r="O41" s="93"/>
+      <c r="P41" s="94"/>
+      <c r="Q41" s="94"/>
+      <c r="R41" s="94"/>
+      <c r="S41" s="94"/>
+      <c r="T41" s="94"/>
+      <c r="U41" s="94"/>
+      <c r="V41" s="94"/>
+    </row>
+    <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -13631,7 +13628,7 @@
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
     </row>
-    <row r="43" spans="1:22" ht="21.95" customHeight="1">
+    <row r="43" spans="1:22" ht="22" customHeight="1">
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -13654,7 +13651,7 @@
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
     </row>
-    <row r="44" spans="1:22" ht="44.1" customHeight="1">
+    <row r="44" spans="1:22" ht="44.15" customHeight="1">
       <c r="B44" s="50" t="s">
         <v>30</v>
       </c>
@@ -13719,7 +13716,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="24.95" customHeight="1">
+    <row r="45" spans="1:22" ht="25" customHeight="1">
       <c r="B45" s="52" t="str">
         <f>"C "&amp;D45</f>
         <v>C -20</v>
@@ -13805,7 +13802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="24.95" customHeight="1">
+    <row r="46" spans="1:22" ht="25" customHeight="1">
       <c r="B46" s="54" t="str">
         <f>"C "&amp;D46</f>
         <v>C -15</v>
@@ -13891,7 +13888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="24.95" customHeight="1">
+    <row r="47" spans="1:22" ht="25" customHeight="1">
       <c r="B47" s="52" t="str">
         <f>"C "&amp;D47</f>
         <v>C -10</v>
@@ -13977,7 +13974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="24.95" customHeight="1">
+    <row r="48" spans="1:22" ht="25" customHeight="1">
       <c r="B48" s="54" t="str">
         <f>"C "&amp;D48</f>
         <v>C -5</v>
@@ -14063,7 +14060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:22" ht="24.95" customHeight="1">
+    <row r="49" spans="2:22" ht="25" customHeight="1">
       <c r="B49" s="52" t="str">
         <f>"C "&amp;D49</f>
         <v>C 0</v>
@@ -14149,7 +14146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:22" ht="21.95" customHeight="1">
+    <row r="50" spans="2:22" ht="22" customHeight="1">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -14172,7 +14169,7 @@
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
     </row>
-    <row r="51" spans="2:22" ht="21.95" customHeight="1">
+    <row r="51" spans="2:22" ht="22" customHeight="1">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -14195,7 +14192,7 @@
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
     </row>
-    <row r="52" spans="2:22" ht="21.95" customHeight="1">
+    <row r="52" spans="2:22" ht="22" customHeight="1">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -14258,7 +14255,7 @@
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
     </row>
-    <row r="54" spans="2:22" ht="24.95" customHeight="1">
+    <row r="54" spans="2:22" ht="25" customHeight="1">
       <c r="B54" s="61">
         <v>0</v>
       </c>
@@ -14298,7 +14295,7 @@
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
     </row>
-    <row r="55" spans="2:22" ht="24.95" customHeight="1">
+    <row r="55" spans="2:22" ht="25" customHeight="1">
       <c r="B55" s="62">
         <v>0.05</v>
       </c>
@@ -14338,7 +14335,7 @@
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
     </row>
-    <row r="56" spans="2:22" ht="24.95" customHeight="1">
+    <row r="56" spans="2:22" ht="25" customHeight="1">
       <c r="B56" s="61">
         <v>0.1</v>
       </c>
@@ -14378,7 +14375,7 @@
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
     </row>
-    <row r="57" spans="2:22" ht="24.95" customHeight="1">
+    <row r="57" spans="2:22" ht="25" customHeight="1">
       <c r="B57" s="62">
         <v>0.15</v>
       </c>
@@ -14418,7 +14415,7 @@
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
     </row>
-    <row r="58" spans="2:22" ht="24.95" customHeight="1">
+    <row r="58" spans="2:22" ht="25" customHeight="1">
       <c r="B58" s="61">
         <v>0.2</v>
       </c>
@@ -14458,7 +14455,7 @@
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
     </row>
-    <row r="59" spans="2:22" ht="24.95" customHeight="1">
+    <row r="59" spans="2:22" ht="25" customHeight="1">
       <c r="B59" s="62">
         <v>0.25</v>
       </c>
@@ -14498,7 +14495,7 @@
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
     </row>
-    <row r="60" spans="2:22" ht="24.95" customHeight="1">
+    <row r="60" spans="2:22" ht="25" customHeight="1">
       <c r="B60" s="61">
         <v>0.3</v>
       </c>
@@ -14538,7 +14535,7 @@
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
     </row>
-    <row r="61" spans="2:22" ht="24.95" customHeight="1">
+    <row r="61" spans="2:22" ht="25" customHeight="1">
       <c r="B61" s="62">
         <v>0.35</v>
       </c>
@@ -14578,7 +14575,7 @@
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
     </row>
-    <row r="62" spans="2:22" ht="24.95" customHeight="1">
+    <row r="62" spans="2:22" ht="25" customHeight="1">
       <c r="B62" s="61">
         <v>0.4</v>
       </c>
@@ -14618,7 +14615,7 @@
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
     </row>
-    <row r="63" spans="2:22" ht="24.95" customHeight="1">
+    <row r="63" spans="2:22" ht="25" customHeight="1">
       <c r="B63" s="62">
         <v>0.45</v>
       </c>
@@ -14658,7 +14655,7 @@
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
     </row>
-    <row r="64" spans="2:22" ht="24.95" customHeight="1">
+    <row r="64" spans="2:22" ht="25" customHeight="1">
       <c r="B64" s="61">
         <v>0.5</v>
       </c>
@@ -14698,7 +14695,7 @@
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
     </row>
-    <row r="65" spans="2:22" ht="24.95" customHeight="1">
+    <row r="65" spans="2:22" ht="25" customHeight="1">
       <c r="B65" s="62">
         <v>0.55000000000000004</v>
       </c>
@@ -14738,7 +14735,7 @@
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
     </row>
-    <row r="66" spans="2:22" ht="24.95" customHeight="1">
+    <row r="66" spans="2:22" ht="25" customHeight="1">
       <c r="B66" s="61">
         <v>0.6</v>
       </c>
@@ -14778,7 +14775,7 @@
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
     </row>
-    <row r="67" spans="2:22" ht="24.95" customHeight="1">
+    <row r="67" spans="2:22" ht="25" customHeight="1">
       <c r="B67" s="62">
         <v>0.65</v>
       </c>
@@ -14818,7 +14815,7 @@
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
     </row>
-    <row r="68" spans="2:22" ht="24.95" customHeight="1">
+    <row r="68" spans="2:22" ht="25" customHeight="1">
       <c r="B68" s="61">
         <v>0.7</v>
       </c>
@@ -14858,7 +14855,7 @@
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
     </row>
-    <row r="69" spans="2:22" ht="24.95" customHeight="1">
+    <row r="69" spans="2:22" ht="25" customHeight="1">
       <c r="B69" s="62">
         <v>0.75</v>
       </c>
@@ -14898,7 +14895,7 @@
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
     </row>
-    <row r="70" spans="2:22" ht="24.95" customHeight="1">
+    <row r="70" spans="2:22" ht="25" customHeight="1">
       <c r="B70" s="61">
         <v>0.8</v>
       </c>
@@ -14938,7 +14935,7 @@
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
     </row>
-    <row r="71" spans="2:22" ht="24.95" customHeight="1">
+    <row r="71" spans="2:22" ht="25" customHeight="1">
       <c r="B71" s="62">
         <v>0.85</v>
       </c>
@@ -14978,7 +14975,7 @@
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
     </row>
-    <row r="72" spans="2:22" ht="24.95" customHeight="1">
+    <row r="72" spans="2:22" ht="25" customHeight="1">
       <c r="B72" s="61">
         <v>0.9</v>
       </c>
@@ -15018,7 +15015,7 @@
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
     </row>
-    <row r="73" spans="2:22" ht="24.95" customHeight="1">
+    <row r="73" spans="2:22" ht="25" customHeight="1">
       <c r="B73" s="62">
         <v>0.95</v>
       </c>
@@ -15058,7 +15055,7 @@
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
     </row>
-    <row r="74" spans="2:22" ht="24.95" customHeight="1">
+    <row r="74" spans="2:22" ht="25" customHeight="1">
       <c r="B74" s="61">
         <v>1</v>
       </c>
@@ -15098,7 +15095,7 @@
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
     </row>
-    <row r="75" spans="2:22" ht="21.95" customHeight="1">
+    <row r="75" spans="2:22" ht="22" customHeight="1">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -15121,7 +15118,7 @@
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
     </row>
-    <row r="76" spans="2:22" ht="21.95" customHeight="1">
+    <row r="76" spans="2:22" ht="22" customHeight="1">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -15144,7 +15141,7 @@
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
     </row>
-    <row r="77" spans="2:22" ht="21.95" customHeight="1">
+    <row r="77" spans="2:22" ht="22" customHeight="1">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -15167,7 +15164,7 @@
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
     </row>
-    <row r="78" spans="2:22" ht="21.95" customHeight="1">
+    <row r="78" spans="2:22" ht="22" customHeight="1">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -15190,7 +15187,7 @@
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
     </row>
-    <row r="79" spans="2:22" ht="21.95" customHeight="1">
+    <row r="79" spans="2:22" ht="22" customHeight="1">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -15213,7 +15210,7 @@
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
     </row>
-    <row r="80" spans="2:22" ht="21.95" customHeight="1">
+    <row r="80" spans="2:22" ht="22" customHeight="1">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -15236,32 +15233,32 @@
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
     </row>
-    <row r="81" spans="2:22" ht="32.1" customHeight="1">
-      <c r="B81" s="95" t="s">
+    <row r="81" spans="2:22" ht="32.15" customHeight="1">
+      <c r="B81" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="C81" s="95"/>
-      <c r="D81" s="95"/>
-      <c r="E81" s="95"/>
-      <c r="F81" s="95"/>
-      <c r="G81" s="95"/>
-      <c r="H81" s="95"/>
-      <c r="I81" s="95"/>
-      <c r="J81" s="95"/>
-      <c r="K81" s="95"/>
-      <c r="L81" s="95"/>
-      <c r="M81" s="95"/>
-      <c r="N81" s="95"/>
-      <c r="O81" s="95"/>
-      <c r="P81" s="95"/>
-      <c r="Q81" s="95"/>
-      <c r="R81" s="95"/>
-      <c r="S81" s="95"/>
-      <c r="T81" s="95"/>
-      <c r="U81" s="95"/>
-      <c r="V81" s="95"/>
-    </row>
-    <row r="82" spans="2:22" ht="21.95" customHeight="1">
+      <c r="C81" s="94"/>
+      <c r="D81" s="94"/>
+      <c r="E81" s="94"/>
+      <c r="F81" s="94"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="94"/>
+      <c r="I81" s="94"/>
+      <c r="J81" s="94"/>
+      <c r="K81" s="94"/>
+      <c r="L81" s="94"/>
+      <c r="M81" s="94"/>
+      <c r="N81" s="94"/>
+      <c r="O81" s="94"/>
+      <c r="P81" s="94"/>
+      <c r="Q81" s="94"/>
+      <c r="R81" s="94"/>
+      <c r="S81" s="94"/>
+      <c r="T81" s="94"/>
+      <c r="U81" s="94"/>
+      <c r="V81" s="94"/>
+    </row>
+    <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -15284,7 +15281,7 @@
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
     </row>
-    <row r="83" spans="2:22" ht="21.95" customHeight="1">
+    <row r="83" spans="2:22" ht="22" customHeight="1">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -15307,7 +15304,7 @@
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
     </row>
-    <row r="84" spans="2:22" ht="44.1" customHeight="1">
+    <row r="84" spans="2:22" ht="44.15" customHeight="1">
       <c r="B84" s="50" t="s">
         <v>30</v>
       </c>
@@ -15372,7 +15369,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" spans="2:22" ht="24.95" customHeight="1">
+    <row r="85" spans="2:22" ht="25" customHeight="1">
       <c r="B85" s="52" t="str">
         <f>"R "&amp;E85</f>
         <v>R -40</v>
@@ -15458,7 +15455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:22" ht="24.95" customHeight="1">
+    <row r="86" spans="2:22" ht="25" customHeight="1">
       <c r="B86" s="54" t="str">
         <f>"R "&amp;E86</f>
         <v>R -30</v>
@@ -15544,7 +15541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:22" ht="24.95" customHeight="1">
+    <row r="87" spans="2:22" ht="25" customHeight="1">
       <c r="B87" s="52" t="str">
         <f>"R "&amp;E87</f>
         <v>R -20</v>
@@ -15630,7 +15627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:22" ht="24.95" customHeight="1">
+    <row r="88" spans="2:22" ht="25" customHeight="1">
       <c r="B88" s="54" t="str">
         <f>"R "&amp;E88</f>
         <v>R -10</v>
@@ -15716,7 +15713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:22" ht="24.95" customHeight="1">
+    <row r="89" spans="2:22" ht="25" customHeight="1">
       <c r="B89" s="52" t="str">
         <f>"R "&amp;E89</f>
         <v>R 0</v>
@@ -15802,7 +15799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:22" ht="21.95" customHeight="1">
+    <row r="90" spans="2:22" ht="22" customHeight="1">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -15825,7 +15822,7 @@
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
     </row>
-    <row r="91" spans="2:22" ht="21.95" customHeight="1">
+    <row r="91" spans="2:22" ht="22" customHeight="1">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -15848,7 +15845,7 @@
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
     </row>
-    <row r="92" spans="2:22" ht="21.95" customHeight="1">
+    <row r="92" spans="2:22" ht="22" customHeight="1">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -15911,7 +15908,7 @@
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
     </row>
-    <row r="94" spans="2:22" ht="24.95" customHeight="1">
+    <row r="94" spans="2:22" ht="25" customHeight="1">
       <c r="B94" s="61">
         <v>0</v>
       </c>
@@ -15951,7 +15948,7 @@
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
     </row>
-    <row r="95" spans="2:22" ht="24.95" customHeight="1">
+    <row r="95" spans="2:22" ht="25" customHeight="1">
       <c r="B95" s="62">
         <v>0.05</v>
       </c>
@@ -15991,7 +15988,7 @@
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
     </row>
-    <row r="96" spans="2:22" ht="24.95" customHeight="1">
+    <row r="96" spans="2:22" ht="25" customHeight="1">
       <c r="B96" s="61">
         <v>0.1</v>
       </c>
@@ -16031,7 +16028,7 @@
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
     </row>
-    <row r="97" spans="2:22" ht="24.95" customHeight="1">
+    <row r="97" spans="2:22" ht="25" customHeight="1">
       <c r="B97" s="62">
         <v>0.15</v>
       </c>
@@ -16071,7 +16068,7 @@
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
     </row>
-    <row r="98" spans="2:22" ht="24.95" customHeight="1">
+    <row r="98" spans="2:22" ht="25" customHeight="1">
       <c r="B98" s="61">
         <v>0.2</v>
       </c>
@@ -16111,7 +16108,7 @@
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
     </row>
-    <row r="99" spans="2:22" ht="24.95" customHeight="1">
+    <row r="99" spans="2:22" ht="25" customHeight="1">
       <c r="B99" s="62">
         <v>0.25</v>
       </c>
@@ -16151,7 +16148,7 @@
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
     </row>
-    <row r="100" spans="2:22" ht="24.95" customHeight="1">
+    <row r="100" spans="2:22" ht="25" customHeight="1">
       <c r="B100" s="61">
         <v>0.3</v>
       </c>
@@ -16191,7 +16188,7 @@
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
     </row>
-    <row r="101" spans="2:22" ht="24.95" customHeight="1">
+    <row r="101" spans="2:22" ht="25" customHeight="1">
       <c r="B101" s="62">
         <v>0.35</v>
       </c>
@@ -16231,7 +16228,7 @@
       <c r="U101" s="4"/>
       <c r="V101" s="4"/>
     </row>
-    <row r="102" spans="2:22" ht="24.95" customHeight="1">
+    <row r="102" spans="2:22" ht="25" customHeight="1">
       <c r="B102" s="61">
         <v>0.4</v>
       </c>
@@ -16271,7 +16268,7 @@
       <c r="U102" s="4"/>
       <c r="V102" s="4"/>
     </row>
-    <row r="103" spans="2:22" ht="24.95" customHeight="1">
+    <row r="103" spans="2:22" ht="25" customHeight="1">
       <c r="B103" s="62">
         <v>0.45</v>
       </c>
@@ -16311,7 +16308,7 @@
       <c r="U103" s="4"/>
       <c r="V103" s="4"/>
     </row>
-    <row r="104" spans="2:22" ht="24.95" customHeight="1">
+    <row r="104" spans="2:22" ht="25" customHeight="1">
       <c r="B104" s="61">
         <v>0.5</v>
       </c>
@@ -16351,7 +16348,7 @@
       <c r="U104" s="4"/>
       <c r="V104" s="4"/>
     </row>
-    <row r="105" spans="2:22" ht="24.95" customHeight="1">
+    <row r="105" spans="2:22" ht="25" customHeight="1">
       <c r="B105" s="62">
         <v>0.55000000000000004</v>
       </c>
@@ -16391,7 +16388,7 @@
       <c r="U105" s="4"/>
       <c r="V105" s="4"/>
     </row>
-    <row r="106" spans="2:22" ht="24.95" customHeight="1">
+    <row r="106" spans="2:22" ht="25" customHeight="1">
       <c r="B106" s="61">
         <v>0.6</v>
       </c>
@@ -16431,7 +16428,7 @@
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
     </row>
-    <row r="107" spans="2:22" ht="24.95" customHeight="1">
+    <row r="107" spans="2:22" ht="25" customHeight="1">
       <c r="B107" s="62">
         <v>0.65</v>
       </c>
@@ -16471,7 +16468,7 @@
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
     </row>
-    <row r="108" spans="2:22" ht="24.95" customHeight="1">
+    <row r="108" spans="2:22" ht="25" customHeight="1">
       <c r="B108" s="61">
         <v>0.7</v>
       </c>
@@ -16511,7 +16508,7 @@
       <c r="U108" s="4"/>
       <c r="V108" s="4"/>
     </row>
-    <row r="109" spans="2:22" ht="24.95" customHeight="1">
+    <row r="109" spans="2:22" ht="25" customHeight="1">
       <c r="B109" s="62">
         <v>0.75</v>
       </c>
@@ -16551,7 +16548,7 @@
       <c r="U109" s="4"/>
       <c r="V109" s="4"/>
     </row>
-    <row r="110" spans="2:22" ht="24.95" customHeight="1">
+    <row r="110" spans="2:22" ht="25" customHeight="1">
       <c r="B110" s="61">
         <v>0.8</v>
       </c>
@@ -16591,7 +16588,7 @@
       <c r="U110" s="4"/>
       <c r="V110" s="4"/>
     </row>
-    <row r="111" spans="2:22" ht="24.95" customHeight="1">
+    <row r="111" spans="2:22" ht="25" customHeight="1">
       <c r="B111" s="62">
         <v>0.85</v>
       </c>
@@ -16631,7 +16628,7 @@
       <c r="U111" s="4"/>
       <c r="V111" s="4"/>
     </row>
-    <row r="112" spans="2:22" ht="24.95" customHeight="1">
+    <row r="112" spans="2:22" ht="25" customHeight="1">
       <c r="B112" s="61">
         <v>0.9</v>
       </c>
@@ -16671,7 +16668,7 @@
       <c r="U112" s="4"/>
       <c r="V112" s="4"/>
     </row>
-    <row r="113" spans="2:22" ht="24.95" customHeight="1">
+    <row r="113" spans="2:22" ht="25" customHeight="1">
       <c r="B113" s="62">
         <v>0.95</v>
       </c>
@@ -16711,7 +16708,7 @@
       <c r="U113" s="4"/>
       <c r="V113" s="4"/>
     </row>
-    <row r="114" spans="2:22" ht="24.95" customHeight="1">
+    <row r="114" spans="2:22" ht="25" customHeight="1">
       <c r="B114" s="61">
         <v>1</v>
       </c>
@@ -16751,7 +16748,7 @@
       <c r="U114" s="4"/>
       <c r="V114" s="4"/>
     </row>
-    <row r="115" spans="2:22" ht="21.95" customHeight="1">
+    <row r="115" spans="2:22" ht="22" customHeight="1">
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
@@ -16774,7 +16771,7 @@
       <c r="U115" s="4"/>
       <c r="V115" s="4"/>
     </row>
-    <row r="116" spans="2:22" ht="21.95" customHeight="1">
+    <row r="116" spans="2:22" ht="22" customHeight="1">
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -16797,7 +16794,7 @@
       <c r="U116" s="4"/>
       <c r="V116" s="4"/>
     </row>
-    <row r="117" spans="2:22" ht="21.95" customHeight="1">
+    <row r="117" spans="2:22" ht="22" customHeight="1">
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
@@ -16820,7 +16817,7 @@
       <c r="U117" s="4"/>
       <c r="V117" s="4"/>
     </row>
-    <row r="118" spans="2:22" ht="21.95" customHeight="1">
+    <row r="118" spans="2:22" ht="22" customHeight="1">
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
@@ -16843,7 +16840,7 @@
       <c r="U118" s="4"/>
       <c r="V118" s="4"/>
     </row>
-    <row r="119" spans="2:22" ht="21.95" customHeight="1">
+    <row r="119" spans="2:22" ht="22" customHeight="1">
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
@@ -16866,7 +16863,7 @@
       <c r="U119" s="4"/>
       <c r="V119" s="4"/>
     </row>
-    <row r="120" spans="2:22" ht="21.95" customHeight="1">
+    <row r="120" spans="2:22" ht="22" customHeight="1">
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
@@ -16889,32 +16886,32 @@
       <c r="U120" s="4"/>
       <c r="V120" s="4"/>
     </row>
-    <row r="121" spans="2:22" ht="32.1" customHeight="1">
-      <c r="B121" s="95" t="s">
+    <row r="121" spans="2:22" ht="32.15" customHeight="1">
+      <c r="B121" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="C121" s="95"/>
-      <c r="D121" s="95"/>
-      <c r="E121" s="95"/>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
-      <c r="H121" s="95"/>
-      <c r="I121" s="95"/>
-      <c r="J121" s="95"/>
-      <c r="K121" s="95"/>
-      <c r="L121" s="95"/>
-      <c r="M121" s="95"/>
-      <c r="N121" s="95"/>
-      <c r="O121" s="95"/>
-      <c r="P121" s="95"/>
-      <c r="Q121" s="95"/>
-      <c r="R121" s="95"/>
-      <c r="S121" s="95"/>
-      <c r="T121" s="95"/>
-      <c r="U121" s="95"/>
-      <c r="V121" s="95"/>
-    </row>
-    <row r="122" spans="2:22" ht="21.95" customHeight="1">
+      <c r="C121" s="94"/>
+      <c r="D121" s="94"/>
+      <c r="E121" s="94"/>
+      <c r="F121" s="94"/>
+      <c r="G121" s="94"/>
+      <c r="H121" s="94"/>
+      <c r="I121" s="94"/>
+      <c r="J121" s="94"/>
+      <c r="K121" s="94"/>
+      <c r="L121" s="94"/>
+      <c r="M121" s="94"/>
+      <c r="N121" s="94"/>
+      <c r="O121" s="94"/>
+      <c r="P121" s="94"/>
+      <c r="Q121" s="94"/>
+      <c r="R121" s="94"/>
+      <c r="S121" s="94"/>
+      <c r="T121" s="94"/>
+      <c r="U121" s="94"/>
+      <c r="V121" s="94"/>
+    </row>
+    <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -16937,7 +16934,7 @@
       <c r="U122" s="4"/>
       <c r="V122" s="4"/>
     </row>
-    <row r="123" spans="2:22" ht="21.95" customHeight="1">
+    <row r="123" spans="2:22" ht="22" customHeight="1">
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
@@ -16960,7 +16957,7 @@
       <c r="U123" s="4"/>
       <c r="V123" s="4"/>
     </row>
-    <row r="124" spans="2:22" ht="44.1" customHeight="1">
+    <row r="124" spans="2:22" ht="44.15" customHeight="1">
       <c r="B124" s="50" t="s">
         <v>30</v>
       </c>
@@ -17025,7 +17022,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="125" spans="2:22" ht="24.95" customHeight="1">
+    <row r="125" spans="2:22" ht="25" customHeight="1">
       <c r="B125" s="52" t="str">
         <f>"c "&amp;C125&amp;" / C "&amp;D125</f>
         <v>c -24 / C -20</v>
@@ -17111,7 +17108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:22" ht="24.95" customHeight="1">
+    <row r="126" spans="2:22" ht="25" customHeight="1">
       <c r="B126" s="54" t="str">
         <f>"c "&amp;C126&amp;" / C "&amp;D126</f>
         <v>c -18 / C -15</v>
@@ -17197,7 +17194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:22" ht="24.95" customHeight="1">
+    <row r="127" spans="2:22" ht="25" customHeight="1">
       <c r="B127" s="52" t="str">
         <f>"c "&amp;C127&amp;" / C "&amp;D127</f>
         <v>c -12 / C -10</v>
@@ -17283,7 +17280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:22" ht="24.95" customHeight="1">
+    <row r="128" spans="2:22" ht="25" customHeight="1">
       <c r="B128" s="54" t="str">
         <f>"c "&amp;C128&amp;" / C "&amp;D128</f>
         <v>c -6 / C -5</v>
@@ -17369,7 +17366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:22" ht="24.95" customHeight="1">
+    <row r="129" spans="2:22" ht="25" customHeight="1">
       <c r="B129" s="52" t="str">
         <f>"c "&amp;C129&amp;" / C "&amp;D129</f>
         <v>c 0 / C 0</v>
@@ -17455,7 +17452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="2:22" ht="21.95" customHeight="1">
+    <row r="130" spans="2:22" ht="22" customHeight="1">
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
@@ -17478,7 +17475,7 @@
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
     </row>
-    <row r="131" spans="2:22" ht="21.95" customHeight="1">
+    <row r="131" spans="2:22" ht="22" customHeight="1">
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
@@ -17501,7 +17498,7 @@
       <c r="U131" s="4"/>
       <c r="V131" s="4"/>
     </row>
-    <row r="132" spans="2:22" ht="21.95" customHeight="1">
+    <row r="132" spans="2:22" ht="22" customHeight="1">
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
@@ -17579,7 +17576,7 @@
       <c r="U133" s="4"/>
       <c r="V133" s="4"/>
     </row>
-    <row r="134" spans="2:22" ht="24.95" customHeight="1">
+    <row r="134" spans="2:22" ht="25" customHeight="1">
       <c r="B134" s="61">
         <v>0</v>
       </c>
@@ -17634,7 +17631,7 @@
       <c r="U134" s="4"/>
       <c r="V134" s="4"/>
     </row>
-    <row r="135" spans="2:22" ht="24.95" customHeight="1">
+    <row r="135" spans="2:22" ht="25" customHeight="1">
       <c r="B135" s="62">
         <v>0.05</v>
       </c>
@@ -17689,7 +17686,7 @@
       <c r="U135" s="4"/>
       <c r="V135" s="4"/>
     </row>
-    <row r="136" spans="2:22" ht="24.95" customHeight="1">
+    <row r="136" spans="2:22" ht="25" customHeight="1">
       <c r="B136" s="61">
         <v>0.1</v>
       </c>
@@ -17744,7 +17741,7 @@
       <c r="U136" s="4"/>
       <c r="V136" s="4"/>
     </row>
-    <row r="137" spans="2:22" ht="24.95" customHeight="1">
+    <row r="137" spans="2:22" ht="25" customHeight="1">
       <c r="B137" s="62">
         <v>0.15</v>
       </c>
@@ -17799,7 +17796,7 @@
       <c r="U137" s="4"/>
       <c r="V137" s="4"/>
     </row>
-    <row r="138" spans="2:22" ht="24.95" customHeight="1">
+    <row r="138" spans="2:22" ht="25" customHeight="1">
       <c r="B138" s="61">
         <v>0.2</v>
       </c>
@@ -17854,7 +17851,7 @@
       <c r="U138" s="4"/>
       <c r="V138" s="4"/>
     </row>
-    <row r="139" spans="2:22" ht="24.95" customHeight="1">
+    <row r="139" spans="2:22" ht="25" customHeight="1">
       <c r="B139" s="62">
         <v>0.25</v>
       </c>
@@ -17909,7 +17906,7 @@
       <c r="U139" s="4"/>
       <c r="V139" s="4"/>
     </row>
-    <row r="140" spans="2:22" ht="24.95" customHeight="1">
+    <row r="140" spans="2:22" ht="25" customHeight="1">
       <c r="B140" s="61">
         <v>0.3</v>
       </c>
@@ -17964,7 +17961,7 @@
       <c r="U140" s="4"/>
       <c r="V140" s="4"/>
     </row>
-    <row r="141" spans="2:22" ht="24.95" customHeight="1">
+    <row r="141" spans="2:22" ht="25" customHeight="1">
       <c r="B141" s="62">
         <v>0.35</v>
       </c>
@@ -18019,7 +18016,7 @@
       <c r="U141" s="4"/>
       <c r="V141" s="4"/>
     </row>
-    <row r="142" spans="2:22" ht="24.95" customHeight="1">
+    <row r="142" spans="2:22" ht="25" customHeight="1">
       <c r="B142" s="61">
         <v>0.4</v>
       </c>
@@ -18074,7 +18071,7 @@
       <c r="U142" s="4"/>
       <c r="V142" s="4"/>
     </row>
-    <row r="143" spans="2:22" ht="24.95" customHeight="1">
+    <row r="143" spans="2:22" ht="25" customHeight="1">
       <c r="B143" s="62">
         <v>0.45</v>
       </c>
@@ -18129,7 +18126,7 @@
       <c r="U143" s="4"/>
       <c r="V143" s="4"/>
     </row>
-    <row r="144" spans="2:22" ht="24.95" customHeight="1">
+    <row r="144" spans="2:22" ht="25" customHeight="1">
       <c r="B144" s="61">
         <v>0.5</v>
       </c>
@@ -18184,7 +18181,7 @@
       <c r="U144" s="4"/>
       <c r="V144" s="4"/>
     </row>
-    <row r="145" spans="2:22" ht="24.95" customHeight="1">
+    <row r="145" spans="2:22" ht="25" customHeight="1">
       <c r="B145" s="62">
         <v>0.55000000000000004</v>
       </c>
@@ -18239,7 +18236,7 @@
       <c r="U145" s="4"/>
       <c r="V145" s="4"/>
     </row>
-    <row r="146" spans="2:22" ht="24.95" customHeight="1">
+    <row r="146" spans="2:22" ht="25" customHeight="1">
       <c r="B146" s="61">
         <v>0.6</v>
       </c>
@@ -18294,7 +18291,7 @@
       <c r="U146" s="4"/>
       <c r="V146" s="4"/>
     </row>
-    <row r="147" spans="2:22" ht="24.95" customHeight="1">
+    <row r="147" spans="2:22" ht="25" customHeight="1">
       <c r="B147" s="62">
         <v>0.65</v>
       </c>
@@ -18349,7 +18346,7 @@
       <c r="U147" s="4"/>
       <c r="V147" s="4"/>
     </row>
-    <row r="148" spans="2:22" ht="24.95" customHeight="1">
+    <row r="148" spans="2:22" ht="25" customHeight="1">
       <c r="B148" s="61">
         <v>0.7</v>
       </c>
@@ -18404,7 +18401,7 @@
       <c r="U148" s="4"/>
       <c r="V148" s="4"/>
     </row>
-    <row r="149" spans="2:22" ht="24.95" customHeight="1">
+    <row r="149" spans="2:22" ht="25" customHeight="1">
       <c r="B149" s="62">
         <v>0.75</v>
       </c>
@@ -18459,7 +18456,7 @@
       <c r="U149" s="4"/>
       <c r="V149" s="4"/>
     </row>
-    <row r="150" spans="2:22" ht="24.95" customHeight="1">
+    <row r="150" spans="2:22" ht="25" customHeight="1">
       <c r="B150" s="61">
         <v>0.8</v>
       </c>
@@ -18514,7 +18511,7 @@
       <c r="U150" s="4"/>
       <c r="V150" s="4"/>
     </row>
-    <row r="151" spans="2:22" ht="24.95" customHeight="1">
+    <row r="151" spans="2:22" ht="25" customHeight="1">
       <c r="B151" s="62">
         <v>0.85</v>
       </c>
@@ -18569,7 +18566,7 @@
       <c r="U151" s="4"/>
       <c r="V151" s="4"/>
     </row>
-    <row r="152" spans="2:22" ht="24.95" customHeight="1">
+    <row r="152" spans="2:22" ht="25" customHeight="1">
       <c r="B152" s="61">
         <v>0.9</v>
       </c>
@@ -18624,7 +18621,7 @@
       <c r="U152" s="4"/>
       <c r="V152" s="4"/>
     </row>
-    <row r="153" spans="2:22" ht="24.95" customHeight="1">
+    <row r="153" spans="2:22" ht="25" customHeight="1">
       <c r="B153" s="62">
         <v>0.95</v>
       </c>
@@ -18679,7 +18676,7 @@
       <c r="U153" s="4"/>
       <c r="V153" s="4"/>
     </row>
-    <row r="154" spans="2:22" ht="24.95" customHeight="1">
+    <row r="154" spans="2:22" ht="25" customHeight="1">
       <c r="B154" s="61">
         <v>1</v>
       </c>
@@ -18734,7 +18731,7 @@
       <c r="U154" s="4"/>
       <c r="V154" s="4"/>
     </row>
-    <row r="155" spans="2:22" ht="21.95" customHeight="1">
+    <row r="155" spans="2:22" ht="22" customHeight="1">
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
@@ -18757,7 +18754,7 @@
       <c r="U155" s="4"/>
       <c r="V155" s="4"/>
     </row>
-    <row r="156" spans="2:22" ht="21.95" customHeight="1">
+    <row r="156" spans="2:22" ht="22" customHeight="1">
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
@@ -18780,7 +18777,7 @@
       <c r="U156" s="4"/>
       <c r="V156" s="4"/>
     </row>
-    <row r="157" spans="2:22" ht="21.95" customHeight="1">
+    <row r="157" spans="2:22" ht="22" customHeight="1">
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
@@ -18803,32 +18800,32 @@
       <c r="U157" s="4"/>
       <c r="V157" s="4"/>
     </row>
-    <row r="161" spans="2:22" ht="32.1" customHeight="1">
-      <c r="B161" s="96" t="s">
+    <row r="161" spans="2:22" ht="32.15" customHeight="1">
+      <c r="B161" s="95" t="s">
         <v>97</v>
       </c>
-      <c r="C161" s="96"/>
-      <c r="D161" s="96"/>
-      <c r="E161" s="96"/>
-      <c r="F161" s="96"/>
-      <c r="G161" s="96"/>
-      <c r="H161" s="96"/>
-      <c r="I161" s="96"/>
-      <c r="J161" s="96"/>
-      <c r="K161" s="96"/>
-      <c r="L161" s="96"/>
-      <c r="M161" s="96"/>
-      <c r="N161" s="96"/>
-      <c r="O161" s="96"/>
-      <c r="P161" s="96"/>
-      <c r="Q161" s="96"/>
-      <c r="R161" s="96"/>
-      <c r="S161" s="96"/>
-      <c r="T161" s="96"/>
-      <c r="U161" s="96"/>
-      <c r="V161" s="96"/>
-    </row>
-    <row r="164" spans="2:22" ht="44.1" customHeight="1">
+      <c r="C161" s="95"/>
+      <c r="D161" s="95"/>
+      <c r="E161" s="95"/>
+      <c r="F161" s="95"/>
+      <c r="G161" s="95"/>
+      <c r="H161" s="95"/>
+      <c r="I161" s="95"/>
+      <c r="J161" s="95"/>
+      <c r="K161" s="95"/>
+      <c r="L161" s="95"/>
+      <c r="M161" s="95"/>
+      <c r="N161" s="95"/>
+      <c r="O161" s="95"/>
+      <c r="P161" s="95"/>
+      <c r="Q161" s="95"/>
+      <c r="R161" s="95"/>
+      <c r="S161" s="95"/>
+      <c r="T161" s="95"/>
+      <c r="U161" s="95"/>
+      <c r="V161" s="95"/>
+    </row>
+    <row r="164" spans="2:22" ht="44.15" customHeight="1">
       <c r="B164" s="63" t="s">
         <v>30</v>
       </c>
@@ -18893,7 +18890,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="2:22" ht="24.95" customHeight="1">
+    <row r="165" spans="2:22" ht="25" customHeight="1">
       <c r="B165" s="66"/>
       <c r="C165" s="65">
         <f>Calculator!C7</f>

--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D60C570-573C-4FDC-87D8-154D1E472998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5E3E38-4988-43EA-892E-45DB66BE9244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2065,14 +2065,50 @@
     <xf numFmtId="0" fontId="81" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2086,14 +2122,17 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="42" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="27" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2101,47 +2140,8 @@
     <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2315,19 +2315,19 @@
                   <c:v>647.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>827.50000000000011</c:v>
+                  <c:v>840.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1007.5</c:v>
+                  <c:v>1032.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1187.5</c:v>
+                  <c:v>1225</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1367.5</c:v>
+                  <c:v>1417.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1547.5</c:v>
+                  <c:v>1610</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2443,19 +2443,19 @@
                   <c:v>940.22499999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1161.0999999999999</c:v>
+                  <c:v>1173.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1381.9749999999999</c:v>
+                  <c:v>1406.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1602.85</c:v>
+                  <c:v>1640.35</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1823.7250000000004</c:v>
+                  <c:v>1873.7250000000004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2044.6000000000001</c:v>
+                  <c:v>2107.1000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2571,19 +2571,19 @@
                   <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1477.42</c:v>
+                  <c:v>1489.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1736.47</c:v>
+                  <c:v>1761.47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1995.52</c:v>
+                  <c:v>2033.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2254.5700000000002</c:v>
+                  <c:v>2304.5700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2513.62</c:v>
+                  <c:v>2576.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2699,19 +2699,19 @@
                   <c:v>1481.9349999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1776.46</c:v>
+                  <c:v>1788.96</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2070.9850000000001</c:v>
+                  <c:v>2095.9850000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2365.5100000000002</c:v>
+                  <c:v>2403.0100000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2660.0349999999999</c:v>
+                  <c:v>2710.0349999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2954.56</c:v>
+                  <c:v>3017.06</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2827,19 +2827,19 @@
                   <c:v>1730.9199999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2058.2200000000003</c:v>
+                  <c:v>2070.7200000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2385.52</c:v>
+                  <c:v>2410.52</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2712.8199999999997</c:v>
+                  <c:v>2750.3199999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3040.1200000000003</c:v>
+                  <c:v>3090.1200000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3367.42</c:v>
+                  <c:v>3429.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3280,22 +3280,22 @@
                   <c:v>1046.82</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1223.3699999999999</c:v>
+                  <c:v>1223.9949999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1444.92</c:v>
+                  <c:v>1451.7950000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1666.47</c:v>
+                  <c:v>1679.595</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1888.02</c:v>
+                  <c:v>1907.395</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2109.5700000000002</c:v>
+                  <c:v>2135.1950000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2331.12</c:v>
+                  <c:v>2362.9949999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3411,19 +3411,19 @@
                   <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1477.42</c:v>
+                  <c:v>1489.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1736.47</c:v>
+                  <c:v>1761.47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1995.52</c:v>
+                  <c:v>2033.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2254.5700000000002</c:v>
+                  <c:v>2304.5700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2513.62</c:v>
+                  <c:v>2576.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3539,19 +3539,19 @@
                   <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1502.42</c:v>
+                  <c:v>1519.2950000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1798.97</c:v>
+                  <c:v>1834.595</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2095.52</c:v>
+                  <c:v>2149.895</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2392.0700000000002</c:v>
+                  <c:v>2465.1950000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2688.62</c:v>
+                  <c:v>2780.4949999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3667,19 +3667,19 @@
                   <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1519.92</c:v>
+                  <c:v>1539.9200000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1853.97</c:v>
+                  <c:v>1898.9700000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2188.02</c:v>
+                  <c:v>2258.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2522.0700000000006</c:v>
+                  <c:v>2617.0700000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2856.12</c:v>
+                  <c:v>2976.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4953,22 +4953,22 @@
                   <c:v>806.84999999999991</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>945.22499999999991</c:v>
+                  <c:v>945.84999999999991</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1128.5999999999999</c:v>
+                  <c:v>1135.4749999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1311.9749999999999</c:v>
+                  <c:v>1325.1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1495.35</c:v>
+                  <c:v>1514.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1678.7250000000001</c:v>
+                  <c:v>1704.3500000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1862.1000000000001</c:v>
+                  <c:v>1893.9750000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5084,19 +5084,19 @@
                   <c:v>1218.3699999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1477.42</c:v>
+                  <c:v>1489.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1736.47</c:v>
+                  <c:v>1761.47</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1995.52</c:v>
+                  <c:v>2033.02</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2254.5700000000002</c:v>
+                  <c:v>2304.5700000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2513.62</c:v>
+                  <c:v>2576.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5212,19 +5212,19 @@
                   <c:v>1481.9349999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1801.46</c:v>
+                  <c:v>1818.335</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2133.4850000000001</c:v>
+                  <c:v>2169.11</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2465.5100000000002</c:v>
+                  <c:v>2519.8850000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2797.5349999999999</c:v>
+                  <c:v>2870.66</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3129.56</c:v>
+                  <c:v>3221.4349999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5340,19 +5340,19 @@
                   <c:v>1730.9199999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2100.7200000000003</c:v>
+                  <c:v>2120.7200000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2503.02</c:v>
+                  <c:v>2548.02</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2905.3199999999997</c:v>
+                  <c:v>2975.3199999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3307.6200000000008</c:v>
+                  <c:v>3402.6200000000008</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3709.92</c:v>
+                  <c:v>3829.92</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6536,14 +6536,14 @@
     </row>
     <row r="2" spans="1:8" ht="35.15" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -6594,7 +6594,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="85" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="6"/>
@@ -6614,7 +6614,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="73"/>
+      <c r="B7" s="85"/>
       <c r="C7" s="6"/>
       <c r="D7" s="19" t="s">
         <v>77</v>
@@ -6746,20 +6746,20 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
@@ -6767,19 +6767,19 @@
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="25" customHeight="1">
@@ -6864,17 +6864,17 @@
       <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -6904,15 +6904,15 @@
         <v>98</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6943,13 +6943,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6990,13 +6990,13 @@
       <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="77">
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="90">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>1736.47</v>
-      </c>
-      <c r="J8" s="78"/>
+        <v>1761.47</v>
+      </c>
+      <c r="J8" s="91"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -7037,13 +7037,13 @@
       <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="77">
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="90">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1519.2</v>
       </c>
-      <c r="J10" s="78"/>
+      <c r="J10" s="91"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -7095,13 +7095,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="74" t="s">
+      <c r="F13" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -7119,11 +7119,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="79" t="s">
+      <c r="F14" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
       <c r="I14" s="34">
         <f>Samples!F165</f>
         <v>3650</v>
@@ -7148,11 +7148,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
       <c r="I15" s="35">
         <f>Samples!I165</f>
         <v>3431</v>
@@ -7172,14 +7172,14 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
       <c r="I16" s="34">
         <f>Samples!J165</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="J16" s="25" t="s">
         <v>11</v>
@@ -7199,11 +7199,11 @@
       <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
       <c r="I17" s="35">
         <f>Samples!L165</f>
-        <v>5181</v>
+        <v>5431</v>
       </c>
       <c r="J17" s="28" t="s">
         <v>11</v>
@@ -7242,11 +7242,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="79" t="s">
+      <c r="F19" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
       <c r="I19" s="34">
         <f>Samples!M165</f>
         <v>3600</v>
@@ -7266,11 +7266,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
       <c r="I20" s="35">
         <f>Samples!P165</f>
         <v>3096</v>
@@ -7307,11 +7307,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
       <c r="I22" s="37">
         <f>Samples!G165</f>
         <v>0.08</v>
@@ -7334,8 +7334,8 @@
       <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
       <c r="I23" s="38">
         <f>Samples!K165</f>
         <v>0.35</v>
@@ -7355,11 +7355,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="79" t="s">
+      <c r="F24" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
       <c r="I24" s="37">
         <f>Samples!N165</f>
         <v>0.25</v>
@@ -7409,20 +7409,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="87"/>
+      <c r="L27" s="87"/>
+      <c r="M27" s="87"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -7683,17 +7683,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -7701,6 +7690,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -7760,17 +7760,17 @@
       <c r="B2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -7800,15 +7800,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8430,18 +8430,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
+      <c r="M41" s="92"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8518,17 +8518,17 @@
       <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -8558,15 +8558,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9188,18 +9188,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
+      <c r="M41" s="92"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9276,17 +9276,17 @@
       <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -9316,15 +9316,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9942,18 +9942,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
+      <c r="M41" s="92"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10026,17 +10026,17 @@
       <c r="B2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -10066,15 +10066,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10692,18 +10692,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
-      <c r="M41" s="69"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
+      <c r="M41" s="92"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10780,37 +10780,37 @@
       <c r="B2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -10834,21 +10834,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="75" t="s">
+      <c r="J5" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -11164,17 +11164,17 @@
       </c>
       <c r="E13" s="43">
         <f>(D13+F13)/2</f>
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="F13" s="29">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="43">
         <f>(F13+H13)/2</f>
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="H13" s="29">
-        <v>3250</v>
+        <v>3750</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="29">
@@ -11478,44 +11478,44 @@
     </row>
     <row r="22" spans="1:15" ht="32.15" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="74" t="s">
+      <c r="B22" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
-      <c r="N22" s="75"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="74"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29.15" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="82" t="s">
+      <c r="B23" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="80"/>
+      <c r="C23" s="77"/>
       <c r="D23" s="31">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="87" t="s">
+      <c r="F23" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="88"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="80"/>
+      <c r="L23" s="80"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="80"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29.15" customHeight="1">
@@ -11523,28 +11523,28 @@
       <c r="B24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="81"/>
+      <c r="C24" s="70"/>
       <c r="D24" s="33">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="88"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29.15" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="80"/>
+      <c r="C25" s="77"/>
       <c r="D25" s="31">
         <v>40</v>
       </c>
@@ -11562,25 +11562,25 @@
     </row>
     <row r="26" spans="1:15" ht="29.15" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="81"/>
+      <c r="C26" s="70"/>
       <c r="D26" s="33">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="89" t="s">
+      <c r="F26" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="86"/>
-      <c r="M26" s="86"/>
-      <c r="N26" s="86"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="73"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29.15" customHeight="1">
@@ -11588,7 +11588,7 @@
       <c r="B27" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="81"/>
+      <c r="C27" s="70"/>
       <c r="D27" s="33">
         <v>10</v>
       </c>
@@ -11606,21 +11606,21 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="90" t="s">
+      <c r="B28" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="91"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="91"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
@@ -11642,19 +11642,19 @@
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="92"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="92"/>
-      <c r="I30" s="92"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="92"/>
-      <c r="L30" s="92"/>
-      <c r="M30" s="92"/>
-      <c r="N30" s="92"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="69"/>
+      <c r="N30" s="69"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
@@ -11846,14 +11846,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -11866,6 +11858,14 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="J5" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K5" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="L5" s="51">
         <f>I5+J5</f>
-        <v>3600</v>
+        <v>3850</v>
       </c>
       <c r="M5" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="J6" s="53">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K6" s="53">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="L6" s="53">
         <f>I6+J6</f>
-        <v>4417.5</v>
+        <v>4667.5</v>
       </c>
       <c r="M6" s="53">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="J7" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K7" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="L7" s="51">
         <f>I7+J7</f>
-        <v>5181</v>
+        <v>5431</v>
       </c>
       <c r="M7" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="J8" s="53">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K8" s="53">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="L8" s="53">
         <f>I8+J8</f>
-        <v>5890.5</v>
+        <v>6140.5</v>
       </c>
       <c r="M8" s="53">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
@@ -12409,7 +12409,7 @@
       </c>
       <c r="J9" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K9" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="L9" s="51">
         <f>I9+J9</f>
-        <v>6546</v>
+        <v>6796</v>
       </c>
       <c r="M9" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
@@ -12908,23 +12908,23 @@
       </c>
       <c r="C22" s="57">
         <f t="shared" si="0"/>
-        <v>827.50000000000011</v>
+        <v>840.00000000000011</v>
       </c>
       <c r="D22" s="57">
         <f t="shared" si="1"/>
-        <v>1161.0999999999999</v>
+        <v>1173.5999999999999</v>
       </c>
       <c r="E22" s="57">
         <f t="shared" si="2"/>
-        <v>1477.42</v>
+        <v>1489.92</v>
       </c>
       <c r="F22" s="57">
         <f t="shared" si="3"/>
-        <v>1776.46</v>
+        <v>1788.96</v>
       </c>
       <c r="G22" s="57">
         <f t="shared" si="4"/>
-        <v>2058.2200000000003</v>
+        <v>2070.7200000000003</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -12949,23 +12949,23 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="0"/>
-        <v>1007.5</v>
+        <v>1032.5</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="1"/>
-        <v>1381.9749999999999</v>
+        <v>1406.9749999999999</v>
       </c>
       <c r="E23" s="58">
         <f t="shared" si="2"/>
-        <v>1736.47</v>
+        <v>1761.47</v>
       </c>
       <c r="F23" s="58">
         <f t="shared" si="3"/>
-        <v>2070.9850000000001</v>
+        <v>2095.9850000000001</v>
       </c>
       <c r="G23" s="58">
         <f t="shared" si="4"/>
-        <v>2385.52</v>
+        <v>2410.52</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -12990,23 +12990,23 @@
       </c>
       <c r="C24" s="57">
         <f t="shared" si="0"/>
-        <v>1187.5</v>
+        <v>1225</v>
       </c>
       <c r="D24" s="57">
         <f t="shared" si="1"/>
-        <v>1602.85</v>
+        <v>1640.35</v>
       </c>
       <c r="E24" s="57">
         <f t="shared" si="2"/>
-        <v>1995.52</v>
+        <v>2033.02</v>
       </c>
       <c r="F24" s="57">
         <f t="shared" si="3"/>
-        <v>2365.5100000000002</v>
+        <v>2403.0100000000002</v>
       </c>
       <c r="G24" s="57">
         <f t="shared" si="4"/>
-        <v>2712.8199999999997</v>
+        <v>2750.3199999999997</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -13031,23 +13031,23 @@
       </c>
       <c r="C25" s="58">
         <f t="shared" si="0"/>
-        <v>1367.5</v>
+        <v>1417.5</v>
       </c>
       <c r="D25" s="58">
         <f t="shared" si="1"/>
-        <v>1823.7250000000004</v>
+        <v>1873.7250000000004</v>
       </c>
       <c r="E25" s="58">
         <f t="shared" si="2"/>
-        <v>2254.5700000000002</v>
+        <v>2304.5700000000002</v>
       </c>
       <c r="F25" s="58">
         <f t="shared" si="3"/>
-        <v>2660.0349999999999</v>
+        <v>2710.0349999999999</v>
       </c>
       <c r="G25" s="58">
         <f t="shared" si="4"/>
-        <v>3040.1200000000003</v>
+        <v>3090.1200000000003</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -13072,23 +13072,23 @@
       </c>
       <c r="C26" s="57">
         <f t="shared" si="0"/>
-        <v>1547.5</v>
+        <v>1610</v>
       </c>
       <c r="D26" s="57">
         <f t="shared" si="1"/>
-        <v>2044.6000000000001</v>
+        <v>2107.1000000000004</v>
       </c>
       <c r="E26" s="57">
         <f t="shared" si="2"/>
-        <v>2513.62</v>
+        <v>2576.12</v>
       </c>
       <c r="F26" s="57">
         <f t="shared" si="3"/>
-        <v>2954.56</v>
+        <v>3017.06</v>
       </c>
       <c r="G26" s="57">
         <f t="shared" si="4"/>
-        <v>3367.42</v>
+        <v>3429.92</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -13113,23 +13113,23 @@
       </c>
       <c r="C27" s="58">
         <f t="shared" si="0"/>
-        <v>1727.5000000000005</v>
+        <v>1802.5000000000005</v>
       </c>
       <c r="D27" s="58">
         <f t="shared" si="1"/>
-        <v>2265.4750000000004</v>
+        <v>2340.4750000000004</v>
       </c>
       <c r="E27" s="58">
         <f t="shared" si="2"/>
-        <v>2772.67</v>
+        <v>2847.67</v>
       </c>
       <c r="F27" s="58">
         <f t="shared" si="3"/>
-        <v>3249.085</v>
+        <v>3324.085</v>
       </c>
       <c r="G27" s="58">
         <f t="shared" si="4"/>
-        <v>3694.7200000000003</v>
+        <v>3769.7200000000003</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -13154,23 +13154,23 @@
       </c>
       <c r="C28" s="57">
         <f t="shared" si="0"/>
-        <v>1907.5</v>
+        <v>1995</v>
       </c>
       <c r="D28" s="57">
         <f t="shared" si="1"/>
-        <v>2486.35</v>
+        <v>2573.85</v>
       </c>
       <c r="E28" s="57">
         <f t="shared" si="2"/>
-        <v>3031.72</v>
+        <v>3119.22</v>
       </c>
       <c r="F28" s="57">
         <f t="shared" si="3"/>
-        <v>3543.61</v>
+        <v>3631.11</v>
       </c>
       <c r="G28" s="57">
         <f t="shared" si="4"/>
-        <v>4022.02</v>
+        <v>4109.5200000000004</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -13195,23 +13195,23 @@
       </c>
       <c r="C29" s="58">
         <f t="shared" si="0"/>
-        <v>2087.5</v>
+        <v>2187.5</v>
       </c>
       <c r="D29" s="58">
         <f t="shared" si="1"/>
-        <v>2707.2250000000004</v>
+        <v>2807.2250000000004</v>
       </c>
       <c r="E29" s="58">
         <f t="shared" si="2"/>
-        <v>3290.77</v>
+        <v>3390.77</v>
       </c>
       <c r="F29" s="58">
         <f t="shared" si="3"/>
-        <v>3838.1350000000002</v>
+        <v>3938.1350000000002</v>
       </c>
       <c r="G29" s="58">
         <f t="shared" si="4"/>
-        <v>4349.32</v>
+        <v>4449.32</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -13236,23 +13236,23 @@
       </c>
       <c r="C30" s="57">
         <f t="shared" si="0"/>
-        <v>2267.5000000000005</v>
+        <v>2380.0000000000005</v>
       </c>
       <c r="D30" s="57">
         <f t="shared" si="1"/>
-        <v>2928.1000000000004</v>
+        <v>3040.6000000000004</v>
       </c>
       <c r="E30" s="57">
         <f t="shared" si="2"/>
-        <v>3549.82</v>
+        <v>3662.32</v>
       </c>
       <c r="F30" s="57">
         <f t="shared" si="3"/>
-        <v>4132.6600000000008</v>
+        <v>4245.1600000000008</v>
       </c>
       <c r="G30" s="57">
         <f t="shared" si="4"/>
-        <v>4676.6200000000008</v>
+        <v>4789.1200000000008</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -13277,23 +13277,23 @@
       </c>
       <c r="C31" s="58">
         <f t="shared" si="0"/>
-        <v>2447.5</v>
+        <v>2572.5</v>
       </c>
       <c r="D31" s="58">
         <f t="shared" si="1"/>
-        <v>3148.9749999999999</v>
+        <v>3273.9749999999999</v>
       </c>
       <c r="E31" s="58">
         <f t="shared" si="2"/>
-        <v>3808.87</v>
+        <v>3933.87</v>
       </c>
       <c r="F31" s="58">
         <f t="shared" si="3"/>
-        <v>4427.1849999999995</v>
+        <v>4552.1849999999995</v>
       </c>
       <c r="G31" s="58">
         <f t="shared" si="4"/>
-        <v>5003.92</v>
+        <v>5128.92</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -13318,23 +13318,23 @@
       </c>
       <c r="C32" s="57">
         <f t="shared" si="0"/>
-        <v>2627.5000000000005</v>
+        <v>2765</v>
       </c>
       <c r="D32" s="57">
         <f t="shared" si="1"/>
-        <v>3369.8500000000004</v>
+        <v>3507.3500000000004</v>
       </c>
       <c r="E32" s="57">
         <f t="shared" si="2"/>
-        <v>4067.92</v>
+        <v>4205.42</v>
       </c>
       <c r="F32" s="57">
         <f t="shared" si="3"/>
-        <v>4721.71</v>
+        <v>4859.21</v>
       </c>
       <c r="G32" s="57">
         <f t="shared" si="4"/>
-        <v>5331.22</v>
+        <v>5468.72</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -13359,23 +13359,23 @@
       </c>
       <c r="C33" s="58">
         <f t="shared" si="0"/>
-        <v>2807.5</v>
+        <v>2957.5</v>
       </c>
       <c r="D33" s="58">
         <f t="shared" si="1"/>
-        <v>3590.7249999999999</v>
+        <v>3740.7249999999999</v>
       </c>
       <c r="E33" s="58">
         <f t="shared" si="2"/>
-        <v>4326.9699999999993</v>
+        <v>4476.9699999999993</v>
       </c>
       <c r="F33" s="58">
         <f t="shared" si="3"/>
-        <v>5016.2350000000006</v>
+        <v>5166.2350000000006</v>
       </c>
       <c r="G33" s="58">
         <f t="shared" si="4"/>
-        <v>5658.5199999999995</v>
+        <v>5808.5199999999995</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -13400,23 +13400,23 @@
       </c>
       <c r="C34" s="57">
         <f t="shared" si="0"/>
-        <v>2987.5</v>
+        <v>3150</v>
       </c>
       <c r="D34" s="57">
         <f t="shared" si="1"/>
-        <v>3811.6</v>
+        <v>3974.1</v>
       </c>
       <c r="E34" s="57">
         <f t="shared" si="2"/>
-        <v>4586.0200000000004</v>
+        <v>4748.5200000000004</v>
       </c>
       <c r="F34" s="57">
         <f t="shared" si="3"/>
-        <v>5310.76</v>
+        <v>5473.26</v>
       </c>
       <c r="G34" s="57">
         <f t="shared" si="4"/>
-        <v>5985.8200000000006</v>
+        <v>6148.3200000000006</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="J46" s="54">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="K46" s="54">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="L46" s="54">
         <f>I46+J46</f>
-        <v>4431</v>
+        <v>4556</v>
       </c>
       <c r="M46" s="54">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
@@ -13923,7 +13923,7 @@
       </c>
       <c r="J47" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K47" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -13931,7 +13931,7 @@
       </c>
       <c r="L47" s="52">
         <f>I47+J47</f>
-        <v>5181</v>
+        <v>5431</v>
       </c>
       <c r="M47" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="J48" s="54">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="K48" s="54">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="L48" s="54">
         <f>I48+J48</f>
-        <v>5931</v>
+        <v>6306</v>
       </c>
       <c r="M48" s="54">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
@@ -14095,7 +14095,7 @@
       </c>
       <c r="J49" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>3250</v>
+        <v>3750</v>
       </c>
       <c r="K49" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
@@ -14103,7 +14103,7 @@
       </c>
       <c r="L49" s="52">
         <f>I49+J49</f>
-        <v>6681</v>
+        <v>7181</v>
       </c>
       <c r="M49" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="D61" s="62">
         <f t="shared" si="6"/>
-        <v>1223.3699999999999</v>
+        <v>1223.9949999999999</v>
       </c>
       <c r="E61" s="62">
         <f t="shared" si="7"/>
@@ -14585,19 +14585,19 @@
       </c>
       <c r="D62" s="61">
         <f t="shared" si="6"/>
-        <v>1444.92</v>
+        <v>1451.7950000000001</v>
       </c>
       <c r="E62" s="61">
         <f t="shared" si="7"/>
-        <v>1477.42</v>
+        <v>1489.92</v>
       </c>
       <c r="F62" s="61">
         <f t="shared" si="8"/>
-        <v>1502.42</v>
+        <v>1519.2950000000001</v>
       </c>
       <c r="G62" s="61">
         <f t="shared" si="9"/>
-        <v>1519.92</v>
+        <v>1539.9200000000003</v>
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -14625,19 +14625,19 @@
       </c>
       <c r="D63" s="62">
         <f t="shared" si="6"/>
-        <v>1666.47</v>
+        <v>1679.595</v>
       </c>
       <c r="E63" s="62">
         <f t="shared" si="7"/>
-        <v>1736.47</v>
+        <v>1761.47</v>
       </c>
       <c r="F63" s="62">
         <f t="shared" si="8"/>
-        <v>1798.97</v>
+        <v>1834.595</v>
       </c>
       <c r="G63" s="62">
         <f t="shared" si="9"/>
-        <v>1853.97</v>
+        <v>1898.9700000000003</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -14665,19 +14665,19 @@
       </c>
       <c r="D64" s="61">
         <f t="shared" si="6"/>
-        <v>1888.02</v>
+        <v>1907.395</v>
       </c>
       <c r="E64" s="61">
         <f t="shared" si="7"/>
-        <v>1995.52</v>
+        <v>2033.02</v>
       </c>
       <c r="F64" s="61">
         <f t="shared" si="8"/>
-        <v>2095.52</v>
+        <v>2149.895</v>
       </c>
       <c r="G64" s="61">
         <f t="shared" si="9"/>
-        <v>2188.02</v>
+        <v>2258.02</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -14705,19 +14705,19 @@
       </c>
       <c r="D65" s="62">
         <f t="shared" si="6"/>
-        <v>2109.5700000000002</v>
+        <v>2135.1950000000002</v>
       </c>
       <c r="E65" s="62">
         <f t="shared" si="7"/>
-        <v>2254.5700000000002</v>
+        <v>2304.5700000000002</v>
       </c>
       <c r="F65" s="62">
         <f t="shared" si="8"/>
-        <v>2392.0700000000002</v>
+        <v>2465.1950000000006</v>
       </c>
       <c r="G65" s="62">
         <f t="shared" si="9"/>
-        <v>2522.0700000000006</v>
+        <v>2617.0700000000006</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -14745,19 +14745,19 @@
       </c>
       <c r="D66" s="61">
         <f t="shared" si="6"/>
-        <v>2331.12</v>
+        <v>2362.9949999999999</v>
       </c>
       <c r="E66" s="61">
         <f t="shared" si="7"/>
-        <v>2513.62</v>
+        <v>2576.12</v>
       </c>
       <c r="F66" s="61">
         <f t="shared" si="8"/>
-        <v>2688.62</v>
+        <v>2780.4949999999999</v>
       </c>
       <c r="G66" s="61">
         <f t="shared" si="9"/>
-        <v>2856.12</v>
+        <v>2976.12</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -14785,19 +14785,19 @@
       </c>
       <c r="D67" s="62">
         <f t="shared" si="6"/>
-        <v>2552.67</v>
+        <v>2590.7950000000001</v>
       </c>
       <c r="E67" s="62">
         <f t="shared" si="7"/>
-        <v>2772.67</v>
+        <v>2847.67</v>
       </c>
       <c r="F67" s="62">
         <f t="shared" si="8"/>
-        <v>2985.17</v>
+        <v>3095.7950000000001</v>
       </c>
       <c r="G67" s="62">
         <f t="shared" si="9"/>
-        <v>3190.17</v>
+        <v>3335.17</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -14825,19 +14825,19 @@
       </c>
       <c r="D68" s="61">
         <f t="shared" si="6"/>
-        <v>2774.22</v>
+        <v>2818.5949999999998</v>
       </c>
       <c r="E68" s="61">
         <f t="shared" si="7"/>
-        <v>3031.72</v>
+        <v>3119.22</v>
       </c>
       <c r="F68" s="61">
         <f t="shared" si="8"/>
-        <v>3281.72</v>
+        <v>3411.0949999999998</v>
       </c>
       <c r="G68" s="61">
         <f t="shared" si="9"/>
-        <v>3524.22</v>
+        <v>3694.2199999999993</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -14865,19 +14865,19 @@
       </c>
       <c r="D69" s="62">
         <f t="shared" si="6"/>
-        <v>2995.77</v>
+        <v>3046.395</v>
       </c>
       <c r="E69" s="62">
         <f t="shared" si="7"/>
-        <v>3290.77</v>
+        <v>3390.77</v>
       </c>
       <c r="F69" s="62">
         <f t="shared" si="8"/>
-        <v>3578.27</v>
+        <v>3726.395</v>
       </c>
       <c r="G69" s="62">
         <f t="shared" si="9"/>
-        <v>3858.27</v>
+        <v>4053.27</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -14905,19 +14905,19 @@
       </c>
       <c r="D70" s="61">
         <f t="shared" si="6"/>
-        <v>3217.32</v>
+        <v>3274.1950000000002</v>
       </c>
       <c r="E70" s="61">
         <f t="shared" si="7"/>
-        <v>3549.82</v>
+        <v>3662.32</v>
       </c>
       <c r="F70" s="61">
         <f t="shared" si="8"/>
-        <v>3874.8200000000006</v>
+        <v>4041.6950000000006</v>
       </c>
       <c r="G70" s="61">
         <f t="shared" si="9"/>
-        <v>4192.3200000000006</v>
+        <v>4412.3200000000006</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -14945,19 +14945,19 @@
       </c>
       <c r="D71" s="62">
         <f t="shared" si="6"/>
-        <v>3438.87</v>
+        <v>3501.9949999999999</v>
       </c>
       <c r="E71" s="62">
         <f t="shared" si="7"/>
-        <v>3808.87</v>
+        <v>3933.87</v>
       </c>
       <c r="F71" s="62">
         <f t="shared" si="8"/>
-        <v>4171.37</v>
+        <v>4356.9949999999999</v>
       </c>
       <c r="G71" s="62">
         <f t="shared" si="9"/>
-        <v>4526.37</v>
+        <v>4771.37</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -14985,19 +14985,19 @@
       </c>
       <c r="D72" s="61">
         <f t="shared" si="6"/>
-        <v>3660.42</v>
+        <v>3729.7950000000001</v>
       </c>
       <c r="E72" s="61">
         <f t="shared" si="7"/>
-        <v>4067.92</v>
+        <v>4205.42</v>
       </c>
       <c r="F72" s="61">
         <f t="shared" si="8"/>
-        <v>4467.92</v>
+        <v>4672.2950000000001</v>
       </c>
       <c r="G72" s="61">
         <f t="shared" si="9"/>
-        <v>4860.42</v>
+        <v>5130.42</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -15025,19 +15025,19 @@
       </c>
       <c r="D73" s="62">
         <f t="shared" si="6"/>
-        <v>3881.97</v>
+        <v>3957.5949999999998</v>
       </c>
       <c r="E73" s="62">
         <f t="shared" si="7"/>
-        <v>4326.9699999999993</v>
+        <v>4476.9699999999993</v>
       </c>
       <c r="F73" s="62">
         <f t="shared" si="8"/>
-        <v>4764.4699999999993</v>
+        <v>4987.5949999999993</v>
       </c>
       <c r="G73" s="62">
         <f t="shared" si="9"/>
-        <v>5194.4699999999993</v>
+        <v>5489.4699999999993</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -15065,19 +15065,19 @@
       </c>
       <c r="D74" s="61">
         <f t="shared" si="6"/>
-        <v>4103.5200000000004</v>
+        <v>4185.3950000000004</v>
       </c>
       <c r="E74" s="61">
         <f t="shared" si="7"/>
-        <v>4586.0200000000004</v>
+        <v>4748.5200000000004</v>
       </c>
       <c r="F74" s="61">
         <f t="shared" si="8"/>
-        <v>5061.0200000000004</v>
+        <v>5302.8950000000004</v>
       </c>
       <c r="G74" s="61">
         <f t="shared" si="9"/>
-        <v>5528.52</v>
+        <v>5848.52</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="J86" s="54">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="K86" s="54">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="L86" s="54">
         <f>I86+J86</f>
-        <v>3667.5</v>
+        <v>3792.5</v>
       </c>
       <c r="M86" s="54">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="J87" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K87" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="L87" s="52">
         <f>I87+J87</f>
-        <v>5181</v>
+        <v>5431</v>
       </c>
       <c r="M87" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="J88" s="54">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="K88" s="54">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="L88" s="54">
         <f>I88+J88</f>
-        <v>6640.5</v>
+        <v>7015.5</v>
       </c>
       <c r="M88" s="54">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="J89" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>3250</v>
+        <v>3750</v>
       </c>
       <c r="K89" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
@@ -15756,7 +15756,7 @@
       </c>
       <c r="L89" s="52">
         <f>I89+J89</f>
-        <v>8046</v>
+        <v>8546</v>
       </c>
       <c r="M89" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="J126" s="54">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>1000</v>
+        <v>1125</v>
       </c>
       <c r="K126" s="54">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="L126" s="54">
         <f>I126+J126</f>
-        <v>3667.5</v>
+        <v>3792.5</v>
       </c>
       <c r="M126" s="54">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="J127" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K127" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
@@ -17237,7 +17237,7 @@
       </c>
       <c r="L127" s="52">
         <f>I127+J127</f>
-        <v>5181</v>
+        <v>5431</v>
       </c>
       <c r="M127" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="J128" s="54">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="K128" s="54">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="L128" s="54">
         <f>I128+J128</f>
-        <v>6640.5</v>
+        <v>7015.5</v>
       </c>
       <c r="M128" s="54">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="J129" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>3250</v>
+        <v>3750</v>
       </c>
       <c r="K129" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="L129" s="52">
         <f>I129+J129</f>
-        <v>8046</v>
+        <v>8546</v>
       </c>
       <c r="M129" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
@@ -17971,7 +17971,7 @@
       </c>
       <c r="D141" s="62">
         <f t="shared" si="16"/>
-        <v>945.22499999999991</v>
+        <v>945.84999999999991</v>
       </c>
       <c r="E141" s="62">
         <f t="shared" si="17"/>
@@ -18026,19 +18026,19 @@
       </c>
       <c r="D142" s="61">
         <f t="shared" si="16"/>
-        <v>1128.5999999999999</v>
+        <v>1135.4749999999999</v>
       </c>
       <c r="E142" s="61">
         <f t="shared" si="17"/>
-        <v>1477.42</v>
+        <v>1489.92</v>
       </c>
       <c r="F142" s="61">
         <f t="shared" si="18"/>
-        <v>1801.46</v>
+        <v>1818.335</v>
       </c>
       <c r="G142" s="61">
         <f t="shared" si="19"/>
-        <v>2100.7200000000003</v>
+        <v>2120.7200000000003</v>
       </c>
       <c r="H142" s="61">
         <f t="shared" si="20"/>
@@ -18081,19 +18081,19 @@
       </c>
       <c r="D143" s="62">
         <f t="shared" si="16"/>
-        <v>1311.9749999999999</v>
+        <v>1325.1</v>
       </c>
       <c r="E143" s="62">
         <f t="shared" si="17"/>
-        <v>1736.47</v>
+        <v>1761.47</v>
       </c>
       <c r="F143" s="62">
         <f t="shared" si="18"/>
-        <v>2133.4850000000001</v>
+        <v>2169.11</v>
       </c>
       <c r="G143" s="62">
         <f t="shared" si="19"/>
-        <v>2503.02</v>
+        <v>2548.02</v>
       </c>
       <c r="H143" s="62">
         <f t="shared" si="20"/>
@@ -18136,19 +18136,19 @@
       </c>
       <c r="D144" s="61">
         <f t="shared" si="16"/>
-        <v>1495.35</v>
+        <v>1514.7249999999999</v>
       </c>
       <c r="E144" s="61">
         <f t="shared" si="17"/>
-        <v>1995.52</v>
+        <v>2033.02</v>
       </c>
       <c r="F144" s="61">
         <f t="shared" si="18"/>
-        <v>2465.5100000000002</v>
+        <v>2519.8850000000002</v>
       </c>
       <c r="G144" s="61">
         <f t="shared" si="19"/>
-        <v>2905.3199999999997</v>
+        <v>2975.3199999999997</v>
       </c>
       <c r="H144" s="61">
         <f t="shared" si="20"/>
@@ -18191,19 +18191,19 @@
       </c>
       <c r="D145" s="62">
         <f t="shared" si="16"/>
-        <v>1678.7250000000001</v>
+        <v>1704.3500000000001</v>
       </c>
       <c r="E145" s="62">
         <f t="shared" si="17"/>
-        <v>2254.5700000000002</v>
+        <v>2304.5700000000002</v>
       </c>
       <c r="F145" s="62">
         <f t="shared" si="18"/>
-        <v>2797.5349999999999</v>
+        <v>2870.66</v>
       </c>
       <c r="G145" s="62">
         <f t="shared" si="19"/>
-        <v>3307.6200000000008</v>
+        <v>3402.6200000000008</v>
       </c>
       <c r="H145" s="62">
         <f t="shared" si="20"/>
@@ -18246,19 +18246,19 @@
       </c>
       <c r="D146" s="61">
         <f t="shared" si="16"/>
-        <v>1862.1000000000001</v>
+        <v>1893.9750000000001</v>
       </c>
       <c r="E146" s="61">
         <f t="shared" si="17"/>
-        <v>2513.62</v>
+        <v>2576.12</v>
       </c>
       <c r="F146" s="61">
         <f t="shared" si="18"/>
-        <v>3129.56</v>
+        <v>3221.4349999999999</v>
       </c>
       <c r="G146" s="61">
         <f t="shared" si="19"/>
-        <v>3709.92</v>
+        <v>3829.92</v>
       </c>
       <c r="H146" s="61">
         <f t="shared" si="20"/>
@@ -18301,19 +18301,19 @@
       </c>
       <c r="D147" s="62">
         <f t="shared" si="16"/>
-        <v>2045.4750000000001</v>
+        <v>2083.6000000000004</v>
       </c>
       <c r="E147" s="62">
         <f t="shared" si="17"/>
-        <v>2772.67</v>
+        <v>2847.67</v>
       </c>
       <c r="F147" s="62">
         <f t="shared" si="18"/>
-        <v>3461.585</v>
+        <v>3572.21</v>
       </c>
       <c r="G147" s="62">
         <f t="shared" si="19"/>
-        <v>4112.22</v>
+        <v>4257.22</v>
       </c>
       <c r="H147" s="62">
         <f t="shared" si="20"/>
@@ -18356,19 +18356,19 @@
       </c>
       <c r="D148" s="61">
         <f t="shared" si="16"/>
-        <v>2228.85</v>
+        <v>2273.2249999999999</v>
       </c>
       <c r="E148" s="61">
         <f t="shared" si="17"/>
-        <v>3031.72</v>
+        <v>3119.22</v>
       </c>
       <c r="F148" s="61">
         <f t="shared" si="18"/>
-        <v>3793.61</v>
+        <v>3922.9850000000001</v>
       </c>
       <c r="G148" s="61">
         <f t="shared" si="19"/>
-        <v>4514.5200000000004</v>
+        <v>4684.5199999999995</v>
       </c>
       <c r="H148" s="61">
         <f t="shared" si="20"/>
@@ -18411,19 +18411,19 @@
       </c>
       <c r="D149" s="62">
         <f t="shared" si="16"/>
-        <v>2412.2250000000004</v>
+        <v>2462.8500000000004</v>
       </c>
       <c r="E149" s="62">
         <f t="shared" si="17"/>
-        <v>3290.77</v>
+        <v>3390.77</v>
       </c>
       <c r="F149" s="62">
         <f t="shared" si="18"/>
-        <v>4125.6350000000002</v>
+        <v>4273.76</v>
       </c>
       <c r="G149" s="62">
         <f t="shared" si="19"/>
-        <v>4916.82</v>
+        <v>5111.82</v>
       </c>
       <c r="H149" s="62">
         <f t="shared" si="20"/>
@@ -18466,19 +18466,19 @@
       </c>
       <c r="D150" s="61">
         <f t="shared" si="16"/>
-        <v>2595.6000000000004</v>
+        <v>2652.4750000000004</v>
       </c>
       <c r="E150" s="61">
         <f t="shared" si="17"/>
-        <v>3549.82</v>
+        <v>3662.32</v>
       </c>
       <c r="F150" s="61">
         <f t="shared" si="18"/>
-        <v>4457.6600000000008</v>
+        <v>4624.5350000000008</v>
       </c>
       <c r="G150" s="61">
         <f t="shared" si="19"/>
-        <v>5319.1200000000008</v>
+        <v>5539.1200000000008</v>
       </c>
       <c r="H150" s="61">
         <f t="shared" si="20"/>
@@ -18521,19 +18521,19 @@
       </c>
       <c r="D151" s="62">
         <f t="shared" si="16"/>
-        <v>2778.9749999999999</v>
+        <v>2842.1</v>
       </c>
       <c r="E151" s="62">
         <f t="shared" si="17"/>
-        <v>3808.87</v>
+        <v>3933.87</v>
       </c>
       <c r="F151" s="62">
         <f t="shared" si="18"/>
-        <v>4789.6849999999995</v>
+        <v>4975.3099999999995</v>
       </c>
       <c r="G151" s="62">
         <f t="shared" si="19"/>
-        <v>5721.42</v>
+        <v>5966.42</v>
       </c>
       <c r="H151" s="62">
         <f t="shared" si="20"/>
@@ -18576,19 +18576,19 @@
       </c>
       <c r="D152" s="61">
         <f t="shared" si="16"/>
-        <v>2962.3500000000004</v>
+        <v>3031.7250000000004</v>
       </c>
       <c r="E152" s="61">
         <f t="shared" si="17"/>
-        <v>4067.92</v>
+        <v>4205.42</v>
       </c>
       <c r="F152" s="61">
         <f t="shared" si="18"/>
-        <v>5121.71</v>
+        <v>5326.085</v>
       </c>
       <c r="G152" s="61">
         <f t="shared" si="19"/>
-        <v>6123.72</v>
+        <v>6393.72</v>
       </c>
       <c r="H152" s="61">
         <f t="shared" si="20"/>
@@ -18631,19 +18631,19 @@
       </c>
       <c r="D153" s="62">
         <f t="shared" si="16"/>
-        <v>3145.7249999999999</v>
+        <v>3221.35</v>
       </c>
       <c r="E153" s="62">
         <f t="shared" si="17"/>
-        <v>4326.9699999999993</v>
+        <v>4476.9699999999993</v>
       </c>
       <c r="F153" s="62">
         <f t="shared" si="18"/>
-        <v>5453.7350000000006</v>
+        <v>5676.8600000000006</v>
       </c>
       <c r="G153" s="62">
         <f t="shared" si="19"/>
-        <v>6526.0199999999995</v>
+        <v>6821.0199999999995</v>
       </c>
       <c r="H153" s="62">
         <f t="shared" si="20"/>
@@ -18686,19 +18686,19 @@
       </c>
       <c r="D154" s="61">
         <f t="shared" si="16"/>
-        <v>3329.1</v>
+        <v>3410.9749999999999</v>
       </c>
       <c r="E154" s="61">
         <f t="shared" si="17"/>
-        <v>4586.0200000000004</v>
+        <v>4748.5200000000004</v>
       </c>
       <c r="F154" s="61">
         <f t="shared" si="18"/>
-        <v>5785.76</v>
+        <v>6027.6350000000002</v>
       </c>
       <c r="G154" s="61">
         <f t="shared" si="19"/>
-        <v>6928.3200000000006</v>
+        <v>7248.3200000000006</v>
       </c>
       <c r="H154" s="61">
         <f t="shared" si="20"/>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="J165" s="65">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R165)+(INDEX(Parameters!$J$13:$N$13,1,R165+1)-INDEX(Parameters!$J$13:$N$13,1,R165))*U165,INDEX(Parameters!$D$13:$H$13,1,R165)+(INDEX(Parameters!$D$13:$H$13,1,R165+1)-INDEX(Parameters!$D$13:$H$13,1,R165))*U165)</f>
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="K165" s="65">
         <f>IF(Calculator!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R165)+(INDEX(Parameters!$D$14:$H$14,1,R165+1)-INDEX(Parameters!$D$14:$H$14,1,R165))*U165)</f>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="L165" s="65">
         <f>I165+J165</f>
-        <v>5181</v>
+        <v>5431</v>
       </c>
       <c r="M165" s="65">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>

--- a/docs/damping_curve_RAx0.xlsx
+++ b/docs/damping_curve_RAx0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5E3E38-4988-43EA-892E-45DB66BE9244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F77BA3-477A-4059-89CD-E9A2C90E6739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="LSR Sweep" sheetId="3" r:id="rId5"/>
     <sheet name="Full Sweep" sheetId="4" r:id="rId6"/>
     <sheet name="Parameters" sheetId="5" r:id="rId7"/>
-    <sheet name="Samples" sheetId="7" r:id="rId8"/>
+    <sheet name="Locale" sheetId="9" state="hidden" r:id="rId8"/>
+    <sheet name="Samples" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Catalog!$B$2:$G$18</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="272">
   <si>
     <t>Valving</t>
   </si>
@@ -51,12 +52,6 @@
     <t>Type-A</t>
   </si>
   <si>
-    <t>固定 HSC</t>
-  </si>
-  <si>
-    <t>固定 LSC</t>
-  </si>
-  <si>
     <t>Type-B</t>
   </si>
   <si>
@@ -90,9 +85,6 @@
     <t>倍率</t>
   </si>
   <si>
-    <t>rebound</t>
-  </si>
-  <si>
     <t>Rebound knee</t>
   </si>
   <si>
@@ -177,12 +169,6 @@
     <t>LSR 区间位置</t>
   </si>
   <si>
-    <t>第一 knee</t>
-  </si>
-  <si>
-    <t>第二 knee</t>
-  </si>
-  <si>
     <t>CTM Racing · RAx0 · Damping Calculator</t>
   </si>
   <si>
@@ -195,15 +181,9 @@
     <t>CTM Racing · RAx0 · Valving Parameters</t>
   </si>
   <si>
-    <t>HSbump · 高速增量</t>
-  </si>
-  <si>
     <t>LSR · R（RA60）</t>
   </si>
   <si>
-    <t>Adjusters · 调节格数</t>
-  </si>
-  <si>
     <t>LSC · 全系列</t>
   </si>
   <si>
@@ -255,12 +235,6 @@
     <t>HBS</t>
   </si>
   <si>
-    <t>可调 · 16 clicks</t>
-  </si>
-  <si>
-    <t>可调 · 8 clicks</t>
-  </si>
-  <si>
     <t>HRS</t>
   </si>
   <si>
@@ -271,62 +245,12 @@
   </si>
   <si>
     <t>DSV</t>
-  </si>
-  <si>
-    <t>Rallycross</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>低速压缩 · c</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>高速压缩 · C</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>回弹 · R</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF283C50"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF283C50"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RA</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>活塞行程</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>有</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CTM Racing · RA · Damper Catalog</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>190 mm</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -338,9 +262,6 @@
     <t>黄色单元格为手动输入。</t>
   </si>
   <si>
-    <t>Sweep 使用 8 系 C、40 格 R。</t>
-  </si>
-  <si>
     <t>HSC · 8 系</t>
   </si>
   <si>
@@ -369,6 +290,580 @@
   </si>
   <si>
     <t>Type-A</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Language / 语言</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>chart.rax0CompressionRebound</t>
+  </si>
+  <si>
+    <t>RAx0 · Compression (+) / Rebound (−)</t>
+  </si>
+  <si>
+    <t>RAx0 · 压缩 (+) / 回弹 (−)</t>
+  </si>
+  <si>
+    <t>chart.rax0HscSweep</t>
+  </si>
+  <si>
+    <t>RAx0 · HSC Sweep</t>
+  </si>
+  <si>
+    <t>RAx0 · 高速压缩调节曲线</t>
+  </si>
+  <si>
+    <t>chart.rax0LscSweep</t>
+  </si>
+  <si>
+    <t>RAx0 · LSC Sweep</t>
+  </si>
+  <si>
+    <t>RAx0 · 低速压缩调节曲线</t>
+  </si>
+  <si>
+    <t>chart.rax0LsrSweep</t>
+  </si>
+  <si>
+    <t>RAx0 · LSR Sweep</t>
+  </si>
+  <si>
+    <t>RAx0 · 低速回弹调节曲线</t>
+  </si>
+  <si>
+    <t>label.adjustableEightClicks</t>
+  </si>
+  <si>
+    <t>Adjustable · 8 clicks</t>
+  </si>
+  <si>
+    <t>可调 · 8 格</t>
+  </si>
+  <si>
+    <t>label.adjustableSixteenClicks</t>
+  </si>
+  <si>
+    <t>Adjustable · 16 clicks</t>
+  </si>
+  <si>
+    <t>可调 · 16 格</t>
+  </si>
+  <si>
+    <t>label.adjusterClicks</t>
+  </si>
+  <si>
+    <t>Adjusters · Clicks</t>
+  </si>
+  <si>
+    <t>调节格数</t>
+  </si>
+  <si>
+    <t>label.adjusterPosition</t>
+  </si>
+  <si>
+    <t>Adjuster position</t>
+  </si>
+  <si>
+    <t>label.available</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>label.availableTrailingSpace</t>
+  </si>
+  <si>
+    <t>label.bump2Multiplier</t>
+  </si>
+  <si>
+    <t>bump2 multiplier</t>
+  </si>
+  <si>
+    <t>label.bumpDampingForceN</t>
+  </si>
+  <si>
+    <t>Bump damping force (N)</t>
+  </si>
+  <si>
+    <t>压缩阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.cTotalClicks</t>
+  </si>
+  <si>
+    <t>c total clicks</t>
+  </si>
+  <si>
+    <t>label.calculator</t>
+  </si>
+  <si>
+    <t>计算器</t>
+  </si>
+  <si>
+    <t>label.clicks</t>
+  </si>
+  <si>
+    <t>clicks</t>
+  </si>
+  <si>
+    <t>label.compressionForceN</t>
+  </si>
+  <si>
+    <t>Compression force (N)</t>
+  </si>
+  <si>
+    <t>label.curve</t>
+  </si>
+  <si>
+    <t>Curve</t>
+  </si>
+  <si>
+    <t>label.damperModel</t>
+  </si>
+  <si>
+    <t>Damper model</t>
+  </si>
+  <si>
+    <t>label.dampingAdjustment</t>
+  </si>
+  <si>
+    <t>Damping adjustment</t>
+  </si>
+  <si>
+    <t>label.dampingForceN</t>
+  </si>
+  <si>
+    <t>Damping force (N)</t>
+  </si>
+  <si>
+    <t>阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.extensionSpeed</t>
+  </si>
+  <si>
+    <t>Extension speed (m/s)</t>
+  </si>
+  <si>
+    <t>伸展速度 (m/s)</t>
+  </si>
+  <si>
+    <t>label.firstKnee</t>
+  </si>
+  <si>
+    <t>First knee</t>
+  </si>
+  <si>
+    <t>第一拐点</t>
+  </si>
+  <si>
+    <t>label.fixedHsc</t>
+  </si>
+  <si>
+    <t>Fixed HSC</t>
+  </si>
+  <si>
+    <t>固定高速压缩</t>
+  </si>
+  <si>
+    <t>label.fixedLsc</t>
+  </si>
+  <si>
+    <t>Fixed LSC</t>
+  </si>
+  <si>
+    <t>固定低速压缩</t>
+  </si>
+  <si>
+    <t>label.fullSweep</t>
+  </si>
+  <si>
+    <t>全范围扫描</t>
+  </si>
+  <si>
+    <t>label.highSpeedBumpIncrement</t>
+  </si>
+  <si>
+    <t>HSbump · High-speed increment</t>
+  </si>
+  <si>
+    <t>label.highSpeedCompressionC</t>
+  </si>
+  <si>
+    <t>High-speed compression · C</t>
+  </si>
+  <si>
+    <t>高速压缩 · C</t>
+  </si>
+  <si>
+    <t>label.hscEightSeries</t>
+  </si>
+  <si>
+    <t>HSC · 8 series</t>
+  </si>
+  <si>
+    <t>label.hscRange</t>
+  </si>
+  <si>
+    <t>HSC range</t>
+  </si>
+  <si>
+    <t>label.hscRangePosition</t>
+  </si>
+  <si>
+    <t>HSC range position</t>
+  </si>
+  <si>
+    <t>label.hscSixSeries</t>
+  </si>
+  <si>
+    <t>HSC · 6 series</t>
+  </si>
+  <si>
+    <t>label.hscSweep</t>
+  </si>
+  <si>
+    <t>HSC 扫描</t>
+  </si>
+  <si>
+    <t>label.hscTotalClicks</t>
+  </si>
+  <si>
+    <t>C total clicks</t>
+  </si>
+  <si>
+    <t>label.hsrMultiplier</t>
+  </si>
+  <si>
+    <t>HSR multiplier</t>
+  </si>
+  <si>
+    <t>label.inputCheck</t>
+  </si>
+  <si>
+    <t>Input check</t>
+  </si>
+  <si>
+    <t>label.lowSpeedCompressionC</t>
+  </si>
+  <si>
+    <t>Low-speed compression · c</t>
+  </si>
+  <si>
+    <t>低速压缩 · c</t>
+  </si>
+  <si>
+    <t>label.lscAllSeries</t>
+  </si>
+  <si>
+    <t>LSC · All series</t>
+  </si>
+  <si>
+    <t>label.lscRange</t>
+  </si>
+  <si>
+    <t>LSC range</t>
+  </si>
+  <si>
+    <t>label.lscRangePosition</t>
+  </si>
+  <si>
+    <t>LSC range position</t>
+  </si>
+  <si>
+    <t>label.lscSweep</t>
+  </si>
+  <si>
+    <t>LSC 扫描</t>
+  </si>
+  <si>
+    <t>label.lsrRa60EightVariant</t>
+  </si>
+  <si>
+    <t>LSR · RA60 / 8-series variant</t>
+  </si>
+  <si>
+    <t>label.lsrRange</t>
+  </si>
+  <si>
+    <t>LSR range</t>
+  </si>
+  <si>
+    <t>label.lsrRangePosition</t>
+  </si>
+  <si>
+    <t>LSR range position</t>
+  </si>
+  <si>
+    <t>label.lsrSweep</t>
+  </si>
+  <si>
+    <t>LSR 扫描</t>
+  </si>
+  <si>
+    <t>label.lsrTotalClicks</t>
+  </si>
+  <si>
+    <t>R total clicks</t>
+  </si>
+  <si>
+    <t>label.multiplier</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>label.pistonTravel</t>
+  </si>
+  <si>
+    <t>Piston travel</t>
+  </si>
+  <si>
+    <t>活塞行程</t>
+  </si>
+  <si>
+    <t>label.rally</t>
+  </si>
+  <si>
+    <t>拉力</t>
+  </si>
+  <si>
+    <t>label.rallycross</t>
+  </si>
+  <si>
+    <t>Rallycross</t>
+  </si>
+  <si>
+    <t>跨界拉力</t>
+  </si>
+  <si>
+    <t>label.ratio</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>label.rebound</t>
+  </si>
+  <si>
+    <t>Rebound</t>
+  </si>
+  <si>
+    <t>回弹</t>
+  </si>
+  <si>
+    <t>label.reboundDampingForceN</t>
+  </si>
+  <si>
+    <t>Rebound damping force (N)</t>
+  </si>
+  <si>
+    <t>回弹阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.reboundForceN</t>
+  </si>
+  <si>
+    <t>Rebound force (N)</t>
+  </si>
+  <si>
+    <t>label.reboundKnee</t>
+  </si>
+  <si>
+    <t>回弹拐点</t>
+  </si>
+  <si>
+    <t>label.reboundR</t>
+  </si>
+  <si>
+    <t>Rebound · R</t>
+  </si>
+  <si>
+    <t>回弹 · R</t>
+  </si>
+  <si>
+    <t>label.secondKnee</t>
+  </si>
+  <si>
+    <t>Second knee</t>
+  </si>
+  <si>
+    <t>第二拐点</t>
+  </si>
+  <si>
+    <t>label.shaftSpeedMagnitudeMps</t>
+  </si>
+  <si>
+    <t>Shaft speed magnitude (m/s)</t>
+  </si>
+  <si>
+    <t>轴速大小 (m/s)</t>
+  </si>
+  <si>
+    <t>label.shaftSpeedMps</t>
+  </si>
+  <si>
+    <t>Shaft speed (m/s)</t>
+  </si>
+  <si>
+    <t>label.shaftVelocityMps</t>
+  </si>
+  <si>
+    <t>label.specification</t>
+  </si>
+  <si>
+    <t>Specification</t>
+  </si>
+  <si>
+    <t>label.threePlusOneWay</t>
+  </si>
+  <si>
+    <t>3+1 向调节</t>
+  </si>
+  <si>
+    <t>label.threeWay</t>
+  </si>
+  <si>
+    <t>3 向调节</t>
+  </si>
+  <si>
+    <t>label.totalHighSpeedCoefficient</t>
+  </si>
+  <si>
+    <t>Total high-speed coefficient</t>
+  </si>
+  <si>
+    <t>label.totalHsCoefficient</t>
+  </si>
+  <si>
+    <t>Total HS coefficient</t>
+  </si>
+  <si>
+    <t>label.valving</t>
+  </si>
+  <si>
+    <t>阀系</t>
+  </si>
+  <si>
+    <t>note.adjusterClicks</t>
+  </si>
+  <si>
+    <t>0 is the hardest setting; negative values are clicks out.</t>
+  </si>
+  <si>
+    <t>note.baseDampingCurve</t>
+  </si>
+  <si>
+    <t>Continuous piecewise theoretical curve; base damping only.</t>
+  </si>
+  <si>
+    <t>note.sweepEightSeriesClicks</t>
+  </si>
+  <si>
+    <t>Sweep uses 8-series C and 40 R clicks.</t>
+  </si>
+  <si>
+    <t>调节曲线使用 8 系 C、40 格 R。</t>
+  </si>
+  <si>
+    <t>note.yellowInputs</t>
+  </si>
+  <si>
+    <t>Yellow cells are manual inputs.</t>
+  </si>
+  <si>
+    <t>status.checkInput</t>
+  </si>
+  <si>
+    <t>Check input</t>
+  </si>
+  <si>
+    <t>检查输入</t>
+  </si>
+  <si>
+    <t>status.ok</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>title.currentCurveParameters</t>
+  </si>
+  <si>
+    <t>Current curve parameters</t>
+  </si>
+  <si>
+    <t>title.currentDampingForce</t>
+  </si>
+  <si>
+    <t>Current input · damping force magnitude</t>
+  </si>
+  <si>
+    <t>title.raDamperCatalog</t>
+  </si>
+  <si>
+    <t>CTM Racing · RA · Damper Catalog</t>
+  </si>
+  <si>
+    <t>CTM Racing · RA · 避震器目录</t>
+  </si>
+  <si>
+    <t>title.rax0DampingCalculator</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx0 · 阻尼计算器</t>
+  </si>
+  <si>
+    <t>title.rax0FullSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx0 · 全范围扫描</t>
+  </si>
+  <si>
+    <t>title.rax0HSCSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx0 · HSC 扫描</t>
+  </si>
+  <si>
+    <t>title.rax0LSCSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx0 · LSC 扫描</t>
+  </si>
+  <si>
+    <t>title.rax0LSRSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx0 · LSR 扫描</t>
+  </si>
+  <si>
+    <t>title.rax0ValvingParameters</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx0 · 阀系参数</t>
+  </si>
+  <si>
+    <t>简体中文</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -380,7 +875,7 @@
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="82">
+  <fonts count="83">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -471,13 +966,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF667B91"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF283C50"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -919,8 +1407,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="71">
+  <fills count="74">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1272,8 +1773,21 @@
         <fgColor rgb="FFF5F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="72">
+  <borders count="73">
     <border>
       <left/>
       <right/>
@@ -1860,6 +2374,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1867,7 +2388,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1930,185 +2451,187 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="25" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="29" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="28" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="35" fillId="24" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="34" fillId="24" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="37" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="36" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="40" fillId="29" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="39" fillId="29" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="41" fillId="30" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="40" fillId="30" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="47" fillId="36" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="46" fillId="36" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="48" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="47" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="49" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="48" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="50" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="49" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="51" fillId="40" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="50" fillId="40" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="49" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="49" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="50" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="50" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="51" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="51" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="52" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="52" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="53" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="53" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="54" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="54" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="55" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="55" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="56" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="56" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="57" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="57" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="58" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="58" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="59" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="59" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="71" fillId="60" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="70" fillId="60" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="72" fillId="61" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="71" fillId="61" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="62" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="62" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="63" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="63" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="75" fillId="64" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="74" fillId="64" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="76" fillId="65" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="75" fillId="65" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="67" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="67" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="68" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="68" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="71" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="82" fillId="73" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2122,34 +2645,40 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="81" fillId="71" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="81" fillId="72" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="26" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="27" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="66" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="66" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2178,22 +2707,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx0 · LSC Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$4</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx0 · 低速压缩调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2882,22 +3420,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Bump damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>压缩阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -2910,7 +3457,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -2933,22 +3480,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$59</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -2968,7 +3524,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -2991,7 +3547,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -3014,7 +3570,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -3028,22 +3584,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx0 · HSC Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$3</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx0 · 高速压缩调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3722,22 +4287,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Bump damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>压缩阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -3750,7 +4324,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -3773,22 +4347,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$59</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -3808,7 +4391,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -3831,7 +4414,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -3854,7 +4437,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -3868,22 +4451,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx0 · LSR Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$5</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx0 · 低速回弹调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -4562,22 +5154,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Rebound damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$53</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>回弹阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -4590,7 +5191,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -4613,22 +5214,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Extension speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>伸展速度 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -4641,7 +5251,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -4664,7 +5274,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -4687,7 +5297,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -4701,22 +5311,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx0 · Compression (+) / Rebound (−)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx0 · 压缩 (+) / 回弹 (−)</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -6034,22 +6653,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -6062,7 +6690,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -6085,22 +6713,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed magnitude (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$58</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速大小 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -6120,7 +6757,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -6143,7 +6780,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -6166,7 +6803,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -6524,26 +7161,39 @@
     <col min="8" max="8" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="12" customHeight="1">
+    <row r="1" spans="1:8" ht="22" customHeight="1">
       <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="88" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="88" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="88" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="89" t="s">
+        <v>271</v>
+      </c>
+      <c r="F1" s="89" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="89" t="s">
+        <v>82</v>
+      </c>
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" ht="35.15" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
+      <c r="B2" s="85" t="str">
+        <f>VLOOKUP("title.raDamperCatalog",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RA · 避震器目录</v>
+      </c>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -6560,17 +7210,18 @@
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="9" t="s">
-        <v>62</v>
+      <c r="D4" s="9" t="str">
+        <f>VLOOKUP("label.specification",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>规格</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H4" s="6"/>
     </row>
@@ -6578,46 +7229,52 @@
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="19" t="s">
-        <v>82</v>
+      <c r="D5" s="19" t="str">
+        <f>VLOOKUP("label.pistonTravel",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>活塞行程</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="85" t="s">
-        <v>81</v>
+      <c r="B6" s="87" t="s">
+        <v>67</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>68</v>
+      <c r="D6" s="13" t="str">
+        <f>VLOOKUP("label.dampingAdjustment",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阻尼调节</v>
+      </c>
+      <c r="E6" s="14" t="str">
+        <f>VLOOKUP("label.threeWay",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>3 向调节</v>
+      </c>
+      <c r="F6" s="14" t="str">
+        <f>VLOOKUP("label.threePlusOneWay",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>3+1 向调节</v>
+      </c>
+      <c r="G6" s="14" t="str">
+        <f>VLOOKUP("label.threePlusOneWay",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>3+1 向调节</v>
       </c>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="85"/>
+      <c r="B7" s="87"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="19" t="s">
-        <v>77</v>
+      <c r="D7" s="19" t="str">
+        <f>VLOOKUP("label.lowSpeedCompressionC",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>低速压缩 · c</v>
       </c>
       <c r="E7" s="15">
         <v>24</v>
@@ -6632,12 +7289,14 @@
     </row>
     <row r="8" spans="1:8" ht="31" customHeight="1">
       <c r="A8" s="6"/>
-      <c r="B8" s="23" t="s">
-        <v>65</v>
+      <c r="B8" s="23" t="str">
+        <f>VLOOKUP("label.rally",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>拉力</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="18" t="s">
-        <v>78</v>
+      <c r="D8" s="18" t="str">
+        <f>VLOOKUP("label.highSpeedCompressionC",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>高速压缩 · C</v>
       </c>
       <c r="E8" s="16">
         <v>10</v>
@@ -6652,12 +7311,14 @@
     </row>
     <row r="9" spans="1:8" ht="31" customHeight="1">
       <c r="A9" s="6"/>
-      <c r="B9" s="17" t="s">
-        <v>76</v>
+      <c r="B9" s="17" t="str">
+        <f>VLOOKUP("label.rallycross",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>跨界拉力</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="19" t="s">
-        <v>79</v>
+      <c r="D9" s="19" t="str">
+        <f>VLOOKUP("label.reboundR",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹 · R</v>
       </c>
       <c r="E9" s="15">
         <v>40</v>
@@ -6675,14 +7336,16 @@
       <c r="B10" s="8"/>
       <c r="C10" s="6"/>
       <c r="D10" s="13" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E10" s="20"/>
-      <c r="F10" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>71</v>
+      <c r="F10" s="14" t="str">
+        <f>VLOOKUP("label.adjustableSixteenClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>可调 · 16 格</v>
+      </c>
+      <c r="G10" s="14" t="str">
+        <f>VLOOKUP("label.adjustableEightClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>可调 · 8 格</v>
       </c>
       <c r="H10" s="6"/>
     </row>
@@ -6691,11 +7354,12 @@
       <c r="B11" s="8"/>
       <c r="C11" s="6"/>
       <c r="D11" s="12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E11" s="21"/>
-      <c r="F11" s="22" t="s">
-        <v>83</v>
+      <c r="F11" s="22" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="6"/>
@@ -6705,16 +7369,19 @@
       <c r="B12" s="8"/>
       <c r="C12" s="6"/>
       <c r="D12" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>74</v>
+        <v>64</v>
+      </c>
+      <c r="E12" s="14" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
+      </c>
+      <c r="F12" s="14" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
+      </c>
+      <c r="G12" s="14" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -6723,11 +7390,12 @@
       <c r="B13" s="8"/>
       <c r="C13" s="6"/>
       <c r="D13" s="12" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E13" s="21"/>
-      <c r="F13" s="22" t="s">
-        <v>80</v>
+      <c r="F13" s="22" t="str">
+        <f>VLOOKUP("label.availableTrailingSpace",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="6"/>
@@ -6746,20 +7414,20 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
@@ -6767,19 +7435,19 @@
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="82"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="25" customHeight="1">
@@ -6813,7 +7481,9 @@
       <c r="H21" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="B2:G2"/>
@@ -6822,8 +7492,13 @@
     <mergeCell ref="D16:G16"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"English,简体中文"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6861,20 +7536,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax0DampingCalculator",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx0 · 阻尼计算器</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -6897,22 +7573,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="25" t="s">
-        <v>0</v>
+      <c r="B4" s="25" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6935,21 +7612,23 @@
     </row>
     <row r="6" spans="1:15" ht="32.15" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="27" t="s">
-        <v>59</v>
+      <c r="B6" s="27" t="str">
+        <f>VLOOKUP("label.damperModel",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>避震器型号</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="75" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
+      <c r="F6" s="74" t="str">
+        <f>VLOOKUP("title.currentDampingForce",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>当前输入 · 阻尼力大小</v>
+      </c>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6959,7 +7638,7 @@
     <row r="7" spans="1:15" ht="28" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="29">
         <v>-12</v>
@@ -6980,23 +7659,24 @@
     <row r="8" spans="1:15" ht="28" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="29">
         <v>-5</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="90">
-        <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
+      <c r="F8" s="1" t="str">
+        <f>VLOOKUP("label.compressionForceN",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>压缩力 (N)</v>
+      </c>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="91">
+        <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$81,4,FALSE),Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),VLOOKUP("status.checkInput",Locale!$A$2:$D$81,4,FALSE))</f>
         <v>1761.47</v>
       </c>
-      <c r="J8" s="91"/>
+      <c r="J8" s="92"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -7006,7 +7686,7 @@
     <row r="9" spans="1:15" ht="28" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="28" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="29">
         <v>-20</v>
@@ -7026,24 +7706,26 @@
     </row>
     <row r="10" spans="1:15" ht="28" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="27" t="s">
-        <v>21</v>
+      <c r="B10" s="27" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C10" s="30">
         <v>0.45</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="90">
-        <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
+      <c r="F10" s="1" t="str">
+        <f>VLOOKUP("label.reboundForceN",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹力 (N)</v>
+      </c>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="91">
+        <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$81,4,FALSE),Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),VLOOKUP("status.checkInput",Locale!$A$2:$D$81,4,FALSE))</f>
         <v>1519.2</v>
       </c>
-      <c r="J10" s="91"/>
+      <c r="J10" s="92"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -7086,8 +7768,9 @@
     </row>
     <row r="13" spans="1:15" ht="32.15" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="27" t="s">
-        <v>23</v>
+      <c r="B13" s="27" t="str">
+        <f>VLOOKUP("label.cTotalClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>c 总格数</v>
       </c>
       <c r="C13" s="31">
         <f>Parameters!D23</f>
@@ -7095,13 +7778,14 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
+      <c r="F13" s="74" t="str">
+        <f>VLOOKUP("title.currentCurveParameters",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>当前曲线参数</v>
+      </c>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -7110,8 +7794,9 @@
     </row>
     <row r="14" spans="1:15" ht="28" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="32" t="s">
-        <v>24</v>
+      <c r="B14" s="32" t="str">
+        <f>VLOOKUP("label.hscTotalClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>C 总格数</v>
       </c>
       <c r="C14" s="33">
         <f>IF(C6="RA60",Parameters!D27,Parameters!D24)</f>
@@ -7119,17 +7804,17 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
+      <c r="F14" s="93" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
       <c r="I14" s="34">
         <f>Samples!F165</f>
         <v>3650</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -7139,8 +7824,9 @@
     </row>
     <row r="15" spans="1:15" ht="28" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="27" t="s">
-        <v>25</v>
+      <c r="B15" s="27" t="str">
+        <f>VLOOKUP("label.lsrTotalClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>R 总格数</v>
       </c>
       <c r="C15" s="31">
         <f>IF(C6="RA80",Parameters!D26,Parameters!D25)</f>
@@ -7148,17 +7834,17 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="70"/>
-      <c r="H15" s="70"/>
+      <c r="F15" s="77" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="35">
         <f>Samples!I165</f>
         <v>3431</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -7172,17 +7858,18 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="76" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="F16" s="75" t="str">
+        <f>VLOOKUP("label.highSpeedBumpIncrement",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSbump · 高速增量</v>
+      </c>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
       <c r="I16" s="34">
         <f>Samples!J165</f>
         <v>2000</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -7196,17 +7883,18 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
+      <c r="F17" s="1" t="str">
+        <f>VLOOKUP("label.totalHighSpeedCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总高速系数</v>
+      </c>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
       <c r="I17" s="35">
         <f>Samples!L165</f>
         <v>5431</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -7216,12 +7904,13 @@
     </row>
     <row r="18" spans="1:15" ht="28" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="27" t="s">
-        <v>28</v>
+      <c r="B18" s="27" t="str">
+        <f>VLOOKUP("label.inputCheck",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>输入检查</v>
       </c>
       <c r="C18" s="36" t="str">
-        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="RA60",C6="RA80",C6="RA80/2"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),"OK","检查输入")</f>
-        <v>OK</v>
+        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="RA60",C6="RA80",C6="RA80/2"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),VLOOKUP("status.ok",Locale!$A$2:$D$81,4,FALSE),VLOOKUP("status.checkInput",Locale!$A$2:$D$81,4,FALSE))</f>
+        <v>正常</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -7242,17 +7931,18 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="88" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
+      <c r="F19" s="93" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="G19" s="76"/>
+      <c r="H19" s="76"/>
       <c r="I19" s="34">
         <f>Samples!M165</f>
         <v>3600</v>
       </c>
       <c r="J19" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -7266,17 +7956,17 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
+      <c r="F20" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
       <c r="I20" s="35">
         <f>Samples!P165</f>
         <v>3096</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -7307,17 +7997,18 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="76" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
+      <c r="F22" s="75" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
       <c r="I22" s="37">
         <f>Samples!G165</f>
         <v>0.08</v>
       </c>
       <c r="J22" s="25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -7331,17 +8022,18 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="70"/>
-      <c r="H23" s="70"/>
+      <c r="F23" s="1" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
       <c r="I23" s="38">
         <f>Samples!K165</f>
         <v>0.35</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -7355,17 +8047,18 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
+      <c r="F24" s="93" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
       <c r="I24" s="37">
         <f>Samples!N165</f>
         <v>0.25</v>
       </c>
       <c r="J24" s="25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -7409,20 +8102,21 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="86" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
+      <c r="B27" s="94" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -7683,6 +8377,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -7690,17 +8395,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -7723,6 +8417,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7757,20 +8452,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax0LSCSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx0 · LSC 扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -7793,22 +8489,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="25" t="s">
-        <v>0</v>
+      <c r="B4" s="25" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7831,8 +8528,9 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="27" t="s">
-        <v>2</v>
+      <c r="B6" s="27" t="str">
+        <f>VLOOKUP("label.fixedHsc",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>固定高速压缩</v>
       </c>
       <c r="C6" s="29">
         <v>-10</v>
@@ -8430,18 +9128,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
-      <c r="M41" s="92"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8480,7 +9178,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -8515,20 +9214,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax0HSCSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx0 · HSC 扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -8551,22 +9251,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="25" t="s">
-        <v>0</v>
+      <c r="B4" s="25" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8589,8 +9290,9 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="27" t="s">
-        <v>3</v>
+      <c r="B6" s="27" t="str">
+        <f>VLOOKUP("label.fixedLsc",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>固定低速压缩</v>
       </c>
       <c r="C6" s="29">
         <v>-12</v>
@@ -9188,18 +9890,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
-      <c r="M41" s="92"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9238,7 +9940,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9273,20 +9976,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax0LSRSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx0 · LSR 扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -9309,22 +10013,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="25" t="s">
-        <v>0</v>
+      <c r="B4" s="25" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9942,18 +10647,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
-      <c r="M41" s="92"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9988,7 +10693,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10023,20 +10729,21 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax0FullSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx0 · 全范围扫描</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
       <c r="N2" s="24"/>
       <c r="O2" s="1"/>
     </row>
@@ -10059,22 +10766,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="25" t="s">
-        <v>0</v>
+      <c r="B4" s="25" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10692,18 +11400,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="92"/>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
-      <c r="M41" s="92"/>
+      <c r="B41" s="96"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10738,7 +11446,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10777,40 +11486,42 @@
     </row>
     <row r="2" spans="1:15" ht="35.15" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax0ValvingParameters",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx0 · 阀系参数</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="73"/>
+      <c r="B3" s="71" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -10834,30 +11545,32 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
+      <c r="J5" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>6</v>
+      <c r="B6" s="39" t="str">
+        <f>VLOOKUP("label.adjusterPosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>调节位置</v>
+      </c>
+      <c r="C6" s="39" t="str">
+        <f>VLOOKUP("label.ratio",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>比例</v>
       </c>
       <c r="D6" s="40">
         <v>0</v>
@@ -10900,10 +11613,11 @@
     <row r="7" spans="1:15" ht="29.15" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="27" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D7" s="31">
         <f>(D$6-1)*$D$23</f>
@@ -10951,10 +11665,11 @@
     <row r="8" spans="1:15" ht="29.15" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="C8" s="32" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D8" s="33">
         <f>(D$6-1)*$D$24</f>
@@ -11019,10 +11734,10 @@
     <row r="10" spans="1:15" ht="29.15" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="29">
         <v>1850</v>
@@ -11063,11 +11778,12 @@
     </row>
     <row r="11" spans="1:15" ht="29.15" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="32" t="s">
-        <v>44</v>
+      <c r="B11" s="32" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="42">
         <v>0.08</v>
@@ -11109,10 +11825,11 @@
     <row r="12" spans="1:15" ht="29.15" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="C12" s="27" t="str">
+        <f>VLOOKUP("label.multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>倍率</v>
       </c>
       <c r="D12" s="42">
         <v>1</v>
@@ -11153,11 +11870,12 @@
     </row>
     <row r="13" spans="1:15" ht="29.15" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="32" t="s">
-        <v>50</v>
+      <c r="B13" s="32" t="str">
+        <f>VLOOKUP("label.highSpeedBumpIncrement",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSbump · 高速增量</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="29">
         <v>250</v>
@@ -11196,11 +11914,12 @@
     </row>
     <row r="14" spans="1:15" ht="29.15" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="27" t="s">
-        <v>45</v>
+      <c r="B14" s="27" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="42">
         <v>0.34</v>
@@ -11259,10 +11978,11 @@
     <row r="16" spans="1:15" ht="30" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="C16" s="39" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D16" s="45">
         <f>(D$6-1)*$D$25</f>
@@ -11309,11 +12029,12 @@
     </row>
     <row r="17" spans="1:15" ht="29.15" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="25" t="s">
-        <v>15</v>
+      <c r="B17" s="25" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="29">
         <v>2100</v>
@@ -11354,11 +12075,12 @@
     </row>
     <row r="18" spans="1:15" ht="29.15" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="28" t="s">
-        <v>16</v>
+      <c r="B18" s="28" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" s="42">
         <v>0.23</v>
@@ -11400,10 +12122,11 @@
     <row r="19" spans="1:15" ht="29.15" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="27" t="s">
         <v>14</v>
+      </c>
+      <c r="C19" s="27" t="str">
+        <f>VLOOKUP("label.multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>倍率</v>
       </c>
       <c r="D19" s="42">
         <v>0.92</v>
@@ -11478,73 +12201,78 @@
     </row>
     <row r="22" spans="1:15" ht="32.15" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="75" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
+      <c r="B22" s="74" t="str">
+        <f>VLOOKUP("label.adjusterClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>调节格数</v>
+      </c>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29.15" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="77"/>
+      <c r="B23" s="75" t="str">
+        <f>VLOOKUP("label.lscAllSeries",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC · 全系列</v>
+      </c>
+      <c r="C23" s="76"/>
       <c r="D23" s="31">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="80"/>
-      <c r="J23" s="80"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="80"/>
-      <c r="M23" s="80"/>
-      <c r="N23" s="80"/>
+      <c r="F23" s="78" t="str">
+        <f>VLOOKUP("note.sweepEightSeriesClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>调节曲线使用 8 系 C、40 格 R。</v>
+      </c>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="79"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29.15" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="70"/>
+      <c r="B24" s="1" t="str">
+        <f>VLOOKUP("label.hscEightSeries",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC · 8 系</v>
+      </c>
+      <c r="C24" s="69"/>
       <c r="D24" s="33">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29.15" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="76" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="77"/>
+      <c r="B25" s="75" t="str">
+        <f>VLOOKUP("label.lsrRa60EightVariant",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR · RA60 / 8系改型</v>
+      </c>
+      <c r="C25" s="76"/>
       <c r="D25" s="31">
         <v>40</v>
       </c>
@@ -11562,33 +12290,35 @@
     </row>
     <row r="26" spans="1:15" ht="29.15" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="78" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="70"/>
+      <c r="B26" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="69"/>
       <c r="D26" s="33">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="73"/>
+      <c r="F26" s="80" t="str">
+        <f>VLOOKUP("note.adjusterClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>0 为最硬，负数为退出格数。</v>
+      </c>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="70"/>
+      <c r="B27" s="1" t="str">
+        <f>VLOOKUP("label.hscSixSeries",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC · 6 系</v>
+      </c>
+      <c r="C27" s="69"/>
       <c r="D27" s="33">
         <v>10</v>
       </c>
@@ -11606,21 +12336,22 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="68"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="68"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="68"/>
-      <c r="N28" s="68"/>
+      <c r="B28" s="81" t="str">
+        <f>VLOOKUP("note.baseDampingCurve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>连续分段理论曲线，仅基础阻尼。</v>
+      </c>
+      <c r="C28" s="82"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="82"/>
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="82"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
@@ -11642,19 +12373,19 @@
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="69"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
+      <c r="J30" s="83"/>
+      <c r="K30" s="83"/>
+      <c r="L30" s="83"/>
+      <c r="M30" s="83"/>
+      <c r="N30" s="83"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
@@ -11846,6 +12577,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -11858,21 +12597,1239 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B2,C2)</f>
+        <v>RAx0 · 压缩 (+) / 回弹 (−)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B3,C3)</f>
+        <v>RAx0 · 高速压缩调节曲线</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B4,C4)</f>
+        <v>RAx0 · 低速压缩调节曲线</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="67" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B5,C5)</f>
+        <v>RAx0 · 低速回弹调节曲线</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B6,C6)</f>
+        <v>可调 · 8 格</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B7,C7)</f>
+        <v>可调 · 16 格</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B8,C8)</f>
+        <v>调节格数</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B9,C9)</f>
+        <v>调节位置</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="67" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B10,C10)</f>
+        <v>有</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B11,C11)</f>
+        <v>有</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B12,C12)</f>
+        <v>bump2 倍率</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B13,C13)</f>
+        <v>压缩阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B14,C14)</f>
+        <v>c 总格数</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="67" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B15,C15)</f>
+        <v>计算器</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B16,C16)</f>
+        <v>格</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B17,C17)</f>
+        <v>压缩力 (N)</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B18,C18)</f>
+        <v>曲线</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B19,C19)</f>
+        <v>避震器型号</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B20,C20)</f>
+        <v>阻尼调节</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B21,C21)</f>
+        <v>阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B22,C22)</f>
+        <v>伸展速度 (m/s)</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="67" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B23,C23)</f>
+        <v>第一拐点</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="67" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B24,C24)</f>
+        <v>固定高速压缩</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="D25" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B25,C25)</f>
+        <v>固定低速压缩</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B26,C26)</f>
+        <v>全范围扫描</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B27,C27)</f>
+        <v>HSbump · 高速增量</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B28,C28)</f>
+        <v>高速压缩 · C</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B29,C29)</f>
+        <v>HSC · 8 系</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="67" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B30,C30)</f>
+        <v>HSC 区间</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B31,C31)</f>
+        <v>HSC 区间位置</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B32,C32)</f>
+        <v>HSC · 6 系</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B33,C33)</f>
+        <v>HSC 扫描</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B34,C34)</f>
+        <v>C 总格数</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B35,C35)</f>
+        <v>HSR 倍率</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B36,C36)</f>
+        <v>输入检查</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" s="67" t="s">
+        <v>172</v>
+      </c>
+      <c r="D37" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B37,C37)</f>
+        <v>低速压缩 · c</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="67" t="s">
+        <v>173</v>
+      </c>
+      <c r="B38" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B38,C38)</f>
+        <v>LSC · 全系列</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="67" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B39,C39)</f>
+        <v>LSC 区间</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B40,C40)</f>
+        <v>LSC 区间位置</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="67" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B41,C41)</f>
+        <v>LSC 扫描</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="67" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B42,C42)</f>
+        <v>LSR · RA60 / 8系改型</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="C43" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B43,C43)</f>
+        <v>LSR 区间</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="67" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" s="67" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B44,C44)</f>
+        <v>LSR 区间位置</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="D45" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B45,C45)</f>
+        <v>LSR 扫描</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B46" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B46,C46)</f>
+        <v>R 总格数</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="B47" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="C47" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B47,C47)</f>
+        <v>倍率</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="B48" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="C48" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="D48" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B48,C48)</f>
+        <v>活塞行程</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="67" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B49,C49)</f>
+        <v>拉力</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="B50" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="C50" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D50" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B50,C50)</f>
+        <v>跨界拉力</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="B51" s="67" t="s">
+        <v>202</v>
+      </c>
+      <c r="C51" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B51,C51)</f>
+        <v>比例</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="C52" s="67" t="s">
+        <v>205</v>
+      </c>
+      <c r="D52" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B52,C52)</f>
+        <v>回弹</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" s="67" t="s">
+        <v>207</v>
+      </c>
+      <c r="C53" s="67" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B53,C53)</f>
+        <v>回弹阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="67" t="s">
+        <v>209</v>
+      </c>
+      <c r="B54" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="C54" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B54,C54)</f>
+        <v>回弹力 (N)</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="B55" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="67" t="s">
+        <v>212</v>
+      </c>
+      <c r="D55" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B55,C55)</f>
+        <v>回弹拐点</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="C56" s="67" t="s">
+        <v>215</v>
+      </c>
+      <c r="D56" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B56,C56)</f>
+        <v>回弹 · R</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="67" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" s="67" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B57,C57)</f>
+        <v>第二拐点</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="67" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" s="67" t="s">
+        <v>221</v>
+      </c>
+      <c r="D58" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B58,C58)</f>
+        <v>轴速大小 (m/s)</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B59,C59)</f>
+        <v>轴速 (m/s)</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="C60" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B60,C60)</f>
+        <v>轴速 (m/s)</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B61,C61)</f>
+        <v>规格</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="67" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="D62" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B62,C62)</f>
+        <v>3+1 向调节</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="C63" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="D63" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B63,C63)</f>
+        <v>3 向调节</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="67" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B64,C64)</f>
+        <v>总高速系数</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="67" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" s="67" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="67" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B65,C65)</f>
+        <v>总 HS 系数</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="D66" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B66,C66)</f>
+        <v>阀系</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="B67" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="C67" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B67,C67)</f>
+        <v>0 为最硬，负数为退出格数。</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" s="67" t="s">
+        <v>240</v>
+      </c>
+      <c r="C68" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="D68" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B68,C68)</f>
+        <v>连续分段理论曲线，仅基础阻尼。</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="67" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="D69" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B69,C69)</f>
+        <v>调节曲线使用 8 系 C、40 格 R。</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="67" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" s="67" t="s">
+        <v>245</v>
+      </c>
+      <c r="C70" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B70,C70)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="67" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="D71" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B71,C71)</f>
+        <v>检查输入</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="B72" s="67" t="s">
+        <v>250</v>
+      </c>
+      <c r="C72" s="67" t="s">
+        <v>251</v>
+      </c>
+      <c r="D72" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B72,C72)</f>
+        <v>正常</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B73" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="C73" s="67" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B73,C73)</f>
+        <v>当前曲线参数</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="67" t="s">
+        <v>254</v>
+      </c>
+      <c r="B74" s="67" t="s">
+        <v>255</v>
+      </c>
+      <c r="C74" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B74,C74)</f>
+        <v>当前输入 · 阻尼力大小</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="67" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" s="67" t="s">
+        <v>257</v>
+      </c>
+      <c r="C75" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="D75" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B75,C75)</f>
+        <v>CTM Racing · RA · 避震器目录</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="67" t="s">
+        <v>259</v>
+      </c>
+      <c r="B76" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="67" t="s">
+        <v>260</v>
+      </c>
+      <c r="D76" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B76,C76)</f>
+        <v>CTM Racing · RAx0 · 阻尼计算器</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="B77" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="D77" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B77,C77)</f>
+        <v>CTM Racing · RAx0 · 全范围扫描</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="67" t="s">
+        <v>263</v>
+      </c>
+      <c r="B78" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="67" t="s">
+        <v>264</v>
+      </c>
+      <c r="D78" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B78,C78)</f>
+        <v>CTM Racing · RAx0 · HSC 扫描</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="67" t="s">
+        <v>265</v>
+      </c>
+      <c r="B79" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="D79" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B79,C79)</f>
+        <v>CTM Racing · RAx0 · LSC 扫描</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="67" t="s">
+        <v>267</v>
+      </c>
+      <c r="B80" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" s="67" t="s">
+        <v>268</v>
+      </c>
+      <c r="D80" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B80,C80)</f>
+        <v>CTM Racing · RAx0 · LSR 扫描</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="67" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81" s="67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="67" t="s">
+        <v>270</v>
+      </c>
+      <c r="D81" s="67" t="str">
+        <f>IF(Catalog!$E$1="English",B81,C81)</f>
+        <v>CTM Racing · RAx0 · 阀系参数</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC59FAD-AB32-47AD-9D8F-634AD654D5A0}">
   <sheetPr>
     <tabColor rgb="FF93A0AC"/>
@@ -11887,29 +13844,30 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32.15" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="93" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
+      <c r="B1" s="97" t="str">
+        <f>VLOOKUP("label.lscSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 扫描</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
@@ -11961,68 +13919,82 @@
     </row>
     <row r="4" spans="1:22" ht="44.15" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="47" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="48" t="s">
+      <c r="F4" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="47" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H4" s="47" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I4" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="48" t="s">
+      <c r="K4" s="47" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L4" s="47" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M4" s="48" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N4" s="48" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O4" s="47" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P4" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="O4" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="50" t="s">
-        <v>43</v>
+      <c r="Q4" s="50" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R4" s="50" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S4" s="50" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T4" s="50" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U4" s="50" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V4" s="50" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="25" customHeight="1">
@@ -12534,8 +14506,9 @@
     </row>
     <row r="13" spans="1:22" ht="30" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="55" t="s">
-        <v>21</v>
+      <c r="B13" s="55" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C13" s="56" t="str">
         <f>B5</f>
@@ -13580,29 +15553,30 @@
     </row>
     <row r="41" spans="1:22" ht="32.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="93" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
-      <c r="N41" s="93"/>
-      <c r="O41" s="93"/>
-      <c r="P41" s="94"/>
-      <c r="Q41" s="94"/>
-      <c r="R41" s="94"/>
-      <c r="S41" s="94"/>
-      <c r="T41" s="94"/>
-      <c r="U41" s="94"/>
-      <c r="V41" s="94"/>
+      <c r="B41" s="97" t="str">
+        <f>VLOOKUP("label.hscSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 扫描</v>
+      </c>
+      <c r="C41" s="97"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="97"/>
+      <c r="F41" s="97"/>
+      <c r="G41" s="97"/>
+      <c r="H41" s="97"/>
+      <c r="I41" s="97"/>
+      <c r="J41" s="97"/>
+      <c r="K41" s="97"/>
+      <c r="L41" s="97"/>
+      <c r="M41" s="97"/>
+      <c r="N41" s="97"/>
+      <c r="O41" s="97"/>
+      <c r="P41" s="98"/>
+      <c r="Q41" s="98"/>
+      <c r="R41" s="98"/>
+      <c r="S41" s="98"/>
+      <c r="T41" s="98"/>
+      <c r="U41" s="98"/>
+      <c r="V41" s="98"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
@@ -13652,68 +15626,82 @@
       <c r="V43" s="4"/>
     </row>
     <row r="44" spans="1:22" ht="44.15" customHeight="1">
-      <c r="B44" s="50" t="s">
+      <c r="B44" s="50" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="D44" s="49" t="s">
+      <c r="F44" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="50" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H44" s="50" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I44" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="E44" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="H44" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="49" t="s">
+      <c r="K44" s="50" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L44" s="50" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M44" s="49" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N44" s="49" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O44" s="50" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P44" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="J44" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="L44" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="M44" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="N44" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="O44" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="P44" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q44" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="R44" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="S44" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="T44" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="U44" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="V44" s="50" t="s">
-        <v>43</v>
+      <c r="Q44" s="50" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R44" s="50" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S44" s="50" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T44" s="50" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U44" s="50" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V44" s="50" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="25" customHeight="1">
@@ -14216,8 +16204,9 @@
       <c r="V52" s="4"/>
     </row>
     <row r="53" spans="2:22" ht="30" customHeight="1">
-      <c r="B53" s="59" t="s">
-        <v>21</v>
+      <c r="B53" s="59" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C53" s="60" t="str">
         <f>B45</f>
@@ -15234,29 +17223,30 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B81" s="94" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81" s="94"/>
-      <c r="D81" s="94"/>
-      <c r="E81" s="94"/>
-      <c r="F81" s="94"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="94"/>
-      <c r="I81" s="94"/>
-      <c r="J81" s="94"/>
-      <c r="K81" s="94"/>
-      <c r="L81" s="94"/>
-      <c r="M81" s="94"/>
-      <c r="N81" s="94"/>
-      <c r="O81" s="94"/>
-      <c r="P81" s="94"/>
-      <c r="Q81" s="94"/>
-      <c r="R81" s="94"/>
-      <c r="S81" s="94"/>
-      <c r="T81" s="94"/>
-      <c r="U81" s="94"/>
-      <c r="V81" s="94"/>
+      <c r="B81" s="98" t="str">
+        <f>VLOOKUP("label.lsrSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 扫描</v>
+      </c>
+      <c r="C81" s="98"/>
+      <c r="D81" s="98"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="98"/>
+      <c r="H81" s="98"/>
+      <c r="I81" s="98"/>
+      <c r="J81" s="98"/>
+      <c r="K81" s="98"/>
+      <c r="L81" s="98"/>
+      <c r="M81" s="98"/>
+      <c r="N81" s="98"/>
+      <c r="O81" s="98"/>
+      <c r="P81" s="98"/>
+      <c r="Q81" s="98"/>
+      <c r="R81" s="98"/>
+      <c r="S81" s="98"/>
+      <c r="T81" s="98"/>
+      <c r="U81" s="98"/>
+      <c r="V81" s="98"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -15305,68 +17295,82 @@
       <c r="V83" s="4"/>
     </row>
     <row r="84" spans="2:22" ht="44.15" customHeight="1">
-      <c r="B84" s="50" t="s">
+      <c r="B84" s="50" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C84" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C84" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="D84" s="49" t="s">
+      <c r="F84" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G84" s="50" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H84" s="50" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I84" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="E84" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="F84" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="G84" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="H84" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="I84" s="49" t="s">
+      <c r="K84" s="50" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L84" s="50" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M84" s="49" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N84" s="49" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O84" s="50" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P84" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="J84" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="K84" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="L84" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="M84" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="N84" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="O84" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="P84" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q84" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="R84" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="S84" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="T84" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="U84" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="V84" s="50" t="s">
-        <v>43</v>
+      <c r="Q84" s="50" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R84" s="50" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S84" s="50" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T84" s="50" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U84" s="50" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V84" s="50" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="85" spans="2:22" ht="25" customHeight="1">
@@ -15869,8 +17873,9 @@
       <c r="V92" s="4"/>
     </row>
     <row r="93" spans="2:22" ht="30" customHeight="1">
-      <c r="B93" s="59" t="s">
-        <v>21</v>
+      <c r="B93" s="59" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C93" s="60" t="str">
         <f>B85</f>
@@ -16887,29 +18892,30 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B121" s="94" t="s">
-        <v>96</v>
-      </c>
-      <c r="C121" s="94"/>
-      <c r="D121" s="94"/>
-      <c r="E121" s="94"/>
-      <c r="F121" s="94"/>
-      <c r="G121" s="94"/>
-      <c r="H121" s="94"/>
-      <c r="I121" s="94"/>
-      <c r="J121" s="94"/>
-      <c r="K121" s="94"/>
-      <c r="L121" s="94"/>
-      <c r="M121" s="94"/>
-      <c r="N121" s="94"/>
-      <c r="O121" s="94"/>
-      <c r="P121" s="94"/>
-      <c r="Q121" s="94"/>
-      <c r="R121" s="94"/>
-      <c r="S121" s="94"/>
-      <c r="T121" s="94"/>
-      <c r="U121" s="94"/>
-      <c r="V121" s="94"/>
+      <c r="B121" s="98" t="str">
+        <f>VLOOKUP("label.fullSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>全范围扫描</v>
+      </c>
+      <c r="C121" s="98"/>
+      <c r="D121" s="98"/>
+      <c r="E121" s="98"/>
+      <c r="F121" s="98"/>
+      <c r="G121" s="98"/>
+      <c r="H121" s="98"/>
+      <c r="I121" s="98"/>
+      <c r="J121" s="98"/>
+      <c r="K121" s="98"/>
+      <c r="L121" s="98"/>
+      <c r="M121" s="98"/>
+      <c r="N121" s="98"/>
+      <c r="O121" s="98"/>
+      <c r="P121" s="98"/>
+      <c r="Q121" s="98"/>
+      <c r="R121" s="98"/>
+      <c r="S121" s="98"/>
+      <c r="T121" s="98"/>
+      <c r="U121" s="98"/>
+      <c r="V121" s="98"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -16958,68 +18964,82 @@
       <c r="V123" s="4"/>
     </row>
     <row r="124" spans="2:22" ht="44.15" customHeight="1">
-      <c r="B124" s="50" t="s">
+      <c r="B124" s="50" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C124" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="E124" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C124" s="49" t="s">
-        <v>31</v>
-      </c>
-      <c r="D124" s="49" t="s">
+      <c r="F124" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G124" s="50" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H124" s="50" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I124" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J124" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="E124" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="F124" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="G124" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="H124" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="I124" s="49" t="s">
+      <c r="K124" s="50" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L124" s="50" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M124" s="49" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N124" s="49" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O124" s="50" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P124" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="J124" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="K124" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="L124" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="M124" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="N124" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="O124" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="P124" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q124" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="R124" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="S124" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="T124" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="U124" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="V124" s="50" t="s">
-        <v>43</v>
+      <c r="Q124" s="50" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R124" s="50" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S124" s="50" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T124" s="50" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U124" s="50" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V124" s="50" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="125" spans="2:22" ht="25" customHeight="1">
@@ -17522,8 +19542,9 @@
       <c r="V132" s="4"/>
     </row>
     <row r="133" spans="2:22" ht="30" customHeight="1">
-      <c r="B133" s="59" t="s">
-        <v>21</v>
+      <c r="B133" s="59" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C133" s="60" t="str">
         <f>B125</f>
@@ -18801,93 +20822,108 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32.15" customHeight="1">
-      <c r="B161" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C161" s="95"/>
-      <c r="D161" s="95"/>
-      <c r="E161" s="95"/>
-      <c r="F161" s="95"/>
-      <c r="G161" s="95"/>
-      <c r="H161" s="95"/>
-      <c r="I161" s="95"/>
-      <c r="J161" s="95"/>
-      <c r="K161" s="95"/>
-      <c r="L161" s="95"/>
-      <c r="M161" s="95"/>
-      <c r="N161" s="95"/>
-      <c r="O161" s="95"/>
-      <c r="P161" s="95"/>
-      <c r="Q161" s="95"/>
-      <c r="R161" s="95"/>
-      <c r="S161" s="95"/>
-      <c r="T161" s="95"/>
-      <c r="U161" s="95"/>
-      <c r="V161" s="95"/>
+      <c r="B161" s="99" t="str">
+        <f>VLOOKUP("label.calculator",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>计算器</v>
+      </c>
+      <c r="C161" s="99"/>
+      <c r="D161" s="99"/>
+      <c r="E161" s="99"/>
+      <c r="F161" s="99"/>
+      <c r="G161" s="99"/>
+      <c r="H161" s="99"/>
+      <c r="I161" s="99"/>
+      <c r="J161" s="99"/>
+      <c r="K161" s="99"/>
+      <c r="L161" s="99"/>
+      <c r="M161" s="99"/>
+      <c r="N161" s="99"/>
+      <c r="O161" s="99"/>
+      <c r="P161" s="99"/>
+      <c r="Q161" s="99"/>
+      <c r="R161" s="99"/>
+      <c r="S161" s="99"/>
+      <c r="T161" s="99"/>
+      <c r="U161" s="99"/>
+      <c r="V161" s="99"/>
     </row>
     <row r="164" spans="2:22" ht="44.15" customHeight="1">
-      <c r="B164" s="63" t="s">
+      <c r="B164" s="63" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C164" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="E164" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="C164" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="D164" s="64" t="s">
+      <c r="F164" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="G164" s="63" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H164" s="63" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I164" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="J164" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="E164" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="F164" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G164" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="H164" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="I164" s="64" t="s">
+      <c r="K164" s="63" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L164" s="63" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M164" s="64" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N164" s="64" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O164" s="63" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P164" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="J164" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="K164" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="L164" s="63" t="s">
-        <v>36</v>
-      </c>
-      <c r="M164" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="N164" s="64" t="s">
-        <v>16</v>
-      </c>
-      <c r="O164" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="P164" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q164" s="63" t="s">
-        <v>38</v>
-      </c>
-      <c r="R164" s="63" t="s">
-        <v>39</v>
-      </c>
-      <c r="S164" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="T164" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="U164" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="V164" s="63" t="s">
-        <v>43</v>
+      <c r="Q164" s="63" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R164" s="63" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S164" s="63" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T164" s="63" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U164" s="63" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V164" s="63" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="165" spans="2:22" ht="25" customHeight="1">
@@ -18983,5 +21019,6 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>